--- a/research/traditional_assets/database/data/luxembourg/luxembourg_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_metals_mining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nyse_nexa" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.008460000000000001</v>
+        <v>0.0265</v>
       </c>
       <c r="G2">
-        <v>0.2505600235026257</v>
+        <v>0.1018302327332982</v>
       </c>
       <c r="H2">
-        <v>0.2505600235026257</v>
+        <v>0.1018302327332982</v>
       </c>
       <c r="I2">
-        <v>-0.0207484117366237</v>
+        <v>0.06161030353242449</v>
       </c>
       <c r="J2">
-        <v>-0.0207484117366237</v>
+        <v>0.06161030353242449</v>
       </c>
       <c r="K2">
-        <v>-277.6</v>
+        <v>-198.4</v>
       </c>
       <c r="L2">
-        <v>-0.1019426389041901</v>
+        <v>-0.07471567372147322</v>
       </c>
       <c r="M2">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="N2">
-        <v>0.02686125211505922</v>
+        <v>0.0187044187044187</v>
       </c>
       <c r="O2">
-        <v>-0.09149855907780978</v>
+        <v>-0.1098790322580645</v>
       </c>
       <c r="P2">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="Q2">
-        <v>0.02686125211505922</v>
+        <v>0.0187044187044187</v>
       </c>
       <c r="R2">
-        <v>-0.09149855907780978</v>
+        <v>-0.1098790322580645</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>414.3</v>
+        <v>513.2</v>
       </c>
       <c r="V2">
-        <v>0.4381345177664975</v>
+        <v>0.4403260403260404</v>
       </c>
       <c r="W2">
-        <v>-0.1868479504610621</v>
+        <v>-0.1565285996055227</v>
       </c>
       <c r="X2">
-        <v>0.1440219029548346</v>
+        <v>0.141569501456546</v>
       </c>
       <c r="Y2">
-        <v>-0.3308698534158968</v>
+        <v>-0.2980981010620687</v>
       </c>
       <c r="Z2">
-        <v>1.225958941112912</v>
+        <v>1.219976109528623</v>
       </c>
       <c r="AA2">
-        <v>-0.02543670088240591</v>
+        <v>0.0751630984103648</v>
       </c>
       <c r="AB2">
-        <v>0.0783911765022809</v>
+        <v>0.08123697545714517</v>
       </c>
       <c r="AC2">
-        <v>-0.1038278773846868</v>
+        <v>-0.006073877046780377</v>
       </c>
       <c r="AD2">
-        <v>1668.1</v>
+        <v>1934.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1668.1</v>
+        <v>1934.4</v>
       </c>
       <c r="AG2">
-        <v>1253.8</v>
+        <v>1421.2</v>
       </c>
       <c r="AH2">
-        <v>0.6382140260932777</v>
+        <v>0.6240201296816027</v>
       </c>
       <c r="AI2">
-        <v>0.5198192583359301</v>
+        <v>0.6044811099653136</v>
       </c>
       <c r="AJ2">
-        <v>0.5700645630626534</v>
+        <v>0.5494259094599298</v>
       </c>
       <c r="AK2">
-        <v>0.4486349160911726</v>
+        <v>0.5289366928430533</v>
       </c>
       <c r="AL2">
-        <v>167.9</v>
+        <v>197.9</v>
       </c>
       <c r="AM2">
-        <v>153.4</v>
+        <v>185.9</v>
       </c>
       <c r="AN2">
-        <v>6.221932114882506</v>
+        <v>4.076712328767123</v>
       </c>
       <c r="AO2">
-        <v>-0.3365098272781417</v>
+        <v>0.8266801414855988</v>
       </c>
       <c r="AP2">
-        <v>4.676613204028347</v>
+        <v>2.995152792413066</v>
       </c>
       <c r="AQ2">
-        <v>-0.3683181225554107</v>
+        <v>0.8800430338891877</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +721,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.008460000000000001</v>
+        <v>0.0265</v>
       </c>
       <c r="G3">
-        <v>0.2505600235026257</v>
+        <v>0.1018302327332982</v>
       </c>
       <c r="H3">
-        <v>0.2505600235026257</v>
+        <v>0.1018302327332982</v>
       </c>
       <c r="I3">
-        <v>-0.0207484117366237</v>
+        <v>0.06161030353242449</v>
       </c>
       <c r="J3">
-        <v>-0.0207484117366237</v>
+        <v>0.06161030353242449</v>
       </c>
       <c r="K3">
-        <v>-277.6</v>
+        <v>-198.4</v>
       </c>
       <c r="L3">
-        <v>-0.1019426389041901</v>
+        <v>-0.07471567372147322</v>
       </c>
       <c r="M3">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="N3">
-        <v>0.02686125211505922</v>
+        <v>0.0187044187044187</v>
       </c>
       <c r="O3">
-        <v>-0.09149855907780978</v>
+        <v>-0.1098790322580645</v>
       </c>
       <c r="P3">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="Q3">
-        <v>0.02686125211505922</v>
+        <v>0.0187044187044187</v>
       </c>
       <c r="R3">
-        <v>-0.09149855907780978</v>
+        <v>-0.1098790322580645</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +766,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>414.3</v>
+        <v>513.2</v>
       </c>
       <c r="V3">
-        <v>0.4381345177664975</v>
+        <v>0.4403260403260404</v>
       </c>
       <c r="W3">
-        <v>-0.1868479504610621</v>
+        <v>-0.1565285996055227</v>
       </c>
       <c r="X3">
-        <v>0.1440219029548346</v>
+        <v>0.141569501456546</v>
       </c>
       <c r="Y3">
-        <v>-0.3308698534158968</v>
+        <v>-0.2980981010620687</v>
       </c>
       <c r="Z3">
-        <v>1.225958941112912</v>
+        <v>1.219976109528623</v>
       </c>
       <c r="AA3">
-        <v>-0.02543670088240591</v>
+        <v>0.0751630984103648</v>
       </c>
       <c r="AB3">
-        <v>0.0783911765022809</v>
+        <v>0.08123697545714517</v>
       </c>
       <c r="AC3">
-        <v>-0.1038278773846868</v>
+        <v>-0.006073877046780377</v>
       </c>
       <c r="AD3">
-        <v>1668.1</v>
+        <v>1934.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1668.1</v>
+        <v>1934.4</v>
       </c>
       <c r="AG3">
-        <v>1253.8</v>
+        <v>1421.2</v>
       </c>
       <c r="AH3">
-        <v>0.6382140260932777</v>
+        <v>0.6240201296816027</v>
       </c>
       <c r="AI3">
-        <v>0.5198192583359301</v>
+        <v>0.6044811099653136</v>
       </c>
       <c r="AJ3">
-        <v>0.5700645630626534</v>
+        <v>0.5494259094599298</v>
       </c>
       <c r="AK3">
-        <v>0.4486349160911726</v>
+        <v>0.5289366928430533</v>
       </c>
       <c r="AL3">
-        <v>167.9</v>
+        <v>197.9</v>
       </c>
       <c r="AM3">
-        <v>153.4</v>
+        <v>185.9</v>
       </c>
       <c r="AN3">
-        <v>6.221932114882506</v>
+        <v>4.076712328767123</v>
       </c>
       <c r="AO3">
-        <v>-0.3365098272781417</v>
+        <v>0.8266801414855988</v>
       </c>
       <c r="AP3">
-        <v>4.676613204028347</v>
+        <v>2.995152792413066</v>
       </c>
       <c r="AQ3">
-        <v>-0.3683181225554107</v>
+        <v>0.8800430338891877</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nexa Resources S.A. (NYSE:NEXA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NYSE:NEXA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2.36099039919151</v>
+      </c>
+      <c r="F2">
+        <v>4.50071658190688</v>
+      </c>
+      <c r="G2">
+        <v>4.07671232876712</v>
+      </c>
+      <c r="H2">
+        <v>6.33699262381454</v>
+      </c>
+      <c r="I2">
+        <v>0.624020129681603</v>
+      </c>
+      <c r="J2">
+        <v>0.97</v>
+      </c>
+      <c r="K2">
+        <v>1165.5</v>
+      </c>
+      <c r="L2">
+        <v>555.925535092496</v>
+      </c>
+      <c r="M2">
+        <v>2586.7</v>
+      </c>
+      <c r="N2">
+        <v>3049.6285350925</v>
+      </c>
+      <c r="O2">
+        <v>1934.4</v>
+      </c>
+      <c r="P2">
+        <v>3006.903</v>
+      </c>
+      <c r="Q2">
+        <v>0.0812369754571452</v>
+      </c>
+      <c r="R2">
+        <v>0.0758577015725678</v>
+      </c>
+      <c r="S2">
+        <v>0.04488588</v>
+      </c>
+      <c r="T2">
+        <v>0.04345974</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.141569501456546</v>
+      </c>
+      <c r="X2">
+        <v>1.12339179241893</v>
+      </c>
+      <c r="Y2">
+        <v>2.210344807899</v>
+      </c>
+      <c r="Z2">
+        <v>24.8706465751885</v>
+      </c>
+      <c r="AA2">
+        <v>1934.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.0598</v>
+      </c>
+      <c r="AC2">
+        <v>2.360990399191511</v>
+      </c>
+      <c r="AD2">
+        <v>1934.4</v>
+      </c>
+      <c r="AE2">
+        <v>197.9</v>
+      </c>
+      <c r="AF2">
+        <v>7.26</v>
+      </c>
+      <c r="AG2">
+        <v>474.5</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>1165.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.043327855959079</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2494</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>302.7</v>
+      </c>
+      <c r="AR2">
+        <v>197.9</v>
+      </c>
+      <c r="AS2">
+        <v>1934.4</v>
+      </c>
+      <c r="AT2">
+        <v>513.2</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08844413846070455</v>
+      </c>
+      <c r="C2">
+        <v>2662.729284064776</v>
+      </c>
+      <c r="D2">
+        <v>2149.529284064776</v>
+      </c>
+      <c r="E2">
+        <v>-1934.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>513.2</v>
+      </c>
+      <c r="H2">
+        <v>1165.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K2">
+        <v>7.26</v>
+      </c>
+      <c r="L2">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="O2">
+        <v>195.4231893333333</v>
+      </c>
+      <c r="P2">
+        <v>588.1501440000001</v>
+      </c>
+      <c r="Q2">
+        <v>595.4101440000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08844413846070455</v>
+      </c>
+      <c r="T2">
+        <v>0.984219909265296</v>
+      </c>
+      <c r="U2">
+        <v>0.0517</v>
+      </c>
+      <c r="V2">
+        <v>0.2494</v>
+      </c>
+      <c r="W2">
+        <v>0.03880602</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08826784417938355</v>
+      </c>
+      <c r="C3">
+        <v>2640.653499444204</v>
+      </c>
+      <c r="D3">
+        <v>2158.452499444204</v>
+      </c>
+      <c r="E3">
+        <v>-1903.401</v>
+      </c>
+      <c r="F3">
+        <v>30.99900000000001</v>
+      </c>
+      <c r="G3">
+        <v>513.2</v>
+      </c>
+      <c r="H3">
+        <v>1165.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K3">
+        <v>7.26</v>
+      </c>
+      <c r="L3">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M3">
+        <v>1.6026483</v>
+      </c>
+      <c r="N3">
+        <v>781.9706850333333</v>
+      </c>
+      <c r="O3">
+        <v>195.0234888473133</v>
+      </c>
+      <c r="P3">
+        <v>586.9471961860199</v>
+      </c>
+      <c r="Q3">
+        <v>594.2071961860199</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08876745856503389</v>
+      </c>
+      <c r="T3">
+        <v>0.991682085668271</v>
+      </c>
+      <c r="U3">
+        <v>0.0517</v>
+      </c>
+      <c r="V3">
+        <v>0.2494</v>
+      </c>
+      <c r="W3">
+        <v>0.03880602</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>488.9240723203794</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08809154989806256</v>
+      </c>
+      <c r="C4">
+        <v>2618.652108495473</v>
+      </c>
+      <c r="D4">
+        <v>2167.450108495474</v>
+      </c>
+      <c r="E4">
+        <v>-1872.402</v>
+      </c>
+      <c r="F4">
+        <v>61.99800000000001</v>
+      </c>
+      <c r="G4">
+        <v>513.2</v>
+      </c>
+      <c r="H4">
+        <v>1165.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K4">
+        <v>7.26</v>
+      </c>
+      <c r="L4">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M4">
+        <v>3.205296600000001</v>
+      </c>
+      <c r="N4">
+        <v>780.3680367333334</v>
+      </c>
+      <c r="O4">
+        <v>194.6237883612934</v>
+      </c>
+      <c r="P4">
+        <v>585.74424837204</v>
+      </c>
+      <c r="Q4">
+        <v>593.00424837204</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08909737703883935</v>
+      </c>
+      <c r="T4">
+        <v>0.9992965513855926</v>
+      </c>
+      <c r="U4">
+        <v>0.0517</v>
+      </c>
+      <c r="V4">
+        <v>0.2494</v>
+      </c>
+      <c r="W4">
+        <v>0.03880602</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>244.4620361601897</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08791525561674154</v>
+      </c>
+      <c r="C5">
+        <v>2596.72604545337</v>
+      </c>
+      <c r="D5">
+        <v>2176.52304545337</v>
+      </c>
+      <c r="E5">
+        <v>-1841.403</v>
+      </c>
+      <c r="F5">
+        <v>92.99700000000001</v>
+      </c>
+      <c r="G5">
+        <v>513.2</v>
+      </c>
+      <c r="H5">
+        <v>1165.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K5">
+        <v>7.26</v>
+      </c>
+      <c r="L5">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M5">
+        <v>4.807944900000001</v>
+      </c>
+      <c r="N5">
+        <v>778.7653884333333</v>
+      </c>
+      <c r="O5">
+        <v>194.2240878752733</v>
+      </c>
+      <c r="P5">
+        <v>584.54130055806</v>
+      </c>
+      <c r="Q5">
+        <v>591.80130055806</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08943409795540366</v>
+      </c>
+      <c r="T5">
+        <v>1.007068016396055</v>
+      </c>
+      <c r="U5">
+        <v>0.0517</v>
+      </c>
+      <c r="V5">
+        <v>0.2494</v>
+      </c>
+      <c r="W5">
+        <v>0.03880602</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>162.9746907734598</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08773896133542056</v>
+      </c>
+      <c r="C6">
+        <v>2574.876260261241</v>
+      </c>
+      <c r="D6">
+        <v>2185.672260261241</v>
+      </c>
+      <c r="E6">
+        <v>-1810.404</v>
+      </c>
+      <c r="F6">
+        <v>123.996</v>
+      </c>
+      <c r="G6">
+        <v>513.2</v>
+      </c>
+      <c r="H6">
+        <v>1165.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K6">
+        <v>7.26</v>
+      </c>
+      <c r="L6">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M6">
+        <v>6.410593200000002</v>
+      </c>
+      <c r="N6">
+        <v>777.1627401333334</v>
+      </c>
+      <c r="O6">
+        <v>193.8243873892534</v>
+      </c>
+      <c r="P6">
+        <v>583.33835274408</v>
+      </c>
+      <c r="Q6">
+        <v>590.59835274408</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08977783389106309</v>
+      </c>
+      <c r="T6">
+        <v>1.015001386927568</v>
+      </c>
+      <c r="U6">
+        <v>0.0517</v>
+      </c>
+      <c r="V6">
+        <v>0.2494</v>
+      </c>
+      <c r="W6">
+        <v>0.03880602</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>122.2310180800949</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08756266705409955</v>
+      </c>
+      <c r="C7">
+        <v>2553.103718902565</v>
+      </c>
+      <c r="D7">
+        <v>2194.898718902564</v>
+      </c>
+      <c r="E7">
+        <v>-1779.405</v>
+      </c>
+      <c r="F7">
+        <v>154.995</v>
+      </c>
+      <c r="G7">
+        <v>513.2</v>
+      </c>
+      <c r="H7">
+        <v>1165.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K7">
+        <v>7.26</v>
+      </c>
+      <c r="L7">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M7">
+        <v>8.013241500000003</v>
+      </c>
+      <c r="N7">
+        <v>775.5600918333333</v>
+      </c>
+      <c r="O7">
+        <v>193.4246869032334</v>
+      </c>
+      <c r="P7">
+        <v>582.1354049301</v>
+      </c>
+      <c r="Q7">
+        <v>589.3954049301</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09012880637273638</v>
+      </c>
+      <c r="T7">
+        <v>1.023101775786061</v>
+      </c>
+      <c r="U7">
+        <v>0.0517</v>
+      </c>
+      <c r="V7">
+        <v>0.2494</v>
+      </c>
+      <c r="W7">
+        <v>0.03880602</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>97.78481446407588</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08738637277277857</v>
+      </c>
+      <c r="C8">
+        <v>2531.409403740925</v>
+      </c>
+      <c r="D8">
+        <v>2204.203403740925</v>
+      </c>
+      <c r="E8">
+        <v>-1748.406</v>
+      </c>
+      <c r="F8">
+        <v>185.994</v>
+      </c>
+      <c r="G8">
+        <v>513.2</v>
+      </c>
+      <c r="H8">
+        <v>1165.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K8">
+        <v>7.26</v>
+      </c>
+      <c r="L8">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M8">
+        <v>9.615889800000001</v>
+      </c>
+      <c r="N8">
+        <v>773.9574435333334</v>
+      </c>
+      <c r="O8">
+        <v>193.0249864172133</v>
+      </c>
+      <c r="P8">
+        <v>580.9324571161201</v>
+      </c>
+      <c r="Q8">
+        <v>588.1924571161201</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09048724635401975</v>
+      </c>
+      <c r="T8">
+        <v>1.03137451334367</v>
+      </c>
+      <c r="U8">
+        <v>0.0517</v>
+      </c>
+      <c r="V8">
+        <v>0.2494</v>
+      </c>
+      <c r="W8">
+        <v>0.03880602</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>81.48734538672991</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08721007849145758</v>
+      </c>
+      <c r="C9">
+        <v>2509.794313868696</v>
+      </c>
+      <c r="D9">
+        <v>2213.587313868696</v>
+      </c>
+      <c r="E9">
+        <v>-1717.407</v>
+      </c>
+      <c r="F9">
+        <v>216.9930000000001</v>
+      </c>
+      <c r="G9">
+        <v>513.2</v>
+      </c>
+      <c r="H9">
+        <v>1165.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K9">
+        <v>7.26</v>
+      </c>
+      <c r="L9">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M9">
+        <v>11.2185381</v>
+      </c>
+      <c r="N9">
+        <v>772.3547952333333</v>
+      </c>
+      <c r="O9">
+        <v>192.6252859311933</v>
+      </c>
+      <c r="P9">
+        <v>579.7295093021401</v>
+      </c>
+      <c r="Q9">
+        <v>586.98950930214</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.0908533947219974</v>
+      </c>
+      <c r="T9">
+        <v>1.039825159235852</v>
+      </c>
+      <c r="U9">
+        <v>0.0517</v>
+      </c>
+      <c r="V9">
+        <v>0.2494</v>
+      </c>
+      <c r="W9">
+        <v>0.03880602</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>69.84629604576848</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08703378421013658</v>
+      </c>
+      <c r="C10">
+        <v>2488.259465464654</v>
+      </c>
+      <c r="D10">
+        <v>2223.051465464654</v>
+      </c>
+      <c r="E10">
+        <v>-1686.408</v>
+      </c>
+      <c r="F10">
+        <v>247.992</v>
+      </c>
+      <c r="G10">
+        <v>513.2</v>
+      </c>
+      <c r="H10">
+        <v>1165.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K10">
+        <v>7.26</v>
+      </c>
+      <c r="L10">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M10">
+        <v>12.8211864</v>
+      </c>
+      <c r="N10">
+        <v>770.7521469333334</v>
+      </c>
+      <c r="O10">
+        <v>192.2255854451734</v>
+      </c>
+      <c r="P10">
+        <v>578.52656148816</v>
+      </c>
+      <c r="Q10">
+        <v>585.78656148816</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09122750283710497</v>
+      </c>
+      <c r="T10">
+        <v>1.048459514821342</v>
+      </c>
+      <c r="U10">
+        <v>0.0517</v>
+      </c>
+      <c r="V10">
+        <v>0.2494</v>
+      </c>
+      <c r="W10">
+        <v>0.03880602</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>61.11550904004743</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08685748992881558</v>
+      </c>
+      <c r="C11">
+        <v>2466.805892160811</v>
+      </c>
+      <c r="D11">
+        <v>2232.596892160811</v>
+      </c>
+      <c r="E11">
+        <v>-1655.409</v>
+      </c>
+      <c r="F11">
+        <v>278.991</v>
+      </c>
+      <c r="G11">
+        <v>513.2</v>
+      </c>
+      <c r="H11">
+        <v>1165.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K11">
+        <v>7.26</v>
+      </c>
+      <c r="L11">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M11">
+        <v>14.4238347</v>
+      </c>
+      <c r="N11">
+        <v>769.1494986333333</v>
+      </c>
+      <c r="O11">
+        <v>191.8258849591533</v>
+      </c>
+      <c r="P11">
+        <v>577.32361367418</v>
+      </c>
+      <c r="Q11">
+        <v>584.58361367418</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09160983310858854</v>
+      </c>
+      <c r="T11">
+        <v>1.057283636463656</v>
+      </c>
+      <c r="U11">
+        <v>0.0517</v>
+      </c>
+      <c r="V11">
+        <v>0.2494</v>
+      </c>
+      <c r="W11">
+        <v>0.03880602</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>54.32489692448661</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08668119564749459</v>
+      </c>
+      <c r="C12">
+        <v>2445.434645418734</v>
+      </c>
+      <c r="D12">
+        <v>2242.224645418734</v>
+      </c>
+      <c r="E12">
+        <v>-1624.41</v>
+      </c>
+      <c r="F12">
+        <v>309.9900000000001</v>
+      </c>
+      <c r="G12">
+        <v>513.2</v>
+      </c>
+      <c r="H12">
+        <v>1165.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K12">
+        <v>7.26</v>
+      </c>
+      <c r="L12">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M12">
+        <v>16.02648300000001</v>
+      </c>
+      <c r="N12">
+        <v>767.5468503333334</v>
+      </c>
+      <c r="O12">
+        <v>191.4261844731334</v>
+      </c>
+      <c r="P12">
+        <v>576.1206658602</v>
+      </c>
+      <c r="Q12">
+        <v>583.3806658602</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09200065960832732</v>
+      </c>
+      <c r="T12">
+        <v>1.066303849698022</v>
+      </c>
+      <c r="U12">
+        <v>0.0517</v>
+      </c>
+      <c r="V12">
+        <v>0.2494</v>
+      </c>
+      <c r="W12">
+        <v>0.03880602</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>48.89240723203794</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08650490136617359</v>
+      </c>
+      <c r="C13">
+        <v>2424.146794915655</v>
+      </c>
+      <c r="D13">
+        <v>2251.935794915655</v>
+      </c>
+      <c r="E13">
+        <v>-1593.411</v>
+      </c>
+      <c r="F13">
+        <v>340.9890000000001</v>
+      </c>
+      <c r="G13">
+        <v>513.2</v>
+      </c>
+      <c r="H13">
+        <v>1165.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K13">
+        <v>7.26</v>
+      </c>
+      <c r="L13">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M13">
+        <v>17.6291313</v>
+      </c>
+      <c r="N13">
+        <v>765.9442020333333</v>
+      </c>
+      <c r="O13">
+        <v>191.0264839871134</v>
+      </c>
+      <c r="P13">
+        <v>574.91771804622</v>
+      </c>
+      <c r="Q13">
+        <v>582.17771804622</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09240026872603774</v>
+      </c>
+      <c r="T13">
+        <v>1.075526764353384</v>
+      </c>
+      <c r="U13">
+        <v>0.0517</v>
+      </c>
+      <c r="V13">
+        <v>0.2494</v>
+      </c>
+      <c r="W13">
+        <v>0.03880602</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>44.44764293821631</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08632860708485258</v>
+      </c>
+      <c r="C14">
+        <v>2402.943428940641</v>
+      </c>
+      <c r="D14">
+        <v>2261.731428940641</v>
+      </c>
+      <c r="E14">
+        <v>-1562.412</v>
+      </c>
+      <c r="F14">
+        <v>371.9880000000001</v>
+      </c>
+      <c r="G14">
+        <v>513.2</v>
+      </c>
+      <c r="H14">
+        <v>1165.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K14">
+        <v>7.26</v>
+      </c>
+      <c r="L14">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M14">
+        <v>19.2317796</v>
+      </c>
+      <c r="N14">
+        <v>764.3415537333334</v>
+      </c>
+      <c r="O14">
+        <v>190.6267835010934</v>
+      </c>
+      <c r="P14">
+        <v>573.71477023224</v>
+      </c>
+      <c r="Q14">
+        <v>580.97477023224</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09280895986915066</v>
+      </c>
+      <c r="T14">
+        <v>1.084959290705459</v>
+      </c>
+      <c r="U14">
+        <v>0.0517</v>
+      </c>
+      <c r="V14">
+        <v>0.2494</v>
+      </c>
+      <c r="W14">
+        <v>0.03880602</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>40.74367269336496</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08615231280353158</v>
+      </c>
+      <c r="C15">
+        <v>2381.825654801165</v>
+      </c>
+      <c r="D15">
+        <v>2271.612654801165</v>
+      </c>
+      <c r="E15">
+        <v>-1531.413</v>
+      </c>
+      <c r="F15">
+        <v>402.9870000000001</v>
+      </c>
+      <c r="G15">
+        <v>513.2</v>
+      </c>
+      <c r="H15">
+        <v>1165.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K15">
+        <v>7.26</v>
+      </c>
+      <c r="L15">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M15">
+        <v>20.8344279</v>
+      </c>
+      <c r="N15">
+        <v>762.7389054333333</v>
+      </c>
+      <c r="O15">
+        <v>190.2270830150733</v>
+      </c>
+      <c r="P15">
+        <v>572.51182241826</v>
+      </c>
+      <c r="Q15">
+        <v>579.7718224182599</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09322704621095584</v>
+      </c>
+      <c r="T15">
+        <v>1.094608656743789</v>
+      </c>
+      <c r="U15">
+        <v>0.0517</v>
+      </c>
+      <c r="V15">
+        <v>0.2494</v>
+      </c>
+      <c r="W15">
+        <v>0.03880602</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>37.60954402464457</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.0859760185222106</v>
+      </c>
+      <c r="C16">
+        <v>2360.79459924037</v>
+      </c>
+      <c r="D16">
+        <v>2281.58059924037</v>
+      </c>
+      <c r="E16">
+        <v>-1500.414</v>
+      </c>
+      <c r="F16">
+        <v>433.9860000000001</v>
+      </c>
+      <c r="G16">
+        <v>513.2</v>
+      </c>
+      <c r="H16">
+        <v>1165.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K16">
+        <v>7.26</v>
+      </c>
+      <c r="L16">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M16">
+        <v>22.43707620000001</v>
+      </c>
+      <c r="N16">
+        <v>761.1362571333334</v>
+      </c>
+      <c r="O16">
+        <v>189.8273825290534</v>
+      </c>
+      <c r="P16">
+        <v>571.30887460428</v>
+      </c>
+      <c r="Q16">
+        <v>578.56887460428</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09365485549094255</v>
+      </c>
+      <c r="T16">
+        <v>1.104482426643476</v>
+      </c>
+      <c r="U16">
+        <v>0.0517</v>
+      </c>
+      <c r="V16">
+        <v>0.2494</v>
+      </c>
+      <c r="W16">
+        <v>0.03880602</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>34.92314802288425</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08579972424088958</v>
+      </c>
+      <c r="C17">
+        <v>2339.851408865374</v>
+      </c>
+      <c r="D17">
+        <v>2291.636408865374</v>
+      </c>
+      <c r="E17">
+        <v>-1469.415</v>
+      </c>
+      <c r="F17">
+        <v>464.9850000000001</v>
+      </c>
+      <c r="G17">
+        <v>513.2</v>
+      </c>
+      <c r="H17">
+        <v>1165.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K17">
+        <v>7.26</v>
+      </c>
+      <c r="L17">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M17">
+        <v>24.03972450000001</v>
+      </c>
+      <c r="N17">
+        <v>759.5336088333333</v>
+      </c>
+      <c r="O17">
+        <v>189.4276820430333</v>
+      </c>
+      <c r="P17">
+        <v>570.1059267903</v>
+      </c>
+      <c r="Q17">
+        <v>577.3659267903</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09409273087163481</v>
+      </c>
+      <c r="T17">
+        <v>1.114588520540801</v>
+      </c>
+      <c r="U17">
+        <v>0.0517</v>
+      </c>
+      <c r="V17">
+        <v>0.2494</v>
+      </c>
+      <c r="W17">
+        <v>0.03880602</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>32.59493815469196</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08562342995956859</v>
+      </c>
+      <c r="C18">
+        <v>2318.997250586946</v>
+      </c>
+      <c r="D18">
+        <v>2301.781250586946</v>
+      </c>
+      <c r="E18">
+        <v>-1438.416</v>
+      </c>
+      <c r="F18">
+        <v>495.9840000000001</v>
+      </c>
+      <c r="G18">
+        <v>513.2</v>
+      </c>
+      <c r="H18">
+        <v>1165.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K18">
+        <v>7.26</v>
+      </c>
+      <c r="L18">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M18">
+        <v>25.64237280000001</v>
+      </c>
+      <c r="N18">
+        <v>757.9309605333334</v>
+      </c>
+      <c r="O18">
+        <v>189.0279815570134</v>
+      </c>
+      <c r="P18">
+        <v>568.90297897632</v>
+      </c>
+      <c r="Q18">
+        <v>576.16297897632</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09454103185662928</v>
+      </c>
+      <c r="T18">
+        <v>1.124935235721397</v>
+      </c>
+      <c r="U18">
+        <v>0.0517</v>
+      </c>
+      <c r="V18">
+        <v>0.2494</v>
+      </c>
+      <c r="W18">
+        <v>0.03880602</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>30.55775452002371</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.0854471356782476</v>
+      </c>
+      <c r="C19">
+        <v>2298.233312070921</v>
+      </c>
+      <c r="D19">
+        <v>2312.016312070921</v>
+      </c>
+      <c r="E19">
+        <v>-1407.417</v>
+      </c>
+      <c r="F19">
+        <v>526.9830000000002</v>
+      </c>
+      <c r="G19">
+        <v>513.2</v>
+      </c>
+      <c r="H19">
+        <v>1165.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K19">
+        <v>7.26</v>
+      </c>
+      <c r="L19">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M19">
+        <v>27.24502110000001</v>
+      </c>
+      <c r="N19">
+        <v>756.3283122333333</v>
+      </c>
+      <c r="O19">
+        <v>188.6282810709934</v>
+      </c>
+      <c r="P19">
+        <v>567.70003116234</v>
+      </c>
+      <c r="Q19">
+        <v>574.96003116234</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09500013527499712</v>
+      </c>
+      <c r="T19">
+        <v>1.13553126934008</v>
+      </c>
+      <c r="U19">
+        <v>0.0517</v>
+      </c>
+      <c r="V19">
+        <v>0.2494</v>
+      </c>
+      <c r="W19">
+        <v>0.03880602</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>28.76023954825761</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08527084139692662</v>
+      </c>
+      <c r="C20">
+        <v>2277.5608022017</v>
+      </c>
+      <c r="D20">
+        <v>2322.342802201701</v>
+      </c>
+      <c r="E20">
+        <v>-1376.418</v>
+      </c>
+      <c r="F20">
+        <v>557.9820000000001</v>
+      </c>
+      <c r="G20">
+        <v>513.2</v>
+      </c>
+      <c r="H20">
+        <v>1165.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K20">
+        <v>7.26</v>
+      </c>
+      <c r="L20">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M20">
+        <v>28.8476694</v>
+      </c>
+      <c r="N20">
+        <v>754.7256639333334</v>
+      </c>
+      <c r="O20">
+        <v>188.2285805849734</v>
+      </c>
+      <c r="P20">
+        <v>566.4970833483601</v>
+      </c>
+      <c r="Q20">
+        <v>573.7570833483601</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09547043633771538</v>
+      </c>
+      <c r="T20">
+        <v>1.14638574280312</v>
+      </c>
+      <c r="U20">
+        <v>0.0517</v>
+      </c>
+      <c r="V20">
+        <v>0.2494</v>
+      </c>
+      <c r="W20">
+        <v>0.03880602</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>27.16244846224331</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.0850945471156056</v>
+      </c>
+      <c r="C21">
+        <v>2256.980951558242</v>
+      </c>
+      <c r="D21">
+        <v>2332.761951558243</v>
+      </c>
+      <c r="E21">
+        <v>-1345.419</v>
+      </c>
+      <c r="F21">
+        <v>588.9810000000001</v>
+      </c>
+      <c r="G21">
+        <v>513.2</v>
+      </c>
+      <c r="H21">
+        <v>1165.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K21">
+        <v>7.26</v>
+      </c>
+      <c r="L21">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M21">
+        <v>30.45031770000001</v>
+      </c>
+      <c r="N21">
+        <v>753.1230156333334</v>
+      </c>
+      <c r="O21">
+        <v>187.8288800989533</v>
+      </c>
+      <c r="P21">
+        <v>565.2941355343801</v>
+      </c>
+      <c r="Q21">
+        <v>572.5541355343801</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09595234977235259</v>
+      </c>
+      <c r="T21">
+        <v>1.157508227956606</v>
+      </c>
+      <c r="U21">
+        <v>0.0517</v>
+      </c>
+      <c r="V21">
+        <v>0.2494</v>
+      </c>
+      <c r="W21">
+        <v>0.03880602</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>25.73284591159892</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.0849182528342846</v>
+      </c>
+      <c r="C22">
+        <v>2236.495012902908</v>
+      </c>
+      <c r="D22">
+        <v>2343.275012902908</v>
+      </c>
+      <c r="E22">
+        <v>-1314.42</v>
+      </c>
+      <c r="F22">
+        <v>619.9800000000001</v>
+      </c>
+      <c r="G22">
+        <v>513.2</v>
+      </c>
+      <c r="H22">
+        <v>1165.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K22">
+        <v>7.26</v>
+      </c>
+      <c r="L22">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M22">
+        <v>32.05296600000001</v>
+      </c>
+      <c r="N22">
+        <v>751.5203673333334</v>
+      </c>
+      <c r="O22">
+        <v>187.4291796129334</v>
+      </c>
+      <c r="P22">
+        <v>564.0911877204001</v>
+      </c>
+      <c r="Q22">
+        <v>571.3511877204</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09644631104285575</v>
+      </c>
+      <c r="T22">
+        <v>1.168908775238929</v>
+      </c>
+      <c r="U22">
+        <v>0.0517</v>
+      </c>
+      <c r="V22">
+        <v>0.2494</v>
+      </c>
+      <c r="W22">
+        <v>0.03880602</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>24.44620361601897</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08474195855296363</v>
+      </c>
+      <c r="C23">
+        <v>2216.104261683596</v>
+      </c>
+      <c r="D23">
+        <v>2353.883261683596</v>
+      </c>
+      <c r="E23">
+        <v>-1283.421</v>
+      </c>
+      <c r="F23">
+        <v>650.979</v>
+      </c>
+      <c r="G23">
+        <v>513.2</v>
+      </c>
+      <c r="H23">
+        <v>1165.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K23">
+        <v>7.26</v>
+      </c>
+      <c r="L23">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M23">
+        <v>33.6556143</v>
+      </c>
+      <c r="N23">
+        <v>749.9177190333334</v>
+      </c>
+      <c r="O23">
+        <v>187.0294791269133</v>
+      </c>
+      <c r="P23">
+        <v>562.88823990642</v>
+      </c>
+      <c r="Q23">
+        <v>570.14823990642</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09695277766197927</v>
+      </c>
+      <c r="T23">
+        <v>1.180597943971437</v>
+      </c>
+      <c r="U23">
+        <v>0.0517</v>
+      </c>
+      <c r="V23">
+        <v>0.2494</v>
+      </c>
+      <c r="W23">
+        <v>0.03880602</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>23.28209868192283</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08456566427164262</v>
+      </c>
+      <c r="C24">
+        <v>2195.809996549589</v>
+      </c>
+      <c r="D24">
+        <v>2364.58799654959</v>
+      </c>
+      <c r="E24">
+        <v>-1252.422</v>
+      </c>
+      <c r="F24">
+        <v>681.9780000000002</v>
+      </c>
+      <c r="G24">
+        <v>513.2</v>
+      </c>
+      <c r="H24">
+        <v>1165.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K24">
+        <v>7.26</v>
+      </c>
+      <c r="L24">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M24">
+        <v>35.25826260000001</v>
+      </c>
+      <c r="N24">
+        <v>748.3150707333334</v>
+      </c>
+      <c r="O24">
+        <v>186.6297786408934</v>
+      </c>
+      <c r="P24">
+        <v>561.68529209244</v>
+      </c>
+      <c r="Q24">
+        <v>568.94529209244</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09747223060467003</v>
+      </c>
+      <c r="T24">
+        <v>1.192586834979138</v>
+      </c>
+      <c r="U24">
+        <v>0.0517</v>
+      </c>
+      <c r="V24">
+        <v>0.2494</v>
+      </c>
+      <c r="W24">
+        <v>0.03880602</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>22.22382146910816</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08438936999032162</v>
+      </c>
+      <c r="C25">
+        <v>2175.61353988151</v>
+      </c>
+      <c r="D25">
+        <v>2375.39053988151</v>
+      </c>
+      <c r="E25">
+        <v>-1221.423</v>
+      </c>
+      <c r="F25">
+        <v>712.9770000000002</v>
+      </c>
+      <c r="G25">
+        <v>513.2</v>
+      </c>
+      <c r="H25">
+        <v>1165.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K25">
+        <v>7.26</v>
+      </c>
+      <c r="L25">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M25">
+        <v>36.86091090000001</v>
+      </c>
+      <c r="N25">
+        <v>746.7124224333334</v>
+      </c>
+      <c r="O25">
+        <v>186.2300781548734</v>
+      </c>
+      <c r="P25">
+        <v>560.48234427846</v>
+      </c>
+      <c r="Q25">
+        <v>567.74234427846</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09800517583158652</v>
+      </c>
+      <c r="T25">
+        <v>1.204887125753273</v>
+      </c>
+      <c r="U25">
+        <v>0.0517</v>
+      </c>
+      <c r="V25">
+        <v>0.2494</v>
+      </c>
+      <c r="W25">
+        <v>0.03880602</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>21.25756836175562</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08421307570900062</v>
+      </c>
+      <c r="C26">
+        <v>2155.516238335899</v>
+      </c>
+      <c r="D26">
+        <v>2386.292238335899</v>
+      </c>
+      <c r="E26">
+        <v>-1190.424</v>
+      </c>
+      <c r="F26">
+        <v>743.9760000000001</v>
+      </c>
+      <c r="G26">
+        <v>513.2</v>
+      </c>
+      <c r="H26">
+        <v>1165.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K26">
+        <v>7.26</v>
+      </c>
+      <c r="L26">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M26">
+        <v>38.46355920000001</v>
+      </c>
+      <c r="N26">
+        <v>745.1097741333334</v>
+      </c>
+      <c r="O26">
+        <v>185.8303776688534</v>
+      </c>
+      <c r="P26">
+        <v>559.27939646448</v>
+      </c>
+      <c r="Q26">
+        <v>566.53939646448</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09855214593289555</v>
+      </c>
+      <c r="T26">
+        <v>1.217511108389885</v>
+      </c>
+      <c r="U26">
+        <v>0.0517</v>
+      </c>
+      <c r="V26">
+        <v>0.2494</v>
+      </c>
+      <c r="W26">
+        <v>0.03880602</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>20.37183634668248</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08403678142767962</v>
+      </c>
+      <c r="C27">
+        <v>2135.519463404842</v>
+      </c>
+      <c r="D27">
+        <v>2397.294463404842</v>
+      </c>
+      <c r="E27">
+        <v>-1159.425</v>
+      </c>
+      <c r="F27">
+        <v>774.9750000000001</v>
+      </c>
+      <c r="G27">
+        <v>513.2</v>
+      </c>
+      <c r="H27">
+        <v>1165.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K27">
+        <v>7.26</v>
+      </c>
+      <c r="L27">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M27">
+        <v>40.06620750000001</v>
+      </c>
+      <c r="N27">
+        <v>743.5071258333334</v>
+      </c>
+      <c r="O27">
+        <v>185.4306771828333</v>
+      </c>
+      <c r="P27">
+        <v>558.0764486505</v>
+      </c>
+      <c r="Q27">
+        <v>565.3364486505</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09911370190357283</v>
+      </c>
+      <c r="T27">
+        <v>1.230471730563473</v>
+      </c>
+      <c r="U27">
+        <v>0.0517</v>
+      </c>
+      <c r="V27">
+        <v>0.2494</v>
+      </c>
+      <c r="W27">
+        <v>0.03880602</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>19.55696289281518</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08386048714635863</v>
+      </c>
+      <c r="C28">
+        <v>2115.624611991158</v>
+      </c>
+      <c r="D28">
+        <v>2408.398611991158</v>
+      </c>
+      <c r="E28">
+        <v>-1128.426</v>
+      </c>
+      <c r="F28">
+        <v>805.9740000000002</v>
+      </c>
+      <c r="G28">
+        <v>513.2</v>
+      </c>
+      <c r="H28">
+        <v>1165.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K28">
+        <v>7.26</v>
+      </c>
+      <c r="L28">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M28">
+        <v>41.66885580000001</v>
+      </c>
+      <c r="N28">
+        <v>741.9044775333334</v>
+      </c>
+      <c r="O28">
+        <v>185.0309766968134</v>
+      </c>
+      <c r="P28">
+        <v>556.8735008365201</v>
+      </c>
+      <c r="Q28">
+        <v>564.1335008365201</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.0996904350626468</v>
+      </c>
+      <c r="T28">
+        <v>1.243782639822834</v>
+      </c>
+      <c r="U28">
+        <v>0.0517</v>
+      </c>
+      <c r="V28">
+        <v>0.2494</v>
+      </c>
+      <c r="W28">
+        <v>0.03880602</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>18.80477201232229</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08368419286503762</v>
+      </c>
+      <c r="C29">
+        <v>2095.833106999647</v>
+      </c>
+      <c r="D29">
+        <v>2419.606106999646</v>
+      </c>
+      <c r="E29">
+        <v>-1097.427</v>
+      </c>
+      <c r="F29">
+        <v>836.9730000000002</v>
+      </c>
+      <c r="G29">
+        <v>513.2</v>
+      </c>
+      <c r="H29">
+        <v>1165.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K29">
+        <v>7.26</v>
+      </c>
+      <c r="L29">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M29">
+        <v>43.27150410000001</v>
+      </c>
+      <c r="N29">
+        <v>740.3018292333334</v>
+      </c>
+      <c r="O29">
+        <v>184.6312762107933</v>
+      </c>
+      <c r="P29">
+        <v>555.67055302254</v>
+      </c>
+      <c r="Q29">
+        <v>562.93055302254</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1002829691301885</v>
+      </c>
+      <c r="T29">
+        <v>1.257458231527657</v>
+      </c>
+      <c r="U29">
+        <v>0.0517</v>
+      </c>
+      <c r="V29">
+        <v>0.2494</v>
+      </c>
+      <c r="W29">
+        <v>0.03880602</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>18.10829897482887</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08350789858371663</v>
+      </c>
+      <c r="C30">
+        <v>2076.146397944907</v>
+      </c>
+      <c r="D30">
+        <v>2430.918397944907</v>
+      </c>
+      <c r="E30">
+        <v>-1066.428</v>
+      </c>
+      <c r="F30">
+        <v>867.9720000000002</v>
+      </c>
+      <c r="G30">
+        <v>513.2</v>
+      </c>
+      <c r="H30">
+        <v>1165.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K30">
+        <v>7.26</v>
+      </c>
+      <c r="L30">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M30">
+        <v>44.87415240000001</v>
+      </c>
+      <c r="N30">
+        <v>738.6991809333333</v>
+      </c>
+      <c r="O30">
+        <v>184.2315757247733</v>
+      </c>
+      <c r="P30">
+        <v>554.4676052085599</v>
+      </c>
+      <c r="Q30">
+        <v>561.7276052085599</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1008919624773842</v>
+      </c>
+      <c r="T30">
+        <v>1.271513700779836</v>
+      </c>
+      <c r="U30">
+        <v>0.0517</v>
+      </c>
+      <c r="V30">
+        <v>0.2494</v>
+      </c>
+      <c r="W30">
+        <v>0.03880602</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>17.46157401144212</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08333160430239563</v>
+      </c>
+      <c r="C31">
+        <v>2056.565961576314</v>
+      </c>
+      <c r="D31">
+        <v>2442.336961576314</v>
+      </c>
+      <c r="E31">
+        <v>-1035.429</v>
+      </c>
+      <c r="F31">
+        <v>898.9710000000001</v>
+      </c>
+      <c r="G31">
+        <v>513.2</v>
+      </c>
+      <c r="H31">
+        <v>1165.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K31">
+        <v>7.26</v>
+      </c>
+      <c r="L31">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M31">
+        <v>46.47680070000001</v>
+      </c>
+      <c r="N31">
+        <v>737.0965326333334</v>
+      </c>
+      <c r="O31">
+        <v>183.8318752387534</v>
+      </c>
+      <c r="P31">
+        <v>553.26465739458</v>
+      </c>
+      <c r="Q31">
+        <v>560.52465739458</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1015181105667544</v>
+      </c>
+      <c r="T31">
+        <v>1.285965098743344</v>
+      </c>
+      <c r="U31">
+        <v>0.0517</v>
+      </c>
+      <c r="V31">
+        <v>0.2494</v>
+      </c>
+      <c r="W31">
+        <v>0.03880602</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>16.85945076966826</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08315531002107464</v>
+      </c>
+      <c r="C32">
+        <v>2037.093302520663</v>
+      </c>
+      <c r="D32">
+        <v>2453.863302520664</v>
+      </c>
+      <c r="E32">
+        <v>-1004.43</v>
+      </c>
+      <c r="F32">
+        <v>929.9700000000001</v>
+      </c>
+      <c r="G32">
+        <v>513.2</v>
+      </c>
+      <c r="H32">
+        <v>1165.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K32">
+        <v>7.26</v>
+      </c>
+      <c r="L32">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M32">
+        <v>48.07944900000001</v>
+      </c>
+      <c r="N32">
+        <v>735.4938843333334</v>
+      </c>
+      <c r="O32">
+        <v>183.4321747527334</v>
+      </c>
+      <c r="P32">
+        <v>552.0617095806001</v>
+      </c>
+      <c r="Q32">
+        <v>559.3217095806001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1021621486015352</v>
+      </c>
+      <c r="T32">
+        <v>1.300829393791524</v>
+      </c>
+      <c r="U32">
+        <v>0.0517</v>
+      </c>
+      <c r="V32">
+        <v>0.2494</v>
+      </c>
+      <c r="W32">
+        <v>0.03880602</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>16.29746907734598</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08297901573975364</v>
+      </c>
+      <c r="C33">
+        <v>2017.729953943121</v>
+      </c>
+      <c r="D33">
+        <v>2465.498953943121</v>
+      </c>
+      <c r="E33">
+        <v>-973.4310000000002</v>
+      </c>
+      <c r="F33">
+        <v>960.9690000000002</v>
+      </c>
+      <c r="G33">
+        <v>513.2</v>
+      </c>
+      <c r="H33">
+        <v>1165.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K33">
+        <v>7.26</v>
+      </c>
+      <c r="L33">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M33">
+        <v>49.68209730000001</v>
+      </c>
+      <c r="N33">
+        <v>733.8912360333334</v>
+      </c>
+      <c r="O33">
+        <v>183.0324742667133</v>
+      </c>
+      <c r="P33">
+        <v>550.8587617666201</v>
+      </c>
+      <c r="Q33">
+        <v>558.1187617666201</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1028248544054401</v>
+      </c>
+      <c r="T33">
+        <v>1.316124537971535</v>
+      </c>
+      <c r="U33">
+        <v>0.0517</v>
+      </c>
+      <c r="V33">
+        <v>0.2494</v>
+      </c>
+      <c r="W33">
+        <v>0.03880602</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>15.77174426839934</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08280272145843263</v>
+      </c>
+      <c r="C34">
+        <v>1998.477478227055</v>
+      </c>
+      <c r="D34">
+        <v>2477.245478227055</v>
+      </c>
+      <c r="E34">
+        <v>-942.4320000000001</v>
+      </c>
+      <c r="F34">
+        <v>991.9680000000002</v>
+      </c>
+      <c r="G34">
+        <v>513.2</v>
+      </c>
+      <c r="H34">
+        <v>1165.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K34">
+        <v>7.26</v>
+      </c>
+      <c r="L34">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M34">
+        <v>51.28474560000002</v>
+      </c>
+      <c r="N34">
+        <v>732.2885877333333</v>
+      </c>
+      <c r="O34">
+        <v>182.6327737806933</v>
+      </c>
+      <c r="P34">
+        <v>549.65581395264</v>
+      </c>
+      <c r="Q34">
+        <v>556.91581395264</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1035070515565186</v>
+      </c>
+      <c r="T34">
+        <v>1.331869539333311</v>
+      </c>
+      <c r="U34">
+        <v>0.0517</v>
+      </c>
+      <c r="V34">
+        <v>0.2494</v>
+      </c>
+      <c r="W34">
+        <v>0.03880602</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>15.27887726001186</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08262642717711163</v>
+      </c>
+      <c r="C35">
+        <v>1979.337467673393</v>
+      </c>
+      <c r="D35">
+        <v>2489.104467673394</v>
+      </c>
+      <c r="E35">
+        <v>-911.4330000000001</v>
+      </c>
+      <c r="F35">
+        <v>1022.967</v>
+      </c>
+      <c r="G35">
+        <v>513.2</v>
+      </c>
+      <c r="H35">
+        <v>1165.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K35">
+        <v>7.26</v>
+      </c>
+      <c r="L35">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M35">
+        <v>52.88739390000001</v>
+      </c>
+      <c r="N35">
+        <v>730.6859394333334</v>
+      </c>
+      <c r="O35">
+        <v>182.2330732946733</v>
+      </c>
+      <c r="P35">
+        <v>548.4528661386601</v>
+      </c>
+      <c r="Q35">
+        <v>555.71286613866</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1042096128016592</v>
+      </c>
+      <c r="T35">
+        <v>1.348084540735737</v>
+      </c>
+      <c r="U35">
+        <v>0.0517</v>
+      </c>
+      <c r="V35">
+        <v>0.2494</v>
+      </c>
+      <c r="W35">
+        <v>0.03880602</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>14.81588097940544</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08245013289579063</v>
+      </c>
+      <c r="C36">
+        <v>1960.311545220181</v>
+      </c>
+      <c r="D36">
+        <v>2501.077545220181</v>
+      </c>
+      <c r="E36">
+        <v>-880.434</v>
+      </c>
+      <c r="F36">
+        <v>1053.966</v>
+      </c>
+      <c r="G36">
+        <v>513.2</v>
+      </c>
+      <c r="H36">
+        <v>1165.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K36">
+        <v>7.26</v>
+      </c>
+      <c r="L36">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M36">
+        <v>54.49004220000002</v>
+      </c>
+      <c r="N36">
+        <v>729.0832911333333</v>
+      </c>
+      <c r="O36">
+        <v>181.8333728086533</v>
+      </c>
+      <c r="P36">
+        <v>547.24991832468</v>
+      </c>
+      <c r="Q36">
+        <v>554.50991832468</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.104933463781501</v>
+      </c>
+      <c r="T36">
+        <v>1.364790905817024</v>
+      </c>
+      <c r="U36">
+        <v>0.0517</v>
+      </c>
+      <c r="V36">
+        <v>0.2494</v>
+      </c>
+      <c r="W36">
+        <v>0.03880602</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>14.38011977412881</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08227383861446964</v>
+      </c>
+      <c r="C37">
+        <v>1941.401365182983</v>
+      </c>
+      <c r="D37">
+        <v>2513.166365182984</v>
+      </c>
+      <c r="E37">
+        <v>-849.4349999999999</v>
+      </c>
+      <c r="F37">
+        <v>1084.965</v>
+      </c>
+      <c r="G37">
+        <v>513.2</v>
+      </c>
+      <c r="H37">
+        <v>1165.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K37">
+        <v>7.26</v>
+      </c>
+      <c r="L37">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M37">
+        <v>56.09269050000002</v>
+      </c>
+      <c r="N37">
+        <v>727.4806428333334</v>
+      </c>
+      <c r="O37">
+        <v>181.4336723226334</v>
+      </c>
+      <c r="P37">
+        <v>546.0469705107</v>
+      </c>
+      <c r="Q37">
+        <v>553.3069705107</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1056795870991841</v>
+      </c>
+      <c r="T37">
+        <v>1.382011312900813</v>
+      </c>
+      <c r="U37">
+        <v>0.0517</v>
+      </c>
+      <c r="V37">
+        <v>0.2494</v>
+      </c>
+      <c r="W37">
+        <v>0.03880602</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>13.9692592091537</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08209754433314864</v>
+      </c>
+      <c r="C38">
+        <v>1922.608614016887</v>
+      </c>
+      <c r="D38">
+        <v>2525.372614016887</v>
+      </c>
+      <c r="E38">
+        <v>-818.4360000000001</v>
+      </c>
+      <c r="F38">
+        <v>1115.964</v>
+      </c>
+      <c r="G38">
+        <v>513.2</v>
+      </c>
+      <c r="H38">
+        <v>1165.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K38">
+        <v>7.26</v>
+      </c>
+      <c r="L38">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M38">
+        <v>57.69533880000001</v>
+      </c>
+      <c r="N38">
+        <v>725.8779945333333</v>
+      </c>
+      <c r="O38">
+        <v>181.0339718366133</v>
+      </c>
+      <c r="P38">
+        <v>544.84402269672</v>
+      </c>
+      <c r="Q38">
+        <v>552.10402269672</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1064490267705448</v>
+      </c>
+      <c r="T38">
+        <v>1.39976985770597</v>
+      </c>
+      <c r="U38">
+        <v>0.0517</v>
+      </c>
+      <c r="V38">
+        <v>0.2494</v>
+      </c>
+      <c r="W38">
+        <v>0.03880602</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>13.58122423112165</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08192125005182765</v>
+      </c>
+      <c r="C39">
+        <v>1903.935011100792</v>
+      </c>
+      <c r="D39">
+        <v>2537.698011100792</v>
+      </c>
+      <c r="E39">
+        <v>-787.4370000000001</v>
+      </c>
+      <c r="F39">
+        <v>1146.963</v>
+      </c>
+      <c r="G39">
+        <v>513.2</v>
+      </c>
+      <c r="H39">
+        <v>1165.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K39">
+        <v>7.26</v>
+      </c>
+      <c r="L39">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M39">
+        <v>59.29798710000001</v>
+      </c>
+      <c r="N39">
+        <v>724.2753462333334</v>
+      </c>
+      <c r="O39">
+        <v>180.6342713505934</v>
+      </c>
+      <c r="P39">
+        <v>543.64107488274</v>
+      </c>
+      <c r="Q39">
+        <v>550.90107488274</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1072428930981391</v>
+      </c>
+      <c r="T39">
+        <v>1.418092165838275</v>
+      </c>
+      <c r="U39">
+        <v>0.0517</v>
+      </c>
+      <c r="V39">
+        <v>0.2494</v>
+      </c>
+      <c r="W39">
+        <v>0.03880602</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>13.21416411676701</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08174495577050665</v>
+      </c>
+      <c r="C40">
+        <v>1885.38230954481</v>
+      </c>
+      <c r="D40">
+        <v>2550.14430954481</v>
+      </c>
+      <c r="E40">
+        <v>-756.4380000000001</v>
+      </c>
+      <c r="F40">
+        <v>1177.962</v>
+      </c>
+      <c r="G40">
+        <v>513.2</v>
+      </c>
+      <c r="H40">
+        <v>1165.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K40">
+        <v>7.26</v>
+      </c>
+      <c r="L40">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M40">
+        <v>60.90063540000001</v>
+      </c>
+      <c r="N40">
+        <v>722.6726979333333</v>
+      </c>
+      <c r="O40">
+        <v>180.2345708645733</v>
+      </c>
+      <c r="P40">
+        <v>542.43812706876</v>
+      </c>
+      <c r="Q40">
+        <v>549.69812706876</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1080623680169462</v>
+      </c>
+      <c r="T40">
+        <v>1.437005516168396</v>
+      </c>
+      <c r="U40">
+        <v>0.0517</v>
+      </c>
+      <c r="V40">
+        <v>0.2494</v>
+      </c>
+      <c r="W40">
+        <v>0.03880602</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>12.86642295579946</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08189066888918566</v>
+      </c>
+      <c r="C41">
+        <v>1844.087310832062</v>
+      </c>
+      <c r="D41">
+        <v>2539.848310832062</v>
+      </c>
+      <c r="E41">
+        <v>-725.4390000000001</v>
+      </c>
+      <c r="F41">
+        <v>1208.961</v>
+      </c>
+      <c r="G41">
+        <v>513.2</v>
+      </c>
+      <c r="H41">
+        <v>1165.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K41">
+        <v>7.26</v>
+      </c>
+      <c r="L41">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M41">
+        <v>63.83314080000001</v>
+      </c>
+      <c r="N41">
+        <v>719.7401925333334</v>
+      </c>
+      <c r="O41">
+        <v>179.5032040178133</v>
+      </c>
+      <c r="P41">
+        <v>540.23698851552</v>
+      </c>
+      <c r="Q41">
+        <v>547.49698851552</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1089087109658781</v>
+      </c>
+      <c r="T41">
+        <v>1.456538976345406</v>
+      </c>
+      <c r="U41">
+        <v>0.0528</v>
+      </c>
+      <c r="V41">
+        <v>0.2494</v>
+      </c>
+      <c r="W41">
+        <v>0.03963168</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>12.27533728582149</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08172263120786466</v>
+      </c>
+      <c r="C42">
+        <v>1824.96912820843</v>
+      </c>
+      <c r="D42">
+        <v>2551.72912820843</v>
+      </c>
+      <c r="E42">
+        <v>-694.4400000000001</v>
+      </c>
+      <c r="F42">
+        <v>1239.96</v>
+      </c>
+      <c r="G42">
+        <v>513.2</v>
+      </c>
+      <c r="H42">
+        <v>1165.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K42">
+        <v>7.26</v>
+      </c>
+      <c r="L42">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M42">
+        <v>65.46988800000001</v>
+      </c>
+      <c r="N42">
+        <v>718.1034453333334</v>
+      </c>
+      <c r="O42">
+        <v>179.0949992661334</v>
+      </c>
+      <c r="P42">
+        <v>539.0084460672001</v>
+      </c>
+      <c r="Q42">
+        <v>546.2684460672001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1097832653464411</v>
+      </c>
+      <c r="T42">
+        <v>1.47672355186165</v>
+      </c>
+      <c r="U42">
+        <v>0.0528</v>
+      </c>
+      <c r="V42">
+        <v>0.2494</v>
+      </c>
+      <c r="W42">
+        <v>0.03963168</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>11.96845385367596</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08155459352654366</v>
+      </c>
+      <c r="C43">
+        <v>1805.962619347928</v>
+      </c>
+      <c r="D43">
+        <v>2563.721619347928</v>
+      </c>
+      <c r="E43">
+        <v>-663.441</v>
+      </c>
+      <c r="F43">
+        <v>1270.959</v>
+      </c>
+      <c r="G43">
+        <v>513.2</v>
+      </c>
+      <c r="H43">
+        <v>1165.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K43">
+        <v>7.26</v>
+      </c>
+      <c r="L43">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M43">
+        <v>67.10663520000001</v>
+      </c>
+      <c r="N43">
+        <v>716.4666981333334</v>
+      </c>
+      <c r="O43">
+        <v>178.6867945144533</v>
+      </c>
+      <c r="P43">
+        <v>537.77990361888</v>
+      </c>
+      <c r="Q43">
+        <v>545.03990361888</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1106874656382096</v>
+      </c>
+      <c r="T43">
+        <v>1.49759235027675</v>
+      </c>
+      <c r="U43">
+        <v>0.0528</v>
+      </c>
+      <c r="V43">
+        <v>0.2494</v>
+      </c>
+      <c r="W43">
+        <v>0.03963168</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>11.67654034504971</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08138655584522267</v>
+      </c>
+      <c r="C44">
+        <v>1787.06936620192</v>
+      </c>
+      <c r="D44">
+        <v>2575.82736620192</v>
+      </c>
+      <c r="E44">
+        <v>-632.4420000000002</v>
+      </c>
+      <c r="F44">
+        <v>1301.958</v>
+      </c>
+      <c r="G44">
+        <v>513.2</v>
+      </c>
+      <c r="H44">
+        <v>1165.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K44">
+        <v>7.26</v>
+      </c>
+      <c r="L44">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M44">
+        <v>68.7433824</v>
+      </c>
+      <c r="N44">
+        <v>714.8299509333334</v>
+      </c>
+      <c r="O44">
+        <v>178.2785897627734</v>
+      </c>
+      <c r="P44">
+        <v>536.5513611705601</v>
+      </c>
+      <c r="Q44">
+        <v>543.8113611705601</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1116228452503839</v>
+      </c>
+      <c r="T44">
+        <v>1.519180762430301</v>
+      </c>
+      <c r="U44">
+        <v>0.0528</v>
+      </c>
+      <c r="V44">
+        <v>0.2494</v>
+      </c>
+      <c r="W44">
+        <v>0.03963168</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>11.39852747969139</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08121851816390167</v>
+      </c>
+      <c r="C45">
+        <v>1768.290980743069</v>
+      </c>
+      <c r="D45">
+        <v>2588.047980743069</v>
+      </c>
+      <c r="E45">
+        <v>-601.4430000000002</v>
+      </c>
+      <c r="F45">
+        <v>1332.957</v>
+      </c>
+      <c r="G45">
+        <v>513.2</v>
+      </c>
+      <c r="H45">
+        <v>1165.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K45">
+        <v>7.26</v>
+      </c>
+      <c r="L45">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M45">
+        <v>70.3801296</v>
+      </c>
+      <c r="N45">
+        <v>713.1932037333333</v>
+      </c>
+      <c r="O45">
+        <v>177.8703850110933</v>
+      </c>
+      <c r="P45">
+        <v>535.3228187222401</v>
+      </c>
+      <c r="Q45">
+        <v>542.5828187222401</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1125910451998275</v>
+      </c>
+      <c r="T45">
+        <v>1.541526662729591</v>
+      </c>
+      <c r="U45">
+        <v>0.0528</v>
+      </c>
+      <c r="V45">
+        <v>0.2494</v>
+      </c>
+      <c r="W45">
+        <v>0.03963168</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>11.13344544527996</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08105048048258069</v>
+      </c>
+      <c r="C46">
+        <v>1749.629105680881</v>
+      </c>
+      <c r="D46">
+        <v>2600.385105680882</v>
+      </c>
+      <c r="E46">
+        <v>-570.444</v>
+      </c>
+      <c r="F46">
+        <v>1363.956</v>
+      </c>
+      <c r="G46">
+        <v>513.2</v>
+      </c>
+      <c r="H46">
+        <v>1165.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K46">
+        <v>7.26</v>
+      </c>
+      <c r="L46">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M46">
+        <v>72.01687680000002</v>
+      </c>
+      <c r="N46">
+        <v>711.5564565333334</v>
+      </c>
+      <c r="O46">
+        <v>177.4621802594133</v>
+      </c>
+      <c r="P46">
+        <v>534.0942762739201</v>
+      </c>
+      <c r="Q46">
+        <v>541.35427627392</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1135938237188941</v>
+      </c>
+      <c r="T46">
+        <v>1.564670630896713</v>
+      </c>
+      <c r="U46">
+        <v>0.0528</v>
+      </c>
+      <c r="V46">
+        <v>0.2494</v>
+      </c>
+      <c r="W46">
+        <v>0.03963168</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>10.88041259425087</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08088244280125967</v>
+      </c>
+      <c r="C47">
+        <v>1731.085415197831</v>
+      </c>
+      <c r="D47">
+        <v>2612.840415197831</v>
+      </c>
+      <c r="E47">
+        <v>-539.4449999999999</v>
+      </c>
+      <c r="F47">
+        <v>1394.955</v>
+      </c>
+      <c r="G47">
+        <v>513.2</v>
+      </c>
+      <c r="H47">
+        <v>1165.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K47">
+        <v>7.26</v>
+      </c>
+      <c r="L47">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M47">
+        <v>73.65362400000002</v>
+      </c>
+      <c r="N47">
+        <v>709.9197093333333</v>
+      </c>
+      <c r="O47">
+        <v>177.0539755077334</v>
+      </c>
+      <c r="P47">
+        <v>532.8657338256</v>
+      </c>
+      <c r="Q47">
+        <v>540.1257338256</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1146330669113812</v>
+      </c>
+      <c r="T47">
+        <v>1.588656197906276</v>
+      </c>
+      <c r="U47">
+        <v>0.0528</v>
+      </c>
+      <c r="V47">
+        <v>0.2494</v>
+      </c>
+      <c r="W47">
+        <v>0.03963168</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>10.63862564771196</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08071440511993869</v>
+      </c>
+      <c r="C48">
+        <v>1712.661615706713</v>
+      </c>
+      <c r="D48">
+        <v>2625.415615706713</v>
+      </c>
+      <c r="E48">
+        <v>-508.4459999999999</v>
+      </c>
+      <c r="F48">
+        <v>1425.954</v>
+      </c>
+      <c r="G48">
+        <v>513.2</v>
+      </c>
+      <c r="H48">
+        <v>1165.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K48">
+        <v>7.26</v>
+      </c>
+      <c r="L48">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M48">
+        <v>75.29037120000002</v>
+      </c>
+      <c r="N48">
+        <v>708.2829621333334</v>
+      </c>
+      <c r="O48">
+        <v>176.6457707560534</v>
+      </c>
+      <c r="P48">
+        <v>531.63719137728</v>
+      </c>
+      <c r="Q48">
+        <v>538.89719137728</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.115710800592479</v>
+      </c>
+      <c r="T48">
+        <v>1.613530119249526</v>
+      </c>
+      <c r="U48">
+        <v>0.0528</v>
+      </c>
+      <c r="V48">
+        <v>0.2494</v>
+      </c>
+      <c r="W48">
+        <v>0.03963168</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>10.40735117710953</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08054636743861769</v>
+      </c>
+      <c r="C49">
+        <v>1694.359446630022</v>
+      </c>
+      <c r="D49">
+        <v>2638.112446630022</v>
+      </c>
+      <c r="E49">
+        <v>-477.4469999999999</v>
+      </c>
+      <c r="F49">
+        <v>1456.953</v>
+      </c>
+      <c r="G49">
+        <v>513.2</v>
+      </c>
+      <c r="H49">
+        <v>1165.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K49">
+        <v>7.26</v>
+      </c>
+      <c r="L49">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M49">
+        <v>76.92711840000003</v>
+      </c>
+      <c r="N49">
+        <v>706.6462149333333</v>
+      </c>
+      <c r="O49">
+        <v>176.2375660043733</v>
+      </c>
+      <c r="P49">
+        <v>530.40864892896</v>
+      </c>
+      <c r="Q49">
+        <v>537.66864892896</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.11682920346909</v>
+      </c>
+      <c r="T49">
+        <v>1.639342679134031</v>
+      </c>
+      <c r="U49">
+        <v>0.0528</v>
+      </c>
+      <c r="V49">
+        <v>0.2494</v>
+      </c>
+      <c r="W49">
+        <v>0.03963168</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>10.18591817334124</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08037832975729668</v>
+      </c>
+      <c r="C50">
+        <v>1676.180681202001</v>
+      </c>
+      <c r="D50">
+        <v>2650.932681202001</v>
+      </c>
+      <c r="E50">
+        <v>-446.4480000000001</v>
+      </c>
+      <c r="F50">
+        <v>1487.952</v>
+      </c>
+      <c r="G50">
+        <v>513.2</v>
+      </c>
+      <c r="H50">
+        <v>1165.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K50">
+        <v>7.26</v>
+      </c>
+      <c r="L50">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M50">
+        <v>78.56386560000001</v>
+      </c>
+      <c r="N50">
+        <v>705.0094677333334</v>
+      </c>
+      <c r="O50">
+        <v>175.8293612526934</v>
+      </c>
+      <c r="P50">
+        <v>529.18010648064</v>
+      </c>
+      <c r="Q50">
+        <v>536.44010648064</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1179906218409552</v>
+      </c>
+      <c r="T50">
+        <v>1.666148029783324</v>
+      </c>
+      <c r="U50">
+        <v>0.0528</v>
+      </c>
+      <c r="V50">
+        <v>0.2494</v>
+      </c>
+      <c r="W50">
+        <v>0.03963168</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>9.973711544729964</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08101943887597568</v>
+      </c>
+      <c r="C51">
+        <v>1596.926025542419</v>
+      </c>
+      <c r="D51">
+        <v>2602.67702554242</v>
+      </c>
+      <c r="E51">
+        <v>-415.4490000000001</v>
+      </c>
+      <c r="F51">
+        <v>1518.951</v>
+      </c>
+      <c r="G51">
+        <v>513.2</v>
+      </c>
+      <c r="H51">
+        <v>1165.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K51">
+        <v>7.26</v>
+      </c>
+      <c r="L51">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M51">
+        <v>83.54230500000001</v>
+      </c>
+      <c r="N51">
+        <v>700.0310283333333</v>
+      </c>
+      <c r="O51">
+        <v>174.5877384663333</v>
+      </c>
+      <c r="P51">
+        <v>525.443289867</v>
+      </c>
+      <c r="Q51">
+        <v>532.703289867</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1191975860313249</v>
+      </c>
+      <c r="T51">
+        <v>1.694004570654159</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.2494</v>
+      </c>
+      <c r="W51">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>9.379359754717484</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08086791439465468</v>
+      </c>
+      <c r="C52">
+        <v>1577.172897820512</v>
+      </c>
+      <c r="D52">
+        <v>2613.922897820513</v>
+      </c>
+      <c r="E52">
+        <v>-384.45</v>
+      </c>
+      <c r="F52">
+        <v>1549.95</v>
+      </c>
+      <c r="G52">
+        <v>513.2</v>
+      </c>
+      <c r="H52">
+        <v>1165.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K52">
+        <v>7.26</v>
+      </c>
+      <c r="L52">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M52">
+        <v>85.24725000000002</v>
+      </c>
+      <c r="N52">
+        <v>698.3260833333334</v>
+      </c>
+      <c r="O52">
+        <v>174.1625251833333</v>
+      </c>
+      <c r="P52">
+        <v>524.16355815</v>
+      </c>
+      <c r="Q52">
+        <v>531.42355815</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1204528287893094</v>
+      </c>
+      <c r="T52">
+        <v>1.722975373159827</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.2494</v>
+      </c>
+      <c r="W52">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>9.191772559623134</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08071638991333369</v>
+      </c>
+      <c r="C53">
+        <v>1557.517376120773</v>
+      </c>
+      <c r="D53">
+        <v>2625.266376120773</v>
+      </c>
+      <c r="E53">
+        <v>-353.451</v>
+      </c>
+      <c r="F53">
+        <v>1580.949</v>
+      </c>
+      <c r="G53">
+        <v>513.2</v>
+      </c>
+      <c r="H53">
+        <v>1165.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K53">
+        <v>7.26</v>
+      </c>
+      <c r="L53">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M53">
+        <v>86.95219500000002</v>
+      </c>
+      <c r="N53">
+        <v>696.6211383333334</v>
+      </c>
+      <c r="O53">
+        <v>173.7373119003334</v>
+      </c>
+      <c r="P53">
+        <v>522.8838264330001</v>
+      </c>
+      <c r="Q53">
+        <v>530.1438264330001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.121759305945579</v>
+      </c>
+      <c r="T53">
+        <v>1.75312865740042</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.2494</v>
+      </c>
+      <c r="W53">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>9.01154172512072</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08056486543201269</v>
+      </c>
+      <c r="C54">
+        <v>1537.960736706033</v>
+      </c>
+      <c r="D54">
+        <v>2636.708736706034</v>
+      </c>
+      <c r="E54">
+        <v>-322.452</v>
+      </c>
+      <c r="F54">
+        <v>1611.948</v>
+      </c>
+      <c r="G54">
+        <v>513.2</v>
+      </c>
+      <c r="H54">
+        <v>1165.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K54">
+        <v>7.26</v>
+      </c>
+      <c r="L54">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M54">
+        <v>88.65714000000001</v>
+      </c>
+      <c r="N54">
+        <v>694.9161933333334</v>
+      </c>
+      <c r="O54">
+        <v>173.3120986173333</v>
+      </c>
+      <c r="P54">
+        <v>521.604094716</v>
+      </c>
+      <c r="Q54">
+        <v>528.864094716</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1231202196500265</v>
+      </c>
+      <c r="T54">
+        <v>1.784538328484371</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.2494</v>
+      </c>
+      <c r="W54">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>8.838242845791475</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08041334095069171</v>
+      </c>
+      <c r="C55">
+        <v>1518.504278187164</v>
+      </c>
+      <c r="D55">
+        <v>2648.251278187165</v>
+      </c>
+      <c r="E55">
+        <v>-291.453</v>
+      </c>
+      <c r="F55">
+        <v>1642.947</v>
+      </c>
+      <c r="G55">
+        <v>513.2</v>
+      </c>
+      <c r="H55">
+        <v>1165.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K55">
+        <v>7.26</v>
+      </c>
+      <c r="L55">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M55">
+        <v>90.36208500000002</v>
+      </c>
+      <c r="N55">
+        <v>693.2112483333334</v>
+      </c>
+      <c r="O55">
+        <v>172.8868853343334</v>
+      </c>
+      <c r="P55">
+        <v>520.3243629990001</v>
+      </c>
+      <c r="Q55">
+        <v>527.5843629990001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1245390445759398</v>
+      </c>
+      <c r="T55">
+        <v>1.817284581316576</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.2494</v>
+      </c>
+      <c r="W55">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>8.671483546814278</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08026181646937069</v>
+      </c>
+      <c r="C56">
+        <v>1499.149322014386</v>
+      </c>
+      <c r="D56">
+        <v>2659.895322014386</v>
+      </c>
+      <c r="E56">
+        <v>-260.454</v>
+      </c>
+      <c r="F56">
+        <v>1673.946</v>
+      </c>
+      <c r="G56">
+        <v>513.2</v>
+      </c>
+      <c r="H56">
+        <v>1165.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K56">
+        <v>7.26</v>
+      </c>
+      <c r="L56">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M56">
+        <v>92.06703000000002</v>
+      </c>
+      <c r="N56">
+        <v>691.5063033333333</v>
+      </c>
+      <c r="O56">
+        <v>172.4616720513334</v>
+      </c>
+      <c r="P56">
+        <v>519.044631282</v>
+      </c>
+      <c r="Q56">
+        <v>526.3046312819999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1260195575421102</v>
+      </c>
+      <c r="T56">
+        <v>1.85145458427192</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.2494</v>
+      </c>
+      <c r="W56">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>8.510900518169569</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.0801102919880497</v>
+      </c>
+      <c r="C57">
+        <v>1479.897212981585</v>
+      </c>
+      <c r="D57">
+        <v>2671.642212981585</v>
+      </c>
+      <c r="E57">
+        <v>-229.4549999999999</v>
+      </c>
+      <c r="F57">
+        <v>1704.945</v>
+      </c>
+      <c r="G57">
+        <v>513.2</v>
+      </c>
+      <c r="H57">
+        <v>1165.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K57">
+        <v>7.26</v>
+      </c>
+      <c r="L57">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M57">
+        <v>93.77197500000003</v>
+      </c>
+      <c r="N57">
+        <v>689.8013583333334</v>
+      </c>
+      <c r="O57">
+        <v>172.0364587683333</v>
+      </c>
+      <c r="P57">
+        <v>517.7648995650001</v>
+      </c>
+      <c r="Q57">
+        <v>525.0248995650001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1275658710845549</v>
+      </c>
+      <c r="T57">
+        <v>1.887143254025279</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.2494</v>
+      </c>
+      <c r="W57">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>8.356156872384666</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.0799587675067287</v>
+      </c>
+      <c r="C58">
+        <v>1460.749319744074</v>
+      </c>
+      <c r="D58">
+        <v>2683.493319744075</v>
+      </c>
+      <c r="E58">
+        <v>-198.4559999999999</v>
+      </c>
+      <c r="F58">
+        <v>1735.944</v>
+      </c>
+      <c r="G58">
+        <v>513.2</v>
+      </c>
+      <c r="H58">
+        <v>1165.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K58">
+        <v>7.26</v>
+      </c>
+      <c r="L58">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M58">
+        <v>95.47692000000002</v>
+      </c>
+      <c r="N58">
+        <v>688.0964133333333</v>
+      </c>
+      <c r="O58">
+        <v>171.6112454853333</v>
+      </c>
+      <c r="P58">
+        <v>516.4851678479999</v>
+      </c>
+      <c r="Q58">
+        <v>523.7451678479999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1291824716062016</v>
+      </c>
+      <c r="T58">
+        <v>1.924454136040154</v>
+      </c>
+      <c r="U58">
+        <v>0.055</v>
+      </c>
+      <c r="V58">
+        <v>0.2494</v>
+      </c>
+      <c r="W58">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>8.206939785377799</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.0798072430254077</v>
+      </c>
+      <c r="C59">
+        <v>1441.707035350182</v>
+      </c>
+      <c r="D59">
+        <v>2695.450035350182</v>
+      </c>
+      <c r="E59">
+        <v>-167.4569999999999</v>
+      </c>
+      <c r="F59">
+        <v>1766.943</v>
+      </c>
+      <c r="G59">
+        <v>513.2</v>
+      </c>
+      <c r="H59">
+        <v>1165.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K59">
+        <v>7.26</v>
+      </c>
+      <c r="L59">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M59">
+        <v>97.18186500000003</v>
+      </c>
+      <c r="N59">
+        <v>686.3914683333334</v>
+      </c>
+      <c r="O59">
+        <v>171.1860322023333</v>
+      </c>
+      <c r="P59">
+        <v>515.2054361310001</v>
+      </c>
+      <c r="Q59">
+        <v>522.465436131</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1308742628497854</v>
+      </c>
+      <c r="T59">
+        <v>1.963500407916186</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.2494</v>
+      </c>
+      <c r="W59">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>8.062958385634328</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.07965571854408671</v>
+      </c>
+      <c r="C60">
+        <v>1422.771777787114</v>
+      </c>
+      <c r="D60">
+        <v>2707.513777787114</v>
+      </c>
+      <c r="E60">
+        <v>-136.4580000000001</v>
+      </c>
+      <c r="F60">
+        <v>1797.942</v>
+      </c>
+      <c r="G60">
+        <v>513.2</v>
+      </c>
+      <c r="H60">
+        <v>1165.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K60">
+        <v>7.26</v>
+      </c>
+      <c r="L60">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M60">
+        <v>98.88681000000001</v>
+      </c>
+      <c r="N60">
+        <v>684.6865233333334</v>
+      </c>
+      <c r="O60">
+        <v>170.7608189193334</v>
+      </c>
+      <c r="P60">
+        <v>513.9257044140001</v>
+      </c>
+      <c r="Q60">
+        <v>521.185704414</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1326466155811588</v>
+      </c>
+      <c r="T60">
+        <v>2.004406026072029</v>
+      </c>
+      <c r="U60">
+        <v>0.055</v>
+      </c>
+      <c r="V60">
+        <v>0.2494</v>
+      </c>
+      <c r="W60">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>7.923941861744082</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.07950419406276572</v>
+      </c>
+      <c r="C61">
+        <v>1403.944990541544</v>
+      </c>
+      <c r="D61">
+        <v>2719.685990541544</v>
+      </c>
+      <c r="E61">
+        <v>-105.4590000000001</v>
+      </c>
+      <c r="F61">
+        <v>1828.941</v>
+      </c>
+      <c r="G61">
+        <v>513.2</v>
+      </c>
+      <c r="H61">
+        <v>1165.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K61">
+        <v>7.26</v>
+      </c>
+      <c r="L61">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M61">
+        <v>100.591755</v>
+      </c>
+      <c r="N61">
+        <v>682.9815783333333</v>
+      </c>
+      <c r="O61">
+        <v>170.3356056363334</v>
+      </c>
+      <c r="P61">
+        <v>512.6459726969999</v>
+      </c>
+      <c r="Q61">
+        <v>519.9059726969999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.134505424543331</v>
+      </c>
+      <c r="T61">
+        <v>2.047307040235475</v>
+      </c>
+      <c r="U61">
+        <v>0.055</v>
+      </c>
+      <c r="V61">
+        <v>0.2494</v>
+      </c>
+      <c r="W61">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>7.789637762392487</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08002820958144471</v>
+      </c>
+      <c r="C62">
+        <v>1331.309057660597</v>
+      </c>
+      <c r="D62">
+        <v>2678.049057660597</v>
+      </c>
+      <c r="E62">
+        <v>-74.46000000000004</v>
+      </c>
+      <c r="F62">
+        <v>1859.94</v>
+      </c>
+      <c r="G62">
+        <v>513.2</v>
+      </c>
+      <c r="H62">
+        <v>1165.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K62">
+        <v>7.26</v>
+      </c>
+      <c r="L62">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M62">
+        <v>105.08661</v>
+      </c>
+      <c r="N62">
+        <v>678.4867233333333</v>
+      </c>
+      <c r="O62">
+        <v>169.2145887993333</v>
+      </c>
+      <c r="P62">
+        <v>509.272134534</v>
+      </c>
+      <c r="Q62">
+        <v>516.532134534</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1364571739536118</v>
+      </c>
+      <c r="T62">
+        <v>2.092353105107092</v>
+      </c>
+      <c r="U62">
+        <v>0.0565</v>
+      </c>
+      <c r="V62">
+        <v>0.2494</v>
+      </c>
+      <c r="W62">
+        <v>0.0424089</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>7.456452666360949</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.07988794410012373</v>
+      </c>
+      <c r="C63">
+        <v>1311.329726050414</v>
+      </c>
+      <c r="D63">
+        <v>2689.068726050414</v>
+      </c>
+      <c r="E63">
+        <v>-43.46100000000001</v>
+      </c>
+      <c r="F63">
+        <v>1890.939</v>
+      </c>
+      <c r="G63">
+        <v>513.2</v>
+      </c>
+      <c r="H63">
+        <v>1165.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K63">
+        <v>7.26</v>
+      </c>
+      <c r="L63">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M63">
+        <v>106.8380535</v>
+      </c>
+      <c r="N63">
+        <v>676.7352798333334</v>
+      </c>
+      <c r="O63">
+        <v>168.7777787904334</v>
+      </c>
+      <c r="P63">
+        <v>507.9575010429</v>
+      </c>
+      <c r="Q63">
+        <v>515.2175010429</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1385090130772403</v>
+      </c>
+      <c r="T63">
+        <v>2.139709224587512</v>
+      </c>
+      <c r="U63">
+        <v>0.0565</v>
+      </c>
+      <c r="V63">
+        <v>0.2494</v>
+      </c>
+      <c r="W63">
+        <v>0.0424089</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>7.334215737404214</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.07974767861880273</v>
+      </c>
+      <c r="C64">
+        <v>1291.441456872397</v>
+      </c>
+      <c r="D64">
+        <v>2700.179456872397</v>
+      </c>
+      <c r="E64">
+        <v>-12.46199999999999</v>
+      </c>
+      <c r="F64">
+        <v>1921.938</v>
+      </c>
+      <c r="G64">
+        <v>513.2</v>
+      </c>
+      <c r="H64">
+        <v>1165.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K64">
+        <v>7.26</v>
+      </c>
+      <c r="L64">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M64">
+        <v>108.589497</v>
+      </c>
+      <c r="N64">
+        <v>674.9838363333333</v>
+      </c>
+      <c r="O64">
+        <v>168.3409687815333</v>
+      </c>
+      <c r="P64">
+        <v>506.6428675518</v>
+      </c>
+      <c r="Q64">
+        <v>513.9028675518</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1406688437336914</v>
+      </c>
+      <c r="T64">
+        <v>2.189557771409005</v>
+      </c>
+      <c r="U64">
+        <v>0.0565</v>
+      </c>
+      <c r="V64">
+        <v>0.2494</v>
+      </c>
+      <c r="W64">
+        <v>0.0424089</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>7.215921935188016</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.07960741313748174</v>
+      </c>
+      <c r="C65">
+        <v>1271.645383568712</v>
+      </c>
+      <c r="D65">
+        <v>2711.382383568713</v>
+      </c>
+      <c r="E65">
+        <v>18.53700000000003</v>
+      </c>
+      <c r="F65">
+        <v>1952.937</v>
+      </c>
+      <c r="G65">
+        <v>513.2</v>
+      </c>
+      <c r="H65">
+        <v>1165.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K65">
+        <v>7.26</v>
+      </c>
+      <c r="L65">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M65">
+        <v>110.3409405</v>
+      </c>
+      <c r="N65">
+        <v>673.2323928333334</v>
+      </c>
+      <c r="O65">
+        <v>167.9041587726334</v>
+      </c>
+      <c r="P65">
+        <v>505.3282340607</v>
+      </c>
+      <c r="Q65">
+        <v>512.5882340607001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1429454219931939</v>
+      </c>
+      <c r="T65">
+        <v>2.242100834274903</v>
+      </c>
+      <c r="U65">
+        <v>0.0565</v>
+      </c>
+      <c r="V65">
+        <v>0.2494</v>
+      </c>
+      <c r="W65">
+        <v>0.0424089</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>7.101383491772333</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.07946714765616072</v>
+      </c>
+      <c r="C66">
+        <v>1251.942658470307</v>
+      </c>
+      <c r="D66">
+        <v>2722.678658470308</v>
+      </c>
+      <c r="E66">
+        <v>49.53600000000006</v>
+      </c>
+      <c r="F66">
+        <v>1983.936</v>
+      </c>
+      <c r="G66">
+        <v>513.2</v>
+      </c>
+      <c r="H66">
+        <v>1165.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K66">
+        <v>7.26</v>
+      </c>
+      <c r="L66">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M66">
+        <v>112.092384</v>
+      </c>
+      <c r="N66">
+        <v>671.4809493333333</v>
+      </c>
+      <c r="O66">
+        <v>167.4673487637334</v>
+      </c>
+      <c r="P66">
+        <v>504.0136005696</v>
+      </c>
+      <c r="Q66">
+        <v>511.2736005696</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1453484768226687</v>
+      </c>
+      <c r="T66">
+        <v>2.297562956188907</v>
+      </c>
+      <c r="U66">
+        <v>0.0565</v>
+      </c>
+      <c r="V66">
+        <v>0.2494</v>
+      </c>
+      <c r="W66">
+        <v>0.0424089</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>6.99042437471339</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.07932688217483973</v>
+      </c>
+      <c r="C67">
+        <v>1232.334453192023</v>
+      </c>
+      <c r="D67">
+        <v>2734.069453192023</v>
+      </c>
+      <c r="E67">
+        <v>80.53500000000008</v>
+      </c>
+      <c r="F67">
+        <v>2014.935</v>
+      </c>
+      <c r="G67">
+        <v>513.2</v>
+      </c>
+      <c r="H67">
+        <v>1165.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K67">
+        <v>7.26</v>
+      </c>
+      <c r="L67">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M67">
+        <v>113.8438275</v>
+      </c>
+      <c r="N67">
+        <v>669.7295058333334</v>
+      </c>
+      <c r="O67">
+        <v>167.0305387548333</v>
+      </c>
+      <c r="P67">
+        <v>502.6989670785001</v>
+      </c>
+      <c r="Q67">
+        <v>509.9589670785001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1478888490709707</v>
+      </c>
+      <c r="T67">
+        <v>2.356194342212282</v>
+      </c>
+      <c r="U67">
+        <v>0.0565</v>
+      </c>
+      <c r="V67">
+        <v>0.2494</v>
+      </c>
+      <c r="W67">
+        <v>0.0424089</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>6.882879384333184</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.07918661669351874</v>
+      </c>
+      <c r="C68">
+        <v>1212.821959037685</v>
+      </c>
+      <c r="D68">
+        <v>2745.555959037685</v>
+      </c>
+      <c r="E68">
+        <v>111.5340000000001</v>
+      </c>
+      <c r="F68">
+        <v>2045.934</v>
+      </c>
+      <c r="G68">
+        <v>513.2</v>
+      </c>
+      <c r="H68">
+        <v>1165.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K68">
+        <v>7.26</v>
+      </c>
+      <c r="L68">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M68">
+        <v>115.595271</v>
+      </c>
+      <c r="N68">
+        <v>667.9780623333334</v>
+      </c>
+      <c r="O68">
+        <v>166.5937287459333</v>
+      </c>
+      <c r="P68">
+        <v>501.3843335874</v>
+      </c>
+      <c r="Q68">
+        <v>508.6443335874</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1505786549809375</v>
+      </c>
+      <c r="T68">
+        <v>2.418274633295856</v>
+      </c>
+      <c r="U68">
+        <v>0.0565</v>
+      </c>
+      <c r="V68">
+        <v>0.2494</v>
+      </c>
+      <c r="W68">
+        <v>0.0424089</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>6.778593333055409</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.07904635121219775</v>
+      </c>
+      <c r="C69">
+        <v>1193.406387415439</v>
+      </c>
+      <c r="D69">
+        <v>2757.139387415439</v>
+      </c>
+      <c r="E69">
+        <v>142.5330000000001</v>
+      </c>
+      <c r="F69">
+        <v>2076.933</v>
+      </c>
+      <c r="G69">
+        <v>513.2</v>
+      </c>
+      <c r="H69">
+        <v>1165.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K69">
+        <v>7.26</v>
+      </c>
+      <c r="L69">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M69">
+        <v>117.3467145</v>
+      </c>
+      <c r="N69">
+        <v>666.2266188333333</v>
+      </c>
+      <c r="O69">
+        <v>166.1569187370333</v>
+      </c>
+      <c r="P69">
+        <v>500.0697000963</v>
+      </c>
+      <c r="Q69">
+        <v>507.3297000963</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1534314794309023</v>
+      </c>
+      <c r="T69">
+        <v>2.484117366263284</v>
+      </c>
+      <c r="U69">
+        <v>0.0565</v>
+      </c>
+      <c r="V69">
+        <v>0.2494</v>
+      </c>
+      <c r="W69">
+        <v>0.0424089</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>6.677420298233685</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.07890608573087673</v>
+      </c>
+      <c r="C70">
+        <v>1174.088970263641</v>
+      </c>
+      <c r="D70">
+        <v>2768.820970263642</v>
+      </c>
+      <c r="E70">
+        <v>173.5320000000004</v>
+      </c>
+      <c r="F70">
+        <v>2107.932000000001</v>
+      </c>
+      <c r="G70">
+        <v>513.2</v>
+      </c>
+      <c r="H70">
+        <v>1165.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K70">
+        <v>7.26</v>
+      </c>
+      <c r="L70">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M70">
+        <v>119.098158</v>
+      </c>
+      <c r="N70">
+        <v>664.4751753333334</v>
+      </c>
+      <c r="O70">
+        <v>165.7201087281333</v>
+      </c>
+      <c r="P70">
+        <v>498.7550666052</v>
+      </c>
+      <c r="Q70">
+        <v>506.0150666052</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1564626054089898</v>
+      </c>
+      <c r="T70">
+        <v>2.554075270041175</v>
+      </c>
+      <c r="U70">
+        <v>0.0565</v>
+      </c>
+      <c r="V70">
+        <v>0.2494</v>
+      </c>
+      <c r="W70">
+        <v>0.0424089</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>6.579222940906719</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.07876582024955574</v>
+      </c>
+      <c r="C71">
+        <v>1154.870960487628</v>
+      </c>
+      <c r="D71">
+        <v>2780.601960487628</v>
+      </c>
+      <c r="E71">
+        <v>204.5310000000002</v>
+      </c>
+      <c r="F71">
+        <v>2138.931</v>
+      </c>
+      <c r="G71">
+        <v>513.2</v>
+      </c>
+      <c r="H71">
+        <v>1165.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K71">
+        <v>7.26</v>
+      </c>
+      <c r="L71">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M71">
+        <v>120.8496015</v>
+      </c>
+      <c r="N71">
+        <v>662.7237318333333</v>
+      </c>
+      <c r="O71">
+        <v>165.2832987192333</v>
+      </c>
+      <c r="P71">
+        <v>497.4404331141</v>
+      </c>
+      <c r="Q71">
+        <v>504.7004331141</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1596892879017927</v>
+      </c>
+      <c r="T71">
+        <v>2.628546586966027</v>
+      </c>
+      <c r="U71">
+        <v>0.0565</v>
+      </c>
+      <c r="V71">
+        <v>0.2494</v>
+      </c>
+      <c r="W71">
+        <v>0.0424089</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>6.483871883792129</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.07862555476823474</v>
+      </c>
+      <c r="C72">
+        <v>1135.75363240768</v>
+      </c>
+      <c r="D72">
+        <v>2792.483632407681</v>
+      </c>
+      <c r="E72">
+        <v>235.5300000000004</v>
+      </c>
+      <c r="F72">
+        <v>2169.930000000001</v>
+      </c>
+      <c r="G72">
+        <v>513.2</v>
+      </c>
+      <c r="H72">
+        <v>1165.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K72">
+        <v>7.26</v>
+      </c>
+      <c r="L72">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M72">
+        <v>122.601045</v>
+      </c>
+      <c r="N72">
+        <v>660.9722883333334</v>
+      </c>
+      <c r="O72">
+        <v>164.8464887103333</v>
+      </c>
+      <c r="P72">
+        <v>496.125799623</v>
+      </c>
+      <c r="Q72">
+        <v>503.385799623</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1631310825607825</v>
+      </c>
+      <c r="T72">
+        <v>2.707982658352536</v>
+      </c>
+      <c r="U72">
+        <v>0.0565</v>
+      </c>
+      <c r="V72">
+        <v>0.2494</v>
+      </c>
+      <c r="W72">
+        <v>0.0424089</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>6.391245142595099</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.07848528928691376</v>
+      </c>
+      <c r="C73">
+        <v>1116.738282218529</v>
+      </c>
+      <c r="D73">
+        <v>2804.467282218529</v>
+      </c>
+      <c r="E73">
+        <v>266.5289999999998</v>
+      </c>
+      <c r="F73">
+        <v>2200.929</v>
+      </c>
+      <c r="G73">
+        <v>513.2</v>
+      </c>
+      <c r="H73">
+        <v>1165.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K73">
+        <v>7.26</v>
+      </c>
+      <c r="L73">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M73">
+        <v>124.3524885</v>
+      </c>
+      <c r="N73">
+        <v>659.2208448333333</v>
+      </c>
+      <c r="O73">
+        <v>164.4096787014333</v>
+      </c>
+      <c r="P73">
+        <v>494.8111661319</v>
+      </c>
+      <c r="Q73">
+        <v>502.0711661319</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1668102423686681</v>
+      </c>
+      <c r="T73">
+        <v>2.792897079489838</v>
+      </c>
+      <c r="U73">
+        <v>0.0565</v>
+      </c>
+      <c r="V73">
+        <v>0.2494</v>
+      </c>
+      <c r="W73">
+        <v>0.0424089</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.301227605375451</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.07834502380559276</v>
+      </c>
+      <c r="C74">
+        <v>1097.82622846073</v>
+      </c>
+      <c r="D74">
+        <v>2816.554228460731</v>
+      </c>
+      <c r="E74">
+        <v>297.528</v>
+      </c>
+      <c r="F74">
+        <v>2231.928</v>
+      </c>
+      <c r="G74">
+        <v>513.2</v>
+      </c>
+      <c r="H74">
+        <v>1165.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K74">
+        <v>7.26</v>
+      </c>
+      <c r="L74">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M74">
+        <v>126.103932</v>
+      </c>
+      <c r="N74">
+        <v>657.4694013333334</v>
+      </c>
+      <c r="O74">
+        <v>163.9728686925334</v>
+      </c>
+      <c r="P74">
+        <v>493.4965326408001</v>
+      </c>
+      <c r="Q74">
+        <v>500.7565326408001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1707521993056884</v>
+      </c>
+      <c r="T74">
+        <v>2.883876816422662</v>
+      </c>
+      <c r="U74">
+        <v>0.0565</v>
+      </c>
+      <c r="V74">
+        <v>0.2494</v>
+      </c>
+      <c r="W74">
+        <v>0.0424089</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>6.213710555300792</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.07897187152427175</v>
+      </c>
+      <c r="C75">
+        <v>1013.602899789542</v>
+      </c>
+      <c r="D75">
+        <v>2763.329899789543</v>
+      </c>
+      <c r="E75">
+        <v>328.5269999999998</v>
+      </c>
+      <c r="F75">
+        <v>2262.927</v>
+      </c>
+      <c r="G75">
+        <v>513.2</v>
+      </c>
+      <c r="H75">
+        <v>1165.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K75">
+        <v>7.26</v>
+      </c>
+      <c r="L75">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M75">
+        <v>131.0234733</v>
+      </c>
+      <c r="N75">
+        <v>652.5498600333334</v>
+      </c>
+      <c r="O75">
+        <v>162.7459350923133</v>
+      </c>
+      <c r="P75">
+        <v>489.8039249410201</v>
+      </c>
+      <c r="Q75">
+        <v>497.06392494102</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1749861530528583</v>
+      </c>
+      <c r="T75">
+        <v>2.981595793128287</v>
+      </c>
+      <c r="U75">
+        <v>0.0579</v>
+      </c>
+      <c r="V75">
+        <v>0.2494</v>
+      </c>
+      <c r="W75">
+        <v>0.04345974</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>5.980404225273529</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.07884211444295075</v>
+      </c>
+      <c r="C76">
+        <v>993.4555546720658</v>
+      </c>
+      <c r="D76">
+        <v>2774.181554672066</v>
+      </c>
+      <c r="E76">
+        <v>359.5260000000001</v>
+      </c>
+      <c r="F76">
+        <v>2293.926</v>
+      </c>
+      <c r="G76">
+        <v>513.2</v>
+      </c>
+      <c r="H76">
+        <v>1165.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K76">
+        <v>7.26</v>
+      </c>
+      <c r="L76">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M76">
+        <v>132.8183154</v>
+      </c>
+      <c r="N76">
+        <v>650.7550179333334</v>
+      </c>
+      <c r="O76">
+        <v>162.2983014725734</v>
+      </c>
+      <c r="P76">
+        <v>488.45671646076</v>
+      </c>
+      <c r="Q76">
+        <v>495.71671646076</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1795457955498106</v>
+      </c>
+      <c r="T76">
+        <v>3.086831614195884</v>
+      </c>
+      <c r="U76">
+        <v>0.0579</v>
+      </c>
+      <c r="V76">
+        <v>0.2494</v>
+      </c>
+      <c r="W76">
+        <v>0.04345974</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>5.899587951959021</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.07871235736162976</v>
+      </c>
+      <c r="C77">
+        <v>973.393774927471</v>
+      </c>
+      <c r="D77">
+        <v>2785.118774927471</v>
+      </c>
+      <c r="E77">
+        <v>390.5249999999999</v>
+      </c>
+      <c r="F77">
+        <v>2324.925</v>
+      </c>
+      <c r="G77">
+        <v>513.2</v>
+      </c>
+      <c r="H77">
+        <v>1165.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K77">
+        <v>7.26</v>
+      </c>
+      <c r="L77">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M77">
+        <v>134.6131575</v>
+      </c>
+      <c r="N77">
+        <v>648.9601758333333</v>
+      </c>
+      <c r="O77">
+        <v>161.8506678528333</v>
+      </c>
+      <c r="P77">
+        <v>487.1095079805</v>
+      </c>
+      <c r="Q77">
+        <v>494.3695079805</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1844702094465191</v>
+      </c>
+      <c r="T77">
+        <v>3.20048630094889</v>
+      </c>
+      <c r="U77">
+        <v>0.0579</v>
+      </c>
+      <c r="V77">
+        <v>0.2494</v>
+      </c>
+      <c r="W77">
+        <v>0.04345974</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>5.820926779266234</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.07858260028030876</v>
+      </c>
+      <c r="C78">
+        <v>953.4185765867919</v>
+      </c>
+      <c r="D78">
+        <v>2796.142576586792</v>
+      </c>
+      <c r="E78">
+        <v>421.5240000000001</v>
+      </c>
+      <c r="F78">
+        <v>2355.924</v>
+      </c>
+      <c r="G78">
+        <v>513.2</v>
+      </c>
+      <c r="H78">
+        <v>1165.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K78">
+        <v>7.26</v>
+      </c>
+      <c r="L78">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M78">
+        <v>136.4079996</v>
+      </c>
+      <c r="N78">
+        <v>647.1653337333333</v>
+      </c>
+      <c r="O78">
+        <v>161.4030342330933</v>
+      </c>
+      <c r="P78">
+        <v>485.76229950024</v>
+      </c>
+      <c r="Q78">
+        <v>493.02229950024</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1898049911679532</v>
+      </c>
+      <c r="T78">
+        <v>3.323612211597978</v>
+      </c>
+      <c r="U78">
+        <v>0.0579</v>
+      </c>
+      <c r="V78">
+        <v>0.2494</v>
+      </c>
+      <c r="W78">
+        <v>0.04345974</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>5.744335637433783</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.07845284319898777</v>
+      </c>
+      <c r="C79">
+        <v>933.5309918312241</v>
+      </c>
+      <c r="D79">
+        <v>2807.253991831225</v>
+      </c>
+      <c r="E79">
+        <v>452.5230000000004</v>
+      </c>
+      <c r="F79">
+        <v>2386.923000000001</v>
+      </c>
+      <c r="G79">
+        <v>513.2</v>
+      </c>
+      <c r="H79">
+        <v>1165.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K79">
+        <v>7.26</v>
+      </c>
+      <c r="L79">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M79">
+        <v>138.2028417000001</v>
+      </c>
+      <c r="N79">
+        <v>645.3704916333334</v>
+      </c>
+      <c r="O79">
+        <v>160.9554006133533</v>
+      </c>
+      <c r="P79">
+        <v>484.41509101998</v>
+      </c>
+      <c r="Q79">
+        <v>491.67509101998</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1956036669521208</v>
+      </c>
+      <c r="T79">
+        <v>3.457444723173074</v>
+      </c>
+      <c r="U79">
+        <v>0.0579</v>
+      </c>
+      <c r="V79">
+        <v>0.2494</v>
+      </c>
+      <c r="W79">
+        <v>0.04345974</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.669733875908668</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.07832308611766678</v>
+      </c>
+      <c r="C80">
+        <v>913.732069314302</v>
+      </c>
+      <c r="D80">
+        <v>2818.454069314303</v>
+      </c>
+      <c r="E80">
+        <v>483.5220000000002</v>
+      </c>
+      <c r="F80">
+        <v>2417.922</v>
+      </c>
+      <c r="G80">
+        <v>513.2</v>
+      </c>
+      <c r="H80">
+        <v>1165.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K80">
+        <v>7.26</v>
+      </c>
+      <c r="L80">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M80">
+        <v>139.9976838</v>
+      </c>
+      <c r="N80">
+        <v>643.5756495333334</v>
+      </c>
+      <c r="O80">
+        <v>160.5077669936134</v>
+      </c>
+      <c r="P80">
+        <v>483.06788253972</v>
+      </c>
+      <c r="Q80">
+        <v>490.32788253972</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2019294950803035</v>
+      </c>
+      <c r="T80">
+        <v>3.603443826709543</v>
+      </c>
+      <c r="U80">
+        <v>0.0579</v>
+      </c>
+      <c r="V80">
+        <v>0.2494</v>
+      </c>
+      <c r="W80">
+        <v>0.04345974</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.597044980063686</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.07819332903634577</v>
+      </c>
+      <c r="C81">
+        <v>894.0228744918199</v>
+      </c>
+      <c r="D81">
+        <v>2829.74387449182</v>
+      </c>
+      <c r="E81">
+        <v>514.5210000000004</v>
+      </c>
+      <c r="F81">
+        <v>2448.921000000001</v>
+      </c>
+      <c r="G81">
+        <v>513.2</v>
+      </c>
+      <c r="H81">
+        <v>1165.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K81">
+        <v>7.26</v>
+      </c>
+      <c r="L81">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M81">
+        <v>141.7925259</v>
+      </c>
+      <c r="N81">
+        <v>641.7808074333334</v>
+      </c>
+      <c r="O81">
+        <v>160.0601333738734</v>
+      </c>
+      <c r="P81">
+        <v>481.7206740594601</v>
+      </c>
+      <c r="Q81">
+        <v>488.9806740594601</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.208857783030218</v>
+      </c>
+      <c r="T81">
+        <v>3.763347606773295</v>
+      </c>
+      <c r="U81">
+        <v>0.0579</v>
+      </c>
+      <c r="V81">
+        <v>0.2494</v>
+      </c>
+      <c r="W81">
+        <v>0.04345974</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.526196309429968</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.07806357195502478</v>
+      </c>
+      <c r="C82">
+        <v>874.404489959687</v>
+      </c>
+      <c r="D82">
+        <v>2841.124489959687</v>
+      </c>
+      <c r="E82">
+        <v>545.5200000000002</v>
+      </c>
+      <c r="F82">
+        <v>2479.920000000001</v>
+      </c>
+      <c r="G82">
+        <v>513.2</v>
+      </c>
+      <c r="H82">
+        <v>1165.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K82">
+        <v>7.26</v>
+      </c>
+      <c r="L82">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M82">
+        <v>143.587368</v>
+      </c>
+      <c r="N82">
+        <v>639.9859653333333</v>
+      </c>
+      <c r="O82">
+        <v>159.6124997541333</v>
+      </c>
+      <c r="P82">
+        <v>480.3734655792</v>
+      </c>
+      <c r="Q82">
+        <v>487.6334655792</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2164788997751239</v>
+      </c>
+      <c r="T82">
+        <v>3.939241764843421</v>
+      </c>
+      <c r="U82">
+        <v>0.0579</v>
+      </c>
+      <c r="V82">
+        <v>0.2494</v>
+      </c>
+      <c r="W82">
+        <v>0.04345974</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.457118855562094</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.07793381487370377</v>
+      </c>
+      <c r="C83">
+        <v>854.8780158000127</v>
+      </c>
+      <c r="D83">
+        <v>2852.597015800013</v>
+      </c>
+      <c r="E83">
+        <v>576.5190000000005</v>
+      </c>
+      <c r="F83">
+        <v>2510.919000000001</v>
+      </c>
+      <c r="G83">
+        <v>513.2</v>
+      </c>
+      <c r="H83">
+        <v>1165.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K83">
+        <v>7.26</v>
+      </c>
+      <c r="L83">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M83">
+        <v>145.3822101</v>
+      </c>
+      <c r="N83">
+        <v>638.1911232333333</v>
+      </c>
+      <c r="O83">
+        <v>159.1648661343933</v>
+      </c>
+      <c r="P83">
+        <v>479.02625709894</v>
+      </c>
+      <c r="Q83">
+        <v>486.28625709894</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2249022393352831</v>
+      </c>
+      <c r="T83">
+        <v>4.133651097447245</v>
+      </c>
+      <c r="U83">
+        <v>0.0579</v>
+      </c>
+      <c r="V83">
+        <v>0.2494</v>
+      </c>
+      <c r="W83">
+        <v>0.04345974</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.389747017839104</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.07780405779238278</v>
+      </c>
+      <c r="C84">
+        <v>835.4445699355656</v>
+      </c>
+      <c r="D84">
+        <v>2864.162569935566</v>
+      </c>
+      <c r="E84">
+        <v>607.5180000000003</v>
+      </c>
+      <c r="F84">
+        <v>2541.918000000001</v>
+      </c>
+      <c r="G84">
+        <v>513.2</v>
+      </c>
+      <c r="H84">
+        <v>1165.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K84">
+        <v>7.26</v>
+      </c>
+      <c r="L84">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M84">
+        <v>147.1770522</v>
+      </c>
+      <c r="N84">
+        <v>636.3962811333333</v>
+      </c>
+      <c r="O84">
+        <v>158.7172325146533</v>
+      </c>
+      <c r="P84">
+        <v>477.67904861868</v>
+      </c>
+      <c r="Q84">
+        <v>484.93904861868</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2342615055132377</v>
+      </c>
+      <c r="T84">
+        <v>4.34966146700705</v>
+      </c>
+      <c r="U84">
+        <v>0.0579</v>
+      </c>
+      <c r="V84">
+        <v>0.2494</v>
+      </c>
+      <c r="W84">
+        <v>0.04345974</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.324018395670335</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.07767430071106178</v>
+      </c>
+      <c r="C85">
+        <v>816.1052884929263</v>
+      </c>
+      <c r="D85">
+        <v>2875.822288492927</v>
+      </c>
+      <c r="E85">
+        <v>638.5170000000005</v>
+      </c>
+      <c r="F85">
+        <v>2572.917000000001</v>
+      </c>
+      <c r="G85">
+        <v>513.2</v>
+      </c>
+      <c r="H85">
+        <v>1165.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K85">
+        <v>7.26</v>
+      </c>
+      <c r="L85">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M85">
+        <v>148.9718943000001</v>
+      </c>
+      <c r="N85">
+        <v>634.6014390333333</v>
+      </c>
+      <c r="O85">
+        <v>158.2695988949133</v>
+      </c>
+      <c r="P85">
+        <v>476.33184013842</v>
+      </c>
+      <c r="Q85">
+        <v>483.59184013842</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2447218618297753</v>
+      </c>
+      <c r="T85">
+        <v>4.591084821220949</v>
+      </c>
+      <c r="U85">
+        <v>0.0579</v>
+      </c>
+      <c r="V85">
+        <v>0.2494</v>
+      </c>
+      <c r="W85">
+        <v>0.04345974</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.2598735957225</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.07754454362974078</v>
+      </c>
+      <c r="C86">
+        <v>796.8613261745249</v>
+      </c>
+      <c r="D86">
+        <v>2887.577326174525</v>
+      </c>
+      <c r="E86">
+        <v>669.5159999999998</v>
+      </c>
+      <c r="F86">
+        <v>2603.916</v>
+      </c>
+      <c r="G86">
+        <v>513.2</v>
+      </c>
+      <c r="H86">
+        <v>1165.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K86">
+        <v>7.26</v>
+      </c>
+      <c r="L86">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M86">
+        <v>150.7667364</v>
+      </c>
+      <c r="N86">
+        <v>632.8065969333334</v>
+      </c>
+      <c r="O86">
+        <v>157.8219652751733</v>
+      </c>
+      <c r="P86">
+        <v>474.98463165816</v>
+      </c>
+      <c r="Q86">
+        <v>482.24463165816</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2564897626858799</v>
+      </c>
+      <c r="T86">
+        <v>4.862686094711584</v>
+      </c>
+      <c r="U86">
+        <v>0.0579</v>
+      </c>
+      <c r="V86">
+        <v>0.2494</v>
+      </c>
+      <c r="W86">
+        <v>0.04345974</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.197256052916281</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.0774147865484198</v>
+      </c>
+      <c r="C87">
+        <v>777.7138566398412</v>
+      </c>
+      <c r="D87">
+        <v>2899.428856639841</v>
+      </c>
+      <c r="E87">
+        <v>700.5150000000001</v>
+      </c>
+      <c r="F87">
+        <v>2634.915</v>
+      </c>
+      <c r="G87">
+        <v>513.2</v>
+      </c>
+      <c r="H87">
+        <v>1165.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K87">
+        <v>7.26</v>
+      </c>
+      <c r="L87">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M87">
+        <v>152.5615785</v>
+      </c>
+      <c r="N87">
+        <v>631.0117548333334</v>
+      </c>
+      <c r="O87">
+        <v>157.3743316554334</v>
+      </c>
+      <c r="P87">
+        <v>473.6374231779</v>
+      </c>
+      <c r="Q87">
+        <v>480.8974231779</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2698267169894653</v>
+      </c>
+      <c r="T87">
+        <v>5.170500871334306</v>
+      </c>
+      <c r="U87">
+        <v>0.0579</v>
+      </c>
+      <c r="V87">
+        <v>0.2494</v>
+      </c>
+      <c r="W87">
+        <v>0.04345974</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.136111864058441</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.07728502946709878</v>
+      </c>
+      <c r="C88">
+        <v>758.6640728960506</v>
+      </c>
+      <c r="D88">
+        <v>2911.378072896051</v>
+      </c>
+      <c r="E88">
+        <v>731.5139999999999</v>
+      </c>
+      <c r="F88">
+        <v>2665.914</v>
+      </c>
+      <c r="G88">
+        <v>513.2</v>
+      </c>
+      <c r="H88">
+        <v>1165.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K88">
+        <v>7.26</v>
+      </c>
+      <c r="L88">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M88">
+        <v>154.3564206</v>
+      </c>
+      <c r="N88">
+        <v>629.2169127333334</v>
+      </c>
+      <c r="O88">
+        <v>156.9266980356934</v>
+      </c>
+      <c r="P88">
+        <v>472.2902146976401</v>
+      </c>
+      <c r="Q88">
+        <v>479.5502146976401</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2850689504792771</v>
+      </c>
+      <c r="T88">
+        <v>5.522289187474558</v>
+      </c>
+      <c r="U88">
+        <v>0.0579</v>
+      </c>
+      <c r="V88">
+        <v>0.2494</v>
+      </c>
+      <c r="W88">
+        <v>0.04345974</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>5.076389633081019</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.0771552723857778</v>
+      </c>
+      <c r="C89">
+        <v>739.7131876983403</v>
+      </c>
+      <c r="D89">
+        <v>2923.426187698341</v>
+      </c>
+      <c r="E89">
+        <v>762.5130000000001</v>
+      </c>
+      <c r="F89">
+        <v>2696.913</v>
+      </c>
+      <c r="G89">
+        <v>513.2</v>
+      </c>
+      <c r="H89">
+        <v>1165.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K89">
+        <v>7.26</v>
+      </c>
+      <c r="L89">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M89">
+        <v>156.1512627</v>
+      </c>
+      <c r="N89">
+        <v>627.4220706333333</v>
+      </c>
+      <c r="O89">
+        <v>156.4790644159533</v>
+      </c>
+      <c r="P89">
+        <v>470.94300621738</v>
+      </c>
+      <c r="Q89">
+        <v>478.20300621738</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3026561429675215</v>
+      </c>
+      <c r="T89">
+        <v>5.928198783021004</v>
+      </c>
+      <c r="U89">
+        <v>0.0579</v>
+      </c>
+      <c r="V89">
+        <v>0.2494</v>
+      </c>
+      <c r="W89">
+        <v>0.04345974</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>5.01804032695365</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.07702551530445681</v>
+      </c>
+      <c r="C90">
+        <v>720.8624339602343</v>
+      </c>
+      <c r="D90">
+        <v>2935.574433960235</v>
+      </c>
+      <c r="E90">
+        <v>793.5120000000004</v>
+      </c>
+      <c r="F90">
+        <v>2727.912000000001</v>
+      </c>
+      <c r="G90">
+        <v>513.2</v>
+      </c>
+      <c r="H90">
+        <v>1165.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K90">
+        <v>7.26</v>
+      </c>
+      <c r="L90">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M90">
+        <v>157.9461048</v>
+      </c>
+      <c r="N90">
+        <v>625.6272285333333</v>
+      </c>
+      <c r="O90">
+        <v>156.0314307962133</v>
+      </c>
+      <c r="P90">
+        <v>469.59579773712</v>
+      </c>
+      <c r="Q90">
+        <v>476.85579773712</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3231745342038067</v>
+      </c>
+      <c r="T90">
+        <v>6.401759977825192</v>
+      </c>
+      <c r="U90">
+        <v>0.0579</v>
+      </c>
+      <c r="V90">
+        <v>0.2494</v>
+      </c>
+      <c r="W90">
+        <v>0.04345974</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>4.961017141420085</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.0768957582231358</v>
+      </c>
+      <c r="C91">
+        <v>702.1130651741746</v>
+      </c>
+      <c r="D91">
+        <v>2947.824065174175</v>
+      </c>
+      <c r="E91">
+        <v>824.5110000000002</v>
+      </c>
+      <c r="F91">
+        <v>2758.911000000001</v>
+      </c>
+      <c r="G91">
+        <v>513.2</v>
+      </c>
+      <c r="H91">
+        <v>1165.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K91">
+        <v>7.26</v>
+      </c>
+      <c r="L91">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M91">
+        <v>159.7409469</v>
+      </c>
+      <c r="N91">
+        <v>623.8323864333333</v>
+      </c>
+      <c r="O91">
+        <v>155.5837971764734</v>
+      </c>
+      <c r="P91">
+        <v>468.24858925686</v>
+      </c>
+      <c r="Q91">
+        <v>475.50858925686</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3474235420285073</v>
+      </c>
+      <c r="T91">
+        <v>6.961423208048322</v>
+      </c>
+      <c r="U91">
+        <v>0.0579</v>
+      </c>
+      <c r="V91">
+        <v>0.2494</v>
+      </c>
+      <c r="W91">
+        <v>0.04345974</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>4.905275375786152</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.07676600114181481</v>
+      </c>
+      <c r="C92">
+        <v>683.4663558426728</v>
+      </c>
+      <c r="D92">
+        <v>2960.176355842674</v>
+      </c>
+      <c r="E92">
+        <v>855.5100000000004</v>
+      </c>
+      <c r="F92">
+        <v>2789.910000000001</v>
+      </c>
+      <c r="G92">
+        <v>513.2</v>
+      </c>
+      <c r="H92">
+        <v>1165.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K92">
+        <v>7.26</v>
+      </c>
+      <c r="L92">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M92">
+        <v>161.5357890000001</v>
+      </c>
+      <c r="N92">
+        <v>622.0375443333334</v>
+      </c>
+      <c r="O92">
+        <v>155.1361635567334</v>
+      </c>
+      <c r="P92">
+        <v>466.9013807766</v>
+      </c>
+      <c r="Q92">
+        <v>474.1613807766</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3765223514181481</v>
+      </c>
+      <c r="T92">
+        <v>7.633019084316078</v>
+      </c>
+      <c r="U92">
+        <v>0.0579</v>
+      </c>
+      <c r="V92">
+        <v>0.2494</v>
+      </c>
+      <c r="W92">
+        <v>0.04345974</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>4.850772316055194</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.0766362440604938</v>
+      </c>
+      <c r="C93">
+        <v>664.9236019203763</v>
+      </c>
+      <c r="D93">
+        <v>2972.632601920377</v>
+      </c>
+      <c r="E93">
+        <v>886.5090000000002</v>
+      </c>
+      <c r="F93">
+        <v>2820.909000000001</v>
+      </c>
+      <c r="G93">
+        <v>513.2</v>
+      </c>
+      <c r="H93">
+        <v>1165.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K93">
+        <v>7.26</v>
+      </c>
+      <c r="L93">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M93">
+        <v>163.3306311</v>
+      </c>
+      <c r="N93">
+        <v>620.2427022333334</v>
+      </c>
+      <c r="O93">
+        <v>154.6885299369933</v>
+      </c>
+      <c r="P93">
+        <v>465.55417229634</v>
+      </c>
+      <c r="Q93">
+        <v>472.81417229634</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4120875628943757</v>
+      </c>
+      <c r="T93">
+        <v>8.453858488643334</v>
+      </c>
+      <c r="U93">
+        <v>0.0579</v>
+      </c>
+      <c r="V93">
+        <v>0.2494</v>
+      </c>
+      <c r="W93">
+        <v>0.04345974</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>4.797467125768874</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.07650648697917281</v>
+      </c>
+      <c r="C94">
+        <v>646.4861212672954</v>
+      </c>
+      <c r="D94">
+        <v>2985.194121267296</v>
+      </c>
+      <c r="E94">
+        <v>917.5080000000005</v>
+      </c>
+      <c r="F94">
+        <v>2851.908000000001</v>
+      </c>
+      <c r="G94">
+        <v>513.2</v>
+      </c>
+      <c r="H94">
+        <v>1165.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K94">
+        <v>7.26</v>
+      </c>
+      <c r="L94">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M94">
+        <v>165.1254732</v>
+      </c>
+      <c r="N94">
+        <v>618.4478601333333</v>
+      </c>
+      <c r="O94">
+        <v>154.2408963172533</v>
+      </c>
+      <c r="P94">
+        <v>464.20696381608</v>
+      </c>
+      <c r="Q94">
+        <v>471.46696381608</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4565440772396604</v>
+      </c>
+      <c r="T94">
+        <v>9.47990774405241</v>
+      </c>
+      <c r="U94">
+        <v>0.0579</v>
+      </c>
+      <c r="V94">
+        <v>0.2494</v>
+      </c>
+      <c r="W94">
+        <v>0.04345974</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.745320743967037</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.07637672989785181</v>
+      </c>
+      <c r="C95">
+        <v>628.155254113623</v>
+      </c>
+      <c r="D95">
+        <v>2997.862254113623</v>
+      </c>
+      <c r="E95">
+        <v>948.5070000000003</v>
+      </c>
+      <c r="F95">
+        <v>2882.907000000001</v>
+      </c>
+      <c r="G95">
+        <v>513.2</v>
+      </c>
+      <c r="H95">
+        <v>1165.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K95">
+        <v>7.26</v>
+      </c>
+      <c r="L95">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M95">
+        <v>166.9203153</v>
+      </c>
+      <c r="N95">
+        <v>616.6530180333334</v>
+      </c>
+      <c r="O95">
+        <v>153.7932626975134</v>
+      </c>
+      <c r="P95">
+        <v>462.8597553358201</v>
+      </c>
+      <c r="Q95">
+        <v>470.1197553358201</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5137024528264548</v>
+      </c>
+      <c r="T95">
+        <v>10.79911392957836</v>
+      </c>
+      <c r="U95">
+        <v>0.0579</v>
+      </c>
+      <c r="V95">
+        <v>0.2494</v>
+      </c>
+      <c r="W95">
+        <v>0.04345974</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.694295789730834</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.07624697281653081</v>
+      </c>
+      <c r="C96">
+        <v>609.9323635363953</v>
+      </c>
+      <c r="D96">
+        <v>3010.638363536396</v>
+      </c>
+      <c r="E96">
+        <v>979.5060000000005</v>
+      </c>
+      <c r="F96">
+        <v>2913.906000000001</v>
+      </c>
+      <c r="G96">
+        <v>513.2</v>
+      </c>
+      <c r="H96">
+        <v>1165.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K96">
+        <v>7.26</v>
+      </c>
+      <c r="L96">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M96">
+        <v>168.7151574</v>
+      </c>
+      <c r="N96">
+        <v>614.8581759333333</v>
+      </c>
+      <c r="O96">
+        <v>153.3456290777733</v>
+      </c>
+      <c r="P96">
+        <v>461.51254685556</v>
+      </c>
+      <c r="Q96">
+        <v>468.77254685556</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.589913620275514</v>
+      </c>
+      <c r="T96">
+        <v>12.55805551027963</v>
+      </c>
+      <c r="U96">
+        <v>0.0579</v>
+      </c>
+      <c r="V96">
+        <v>0.2494</v>
+      </c>
+      <c r="W96">
+        <v>0.04345974</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.644356472818803</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.07611721573520983</v>
+      </c>
+      <c r="C97">
+        <v>591.8188359484202</v>
+      </c>
+      <c r="D97">
+        <v>3023.523835948421</v>
+      </c>
+      <c r="E97">
+        <v>1010.505</v>
+      </c>
+      <c r="F97">
+        <v>2944.905000000001</v>
+      </c>
+      <c r="G97">
+        <v>513.2</v>
+      </c>
+      <c r="H97">
+        <v>1165.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K97">
+        <v>7.26</v>
+      </c>
+      <c r="L97">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M97">
+        <v>170.5099995</v>
+      </c>
+      <c r="N97">
+        <v>613.0633338333333</v>
+      </c>
+      <c r="O97">
+        <v>152.8979954580333</v>
+      </c>
+      <c r="P97">
+        <v>460.1653383753</v>
+      </c>
+      <c r="Q97">
+        <v>467.4253383753</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.6966092547041972</v>
+      </c>
+      <c r="T97">
+        <v>15.02057372326141</v>
+      </c>
+      <c r="U97">
+        <v>0.0579</v>
+      </c>
+      <c r="V97">
+        <v>0.2494</v>
+      </c>
+      <c r="W97">
+        <v>0.04345974</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.595468509947025</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.07598745865388881</v>
+      </c>
+      <c r="C98">
+        <v>573.8160815998126</v>
+      </c>
+      <c r="D98">
+        <v>3036.520081599813</v>
+      </c>
+      <c r="E98">
+        <v>1041.504</v>
+      </c>
+      <c r="F98">
+        <v>2975.904</v>
+      </c>
+      <c r="G98">
+        <v>513.2</v>
+      </c>
+      <c r="H98">
+        <v>1165.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K98">
+        <v>7.26</v>
+      </c>
+      <c r="L98">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M98">
+        <v>172.3048416</v>
+      </c>
+      <c r="N98">
+        <v>611.2684917333333</v>
+      </c>
+      <c r="O98">
+        <v>152.4503618382933</v>
+      </c>
+      <c r="P98">
+        <v>458.81812989504</v>
+      </c>
+      <c r="Q98">
+        <v>466.07812989504</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.8566527063472198</v>
+      </c>
+      <c r="T98">
+        <v>18.71435104273403</v>
+      </c>
+      <c r="U98">
+        <v>0.0579</v>
+      </c>
+      <c r="V98">
+        <v>0.2494</v>
+      </c>
+      <c r="W98">
+        <v>0.04345974</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.547599046301745</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.07585770157256783</v>
+      </c>
+      <c r="C99">
+        <v>555.9255350924959</v>
+      </c>
+      <c r="D99">
+        <v>3049.628535092496</v>
+      </c>
+      <c r="E99">
+        <v>1072.503</v>
+      </c>
+      <c r="F99">
+        <v>3006.903</v>
+      </c>
+      <c r="G99">
+        <v>513.2</v>
+      </c>
+      <c r="H99">
+        <v>1165.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K99">
+        <v>7.26</v>
+      </c>
+      <c r="L99">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M99">
+        <v>174.0996837</v>
+      </c>
+      <c r="N99">
+        <v>609.4736496333334</v>
+      </c>
+      <c r="O99">
+        <v>152.0027282185534</v>
+      </c>
+      <c r="P99">
+        <v>457.47092141478</v>
+      </c>
+      <c r="Q99">
+        <v>464.73092141478</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.123391792418927</v>
+      </c>
+      <c r="T99">
+        <v>24.87064657518845</v>
+      </c>
+      <c r="U99">
+        <v>0.0579</v>
+      </c>
+      <c r="V99">
+        <v>0.2494</v>
+      </c>
+      <c r="W99">
+        <v>0.04345974</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.500716581906882</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.07764047329124682</v>
+      </c>
+      <c r="C100">
+        <v>354.1755712136405</v>
+      </c>
+      <c r="D100">
+        <v>2878.877571213641</v>
+      </c>
+      <c r="E100">
+        <v>1103.502</v>
+      </c>
+      <c r="F100">
+        <v>3037.902</v>
+      </c>
+      <c r="G100">
+        <v>513.2</v>
+      </c>
+      <c r="H100">
+        <v>1165.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K100">
+        <v>7.26</v>
+      </c>
+      <c r="L100">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M100">
+        <v>183.793071</v>
+      </c>
+      <c r="N100">
+        <v>599.7802623333333</v>
+      </c>
+      <c r="O100">
+        <v>149.5851974259333</v>
+      </c>
+      <c r="P100">
+        <v>450.1950649074</v>
+      </c>
+      <c r="Q100">
+        <v>457.4550649074</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.65686996456234</v>
+      </c>
+      <c r="T100">
+        <v>37.18323764009729</v>
+      </c>
+      <c r="U100">
+        <v>0.0605</v>
+      </c>
+      <c r="V100">
+        <v>0.2494</v>
+      </c>
+      <c r="W100">
+        <v>0.04541129999999999</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.263345343053402</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.07753023180992583</v>
+      </c>
+      <c r="C101">
+        <v>333.1787587139884</v>
+      </c>
+      <c r="D101">
+        <v>2888.879758713988</v>
+      </c>
+      <c r="E101">
+        <v>1134.501</v>
+      </c>
+      <c r="F101">
+        <v>3068.901</v>
+      </c>
+      <c r="G101">
+        <v>513.2</v>
+      </c>
+      <c r="H101">
+        <v>1165.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>790.8333333333334</v>
+      </c>
+      <c r="K101">
+        <v>7.26</v>
+      </c>
+      <c r="L101">
+        <v>783.5733333333334</v>
+      </c>
+      <c r="M101">
+        <v>185.6685105</v>
+      </c>
+      <c r="N101">
+        <v>597.9048228333334</v>
+      </c>
+      <c r="O101">
+        <v>149.1174628146333</v>
+      </c>
+      <c r="P101">
+        <v>448.7873600187</v>
+      </c>
+      <c r="Q101">
+        <v>456.0473600187</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.25730448099258</v>
+      </c>
+      <c r="T101">
+        <v>74.12101083482381</v>
+      </c>
+      <c r="U101">
+        <v>0.0605</v>
+      </c>
+      <c r="V101">
+        <v>0.2494</v>
+      </c>
+      <c r="W101">
+        <v>0.04541129999999999</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.220281248679125</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_metals_mining.xlsx
@@ -644,10 +644,10 @@
         <v>-0.1565285996055227</v>
       </c>
       <c r="X2">
-        <v>0.141569501456546</v>
+        <v>0.1415079301820267</v>
       </c>
       <c r="Y2">
-        <v>-0.2980981010620687</v>
+        <v>-0.2980365297875494</v>
       </c>
       <c r="Z2">
         <v>1.219976109528623</v>
@@ -656,10 +656,10 @@
         <v>0.0751630984103648</v>
       </c>
       <c r="AB2">
-        <v>0.08123697545714517</v>
+        <v>0.08121382589733606</v>
       </c>
       <c r="AC2">
-        <v>-0.006073877046780377</v>
+        <v>-0.006050727486971261</v>
       </c>
       <c r="AD2">
         <v>1934.4</v>
@@ -775,10 +775,10 @@
         <v>-0.1565285996055227</v>
       </c>
       <c r="X3">
-        <v>0.141569501456546</v>
+        <v>0.1415079301820267</v>
       </c>
       <c r="Y3">
-        <v>-0.2980981010620687</v>
+        <v>-0.2980365297875494</v>
       </c>
       <c r="Z3">
         <v>1.219976109528623</v>
@@ -787,10 +787,10 @@
         <v>0.0751630984103648</v>
       </c>
       <c r="AB3">
-        <v>0.08123697545714517</v>
+        <v>0.08121382589733606</v>
       </c>
       <c r="AC3">
-        <v>-0.006073877046780377</v>
+        <v>-0.006050727486971261</v>
       </c>
       <c r="AD3">
         <v>1934.4</v>
@@ -1127,49 +1127,49 @@
         <v>2.36099039919151</v>
       </c>
       <c r="F2">
-        <v>4.50071658190688</v>
+        <v>4.61712505506487</v>
       </c>
       <c r="G2">
         <v>4.07671232876712</v>
       </c>
       <c r="H2">
-        <v>6.33699262381454</v>
+        <v>6.46765226554268</v>
       </c>
       <c r="I2">
         <v>0.624020129681603</v>
       </c>
       <c r="J2">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="K2">
         <v>1165.5</v>
       </c>
       <c r="L2">
-        <v>555.925535092496</v>
+        <v>734.057020674078</v>
       </c>
       <c r="M2">
         <v>2586.7</v>
       </c>
       <c r="N2">
-        <v>3049.6285350925</v>
+        <v>3289.75802067408</v>
       </c>
       <c r="O2">
         <v>1934.4</v>
       </c>
       <c r="P2">
-        <v>3006.903</v>
+        <v>3068.901</v>
       </c>
       <c r="Q2">
-        <v>0.0812369754571452</v>
+        <v>0.0812138258973361</v>
       </c>
       <c r="R2">
-        <v>0.0758577015725678</v>
+        <v>0.0736454958914787</v>
       </c>
       <c r="S2">
         <v>0.04488588</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.141569501456546</v>
+        <v>0.141507930182027</v>
       </c>
       <c r="X2">
-        <v>1.12339179241893</v>
+        <v>3.25523976914787</v>
       </c>
       <c r="Y2">
         <v>2.210344807899</v>
       </c>
       <c r="Z2">
-        <v>24.8706465751885</v>
+        <v>74.12101083482381</v>
       </c>
       <c r="AA2">
         <v>1934.4</v>
@@ -1224,7 +1224,7 @@
         <v>1165.5</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08844413846070455</v>
+        <v>0.08841672207118731</v>
       </c>
       <c r="C2">
-        <v>2662.729284064776</v>
+        <v>2662.70702439342</v>
       </c>
       <c r="D2">
-        <v>2149.529284064776</v>
+        <v>2149.50702439342</v>
       </c>
       <c r="E2">
         <v>-1934.4</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08844413846070455</v>
+        <v>0.08841672207118731</v>
       </c>
       <c r="T2">
         <v>0.984219909265296</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08826784417938355</v>
+        <v>0.08822998776634178</v>
       </c>
       <c r="C3">
-        <v>2640.653499444204</v>
+        <v>2641.168001194996</v>
       </c>
       <c r="D3">
-        <v>2158.452499444204</v>
+        <v>2158.967001194995</v>
       </c>
       <c r="E3">
         <v>-1903.401</v>
@@ -1527,37 +1527,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M3">
-        <v>1.6026483</v>
+        <v>1.5592497</v>
       </c>
       <c r="N3">
-        <v>781.9706850333333</v>
+        <v>782.0140836333334</v>
       </c>
       <c r="O3">
-        <v>195.0234888473133</v>
+        <v>195.0343124581534</v>
       </c>
       <c r="P3">
-        <v>586.9471961860199</v>
+        <v>586.9797711751801</v>
       </c>
       <c r="Q3">
-        <v>594.2071961860199</v>
+        <v>594.2397711751801</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08876745856503389</v>
+        <v>0.08873983430943613</v>
       </c>
       <c r="T3">
         <v>0.991682085668271</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>488.9240723203794</v>
+        <v>502.5322969972887</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08809154989806256</v>
+        <v>0.08804325346149623</v>
       </c>
       <c r="C4">
-        <v>2618.652108495473</v>
+        <v>2619.712612757019</v>
       </c>
       <c r="D4">
-        <v>2167.450108495474</v>
+        <v>2168.510612757018</v>
       </c>
       <c r="E4">
         <v>-1872.402</v>
@@ -1609,37 +1609,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M4">
-        <v>3.205296600000001</v>
+        <v>3.118499400000001</v>
       </c>
       <c r="N4">
-        <v>780.3680367333334</v>
+        <v>780.4548339333334</v>
       </c>
       <c r="O4">
-        <v>194.6237883612934</v>
+        <v>194.6454355829733</v>
       </c>
       <c r="P4">
-        <v>585.74424837204</v>
+        <v>585.80939835036</v>
       </c>
       <c r="Q4">
-        <v>593.00424837204</v>
+        <v>593.06939835036</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08909737703883935</v>
+        <v>0.08906954067499616</v>
       </c>
       <c r="T4">
         <v>0.9992965513855926</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>244.4620361601897</v>
+        <v>251.2661484986443</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08791525561674154</v>
+        <v>0.08785651915665069</v>
       </c>
       <c r="C5">
-        <v>2596.72604545337</v>
+        <v>2598.341973114544</v>
       </c>
       <c r="D5">
-        <v>2176.52304545337</v>
+        <v>2178.138973114543</v>
       </c>
       <c r="E5">
         <v>-1841.403</v>
@@ -1691,37 +1691,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M5">
-        <v>4.807944900000001</v>
+        <v>4.677749100000001</v>
       </c>
       <c r="N5">
-        <v>778.7653884333333</v>
+        <v>778.8955842333334</v>
       </c>
       <c r="O5">
-        <v>194.2240878752733</v>
+        <v>194.2565587077933</v>
       </c>
       <c r="P5">
-        <v>584.54130055806</v>
+        <v>584.63902552554</v>
       </c>
       <c r="Q5">
-        <v>591.80130055806</v>
+        <v>591.89902552554</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08943409795540366</v>
+        <v>0.08940604510994916</v>
       </c>
       <c r="T5">
         <v>1.007068016396055</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>162.9746907734598</v>
+        <v>167.5107656657629</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08773896133542056</v>
+        <v>0.08766978485180515</v>
       </c>
       <c r="C6">
-        <v>2574.876260261241</v>
+        <v>2577.057216176481</v>
       </c>
       <c r="D6">
-        <v>2185.672260261241</v>
+        <v>2187.853216176482</v>
       </c>
       <c r="E6">
         <v>-1810.404</v>
@@ -1773,37 +1773,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M6">
-        <v>6.410593200000002</v>
+        <v>6.236998800000001</v>
       </c>
       <c r="N6">
-        <v>777.1627401333334</v>
+        <v>777.3363345333333</v>
       </c>
       <c r="O6">
-        <v>193.8243873892534</v>
+        <v>193.8676818326134</v>
       </c>
       <c r="P6">
-        <v>583.33835274408</v>
+        <v>583.46865270072</v>
       </c>
       <c r="Q6">
-        <v>590.59835274408</v>
+        <v>590.72865270072</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08977783389106309</v>
+        <v>0.0897495600539637</v>
       </c>
       <c r="T6">
         <v>1.015001386927568</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>122.2310180800949</v>
+        <v>125.6330742493222</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08756266705409955</v>
+        <v>0.08748305054695961</v>
       </c>
       <c r="C7">
-        <v>2553.103718902565</v>
+        <v>2555.859496170769</v>
       </c>
       <c r="D7">
-        <v>2194.898718902564</v>
+        <v>2197.65449617077</v>
       </c>
       <c r="E7">
         <v>-1779.405</v>
@@ -1855,37 +1855,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M7">
-        <v>8.013241500000003</v>
+        <v>7.796248500000002</v>
       </c>
       <c r="N7">
-        <v>775.5600918333333</v>
+        <v>775.7770848333333</v>
       </c>
       <c r="O7">
-        <v>193.4246869032334</v>
+        <v>193.4788049574333</v>
       </c>
       <c r="P7">
-        <v>582.1354049301</v>
+        <v>582.2982798759</v>
       </c>
       <c r="Q7">
-        <v>589.3954049301</v>
+        <v>589.5582798759</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09012880637273638</v>
+        <v>0.09010030689153643</v>
       </c>
       <c r="T7">
         <v>1.023101775786061</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>97.78481446407588</v>
+        <v>100.5064593994577</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08738637277277857</v>
+        <v>0.08729631624211405</v>
       </c>
       <c r="C8">
-        <v>2531.409403740925</v>
+        <v>2534.749988101541</v>
       </c>
       <c r="D8">
-        <v>2204.203403740925</v>
+        <v>2207.543988101542</v>
       </c>
       <c r="E8">
         <v>-1748.406</v>
@@ -1937,37 +1937,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M8">
-        <v>9.615889800000001</v>
+        <v>9.355498200000001</v>
       </c>
       <c r="N8">
-        <v>773.9574435333334</v>
+        <v>774.2178351333333</v>
       </c>
       <c r="O8">
-        <v>193.0249864172133</v>
+        <v>193.0899280822534</v>
       </c>
       <c r="P8">
-        <v>580.9324571161201</v>
+        <v>581.12790705108</v>
       </c>
       <c r="Q8">
-        <v>588.1924571161201</v>
+        <v>588.38790705108</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09048724635401975</v>
+        <v>0.09045851642778091</v>
       </c>
       <c r="T8">
         <v>1.03137451334367</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>81.48734538672991</v>
+        <v>83.75538283288144</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08721007849145758</v>
+        <v>0.08710958193726852</v>
       </c>
       <c r="C9">
-        <v>2509.794313868696</v>
+        <v>2513.729888218712</v>
       </c>
       <c r="D9">
-        <v>2213.587313868696</v>
+        <v>2217.522888218712</v>
       </c>
       <c r="E9">
         <v>-1717.407</v>
@@ -2019,37 +2019,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M9">
-        <v>11.2185381</v>
+        <v>10.9147479</v>
       </c>
       <c r="N9">
-        <v>772.3547952333333</v>
+        <v>772.6585854333334</v>
       </c>
       <c r="O9">
-        <v>192.6252859311933</v>
+        <v>192.7010512070734</v>
       </c>
       <c r="P9">
-        <v>579.7295093021401</v>
+        <v>579.9575342262601</v>
       </c>
       <c r="Q9">
-        <v>586.98950930214</v>
+        <v>587.2175342262601</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0908533947219974</v>
+        <v>0.09082442939491239</v>
       </c>
       <c r="T9">
         <v>1.039825159235852</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>69.84629604576848</v>
+        <v>71.79032814246982</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08703378421013658</v>
+        <v>0.086922847632423</v>
       </c>
       <c r="C10">
-        <v>2488.259465464654</v>
+        <v>2492.800414500352</v>
       </c>
       <c r="D10">
-        <v>2223.051465464654</v>
+        <v>2227.592414500352</v>
       </c>
       <c r="E10">
         <v>-1686.408</v>
@@ -2101,37 +2101,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M10">
-        <v>12.8211864</v>
+        <v>12.4739976</v>
       </c>
       <c r="N10">
-        <v>770.7521469333334</v>
+        <v>771.0993357333334</v>
       </c>
       <c r="O10">
-        <v>192.2255854451734</v>
+        <v>192.3121743318934</v>
       </c>
       <c r="P10">
-        <v>578.52656148816</v>
+        <v>578.78716140144</v>
       </c>
       <c r="Q10">
-        <v>585.78656148816</v>
+        <v>586.04716140144</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09122750283710497</v>
+        <v>0.09119829699176413</v>
       </c>
       <c r="T10">
         <v>1.048459514821342</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>61.11550904004743</v>
+        <v>62.81653712466108</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08685748992881558</v>
+        <v>0.08673611332757745</v>
       </c>
       <c r="C11">
-        <v>2466.805892160811</v>
+        <v>2471.962807148264</v>
       </c>
       <c r="D11">
-        <v>2232.596892160811</v>
+        <v>2237.753807148264</v>
       </c>
       <c r="E11">
         <v>-1655.409</v>
@@ -2183,37 +2183,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M11">
-        <v>14.4238347</v>
+        <v>14.0332473</v>
       </c>
       <c r="N11">
-        <v>769.1494986333333</v>
+        <v>769.5400860333334</v>
       </c>
       <c r="O11">
-        <v>191.8258849591533</v>
+        <v>191.9232974567134</v>
       </c>
       <c r="P11">
-        <v>577.32361367418</v>
+        <v>577.61678857662</v>
       </c>
       <c r="Q11">
-        <v>584.58361367418</v>
+        <v>584.87678857662</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09160983310858854</v>
+        <v>0.09158038145887631</v>
       </c>
       <c r="T11">
         <v>1.057283636463656</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>54.32489692448661</v>
+        <v>55.83692188858764</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08668119564749459</v>
+        <v>0.08654937902273192</v>
       </c>
       <c r="C12">
-        <v>2445.434645418734</v>
+        <v>2451.218329097179</v>
       </c>
       <c r="D12">
-        <v>2242.224645418734</v>
+        <v>2248.008329097179</v>
       </c>
       <c r="E12">
         <v>-1624.41</v>
@@ -2265,37 +2265,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M12">
-        <v>16.02648300000001</v>
+        <v>15.592497</v>
       </c>
       <c r="N12">
-        <v>767.5468503333334</v>
+        <v>767.9808363333334</v>
       </c>
       <c r="O12">
-        <v>191.4261844731334</v>
+        <v>191.5344205815334</v>
       </c>
       <c r="P12">
-        <v>576.1206658602</v>
+        <v>576.4464157518</v>
       </c>
       <c r="Q12">
-        <v>583.3806658602</v>
+        <v>583.7064157518</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09200065960832732</v>
+        <v>0.09197095669192434</v>
       </c>
       <c r="T12">
         <v>1.066303849698022</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>48.89240723203794</v>
+        <v>50.25322969972886</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08650490136617359</v>
+        <v>0.08636264471788635</v>
       </c>
       <c r="C13">
-        <v>2424.146794915655</v>
+        <v>2430.568266538034</v>
       </c>
       <c r="D13">
-        <v>2251.935794915655</v>
+        <v>2258.357266538034</v>
       </c>
       <c r="E13">
         <v>-1593.411</v>
@@ -2347,37 +2347,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M13">
-        <v>17.6291313</v>
+        <v>17.1517467</v>
       </c>
       <c r="N13">
-        <v>765.9442020333333</v>
+        <v>766.4215866333334</v>
       </c>
       <c r="O13">
-        <v>191.0264839871134</v>
+        <v>191.1455437063534</v>
       </c>
       <c r="P13">
-        <v>574.91771804622</v>
+        <v>575.27604292698</v>
       </c>
       <c r="Q13">
-        <v>582.17771804622</v>
+        <v>582.53604292698</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09240026872603774</v>
+        <v>0.09237030889650152</v>
       </c>
       <c r="T13">
         <v>1.075526764353384</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>44.44764293821631</v>
+        <v>45.68475427248079</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08632860708485258</v>
+        <v>0.0861759104130408</v>
       </c>
       <c r="C14">
-        <v>2402.943428940641</v>
+        <v>2410.013929455744</v>
       </c>
       <c r="D14">
-        <v>2261.731428940641</v>
+        <v>2268.801929455744</v>
       </c>
       <c r="E14">
         <v>-1562.412</v>
@@ -2429,37 +2429,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M14">
-        <v>19.2317796</v>
+        <v>18.7109964</v>
       </c>
       <c r="N14">
-        <v>764.3415537333334</v>
+        <v>764.8623369333334</v>
       </c>
       <c r="O14">
-        <v>190.6267835010934</v>
+        <v>190.7566668311734</v>
       </c>
       <c r="P14">
-        <v>573.71477023224</v>
+        <v>574.10567010216</v>
       </c>
       <c r="Q14">
-        <v>580.97477023224</v>
+        <v>581.36567010216</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09280895986915066</v>
+        <v>0.09277873728754638</v>
       </c>
       <c r="T14">
         <v>1.084959290705459</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>40.74367269336496</v>
+        <v>41.87769141644073</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08615231280353158</v>
+        <v>0.08598917610819527</v>
       </c>
       <c r="C15">
-        <v>2381.825654801165</v>
+        <v>2389.556652181996</v>
       </c>
       <c r="D15">
-        <v>2271.612654801165</v>
+        <v>2279.343652181996</v>
       </c>
       <c r="E15">
         <v>-1531.413</v>
@@ -2511,37 +2511,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M15">
-        <v>20.8344279</v>
+        <v>20.2702461</v>
       </c>
       <c r="N15">
-        <v>762.7389054333333</v>
+        <v>763.3030872333334</v>
       </c>
       <c r="O15">
-        <v>190.2270830150733</v>
+        <v>190.3677899559933</v>
       </c>
       <c r="P15">
-        <v>572.51182241826</v>
+        <v>572.9352972773401</v>
       </c>
       <c r="Q15">
-        <v>579.7718224182599</v>
+        <v>580.19529727734</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09322704621095584</v>
+        <v>0.09319655483700606</v>
       </c>
       <c r="T15">
         <v>1.094608656743789</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>37.60954402464457</v>
+        <v>38.65633053825298</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0859760185222106</v>
+        <v>0.08580244180334973</v>
       </c>
       <c r="C16">
-        <v>2360.79459924037</v>
+        <v>2369.197793963508</v>
       </c>
       <c r="D16">
-        <v>2281.58059924037</v>
+        <v>2289.983793963508</v>
       </c>
       <c r="E16">
         <v>-1500.414</v>
@@ -2593,37 +2593,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M16">
-        <v>22.43707620000001</v>
+        <v>21.8294958</v>
       </c>
       <c r="N16">
-        <v>761.1362571333334</v>
+        <v>761.7438375333334</v>
       </c>
       <c r="O16">
-        <v>189.8273825290534</v>
+        <v>189.9789130808134</v>
       </c>
       <c r="P16">
-        <v>571.30887460428</v>
+        <v>571.7649244525201</v>
       </c>
       <c r="Q16">
-        <v>578.56887460428</v>
+        <v>579.0249244525201</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09365485549094255</v>
+        <v>0.09362408907366249</v>
       </c>
       <c r="T16">
         <v>1.104482426643476</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>34.92314802288425</v>
+        <v>35.8951640712349</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08579972424088958</v>
+        <v>0.0856157074985042</v>
       </c>
       <c r="C17">
-        <v>2339.851408865374</v>
+        <v>2348.938739546275</v>
       </c>
       <c r="D17">
-        <v>2291.636408865374</v>
+        <v>2300.723739546275</v>
       </c>
       <c r="E17">
         <v>-1469.415</v>
@@ -2675,37 +2675,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M17">
-        <v>24.03972450000001</v>
+        <v>23.3887455</v>
       </c>
       <c r="N17">
-        <v>759.5336088333333</v>
+        <v>760.1845878333334</v>
       </c>
       <c r="O17">
-        <v>189.4276820430333</v>
+        <v>189.5900362056333</v>
       </c>
       <c r="P17">
-        <v>570.1059267903</v>
+        <v>570.5945516277</v>
       </c>
       <c r="Q17">
-        <v>577.3659267903</v>
+        <v>577.8545516276999</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09409273087163481</v>
+        <v>0.0940616829394167</v>
       </c>
       <c r="T17">
         <v>1.114588520540801</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>32.59493815469196</v>
+        <v>33.50215313315258</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08562342995956859</v>
+        <v>0.08542897319365865</v>
       </c>
       <c r="C18">
-        <v>2318.997250586946</v>
+        <v>2328.780899776351</v>
       </c>
       <c r="D18">
-        <v>2301.781250586946</v>
+        <v>2311.564899776351</v>
       </c>
       <c r="E18">
         <v>-1438.416</v>
@@ -2757,37 +2757,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M18">
-        <v>25.64237280000001</v>
+        <v>24.9479952</v>
       </c>
       <c r="N18">
-        <v>757.9309605333334</v>
+        <v>758.6253381333333</v>
       </c>
       <c r="O18">
-        <v>189.0279815570134</v>
+        <v>189.2011593304534</v>
       </c>
       <c r="P18">
-        <v>568.90297897632</v>
+        <v>569.42417880288</v>
       </c>
       <c r="Q18">
-        <v>576.16297897632</v>
+        <v>576.68417880288</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09454103185662928</v>
+        <v>0.09450969570673649</v>
       </c>
       <c r="T18">
         <v>1.124935235721397</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>30.55775452002371</v>
+        <v>31.40826856233054</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0854471356782476</v>
+        <v>0.08524223888881312</v>
       </c>
       <c r="C19">
-        <v>2298.233312070921</v>
+        <v>2308.725712217674</v>
       </c>
       <c r="D19">
-        <v>2312.016312070921</v>
+        <v>2322.508712217675</v>
       </c>
       <c r="E19">
         <v>-1407.417</v>
@@ -2839,37 +2839,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M19">
-        <v>27.24502110000001</v>
+        <v>26.50724490000001</v>
       </c>
       <c r="N19">
-        <v>756.3283122333333</v>
+        <v>757.0660884333333</v>
       </c>
       <c r="O19">
-        <v>188.6282810709934</v>
+        <v>188.8122824552733</v>
       </c>
       <c r="P19">
-        <v>567.70003116234</v>
+        <v>568.25380597806</v>
       </c>
       <c r="Q19">
-        <v>574.96003116234</v>
+        <v>575.51380597806</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09500013527499712</v>
+        <v>0.09496850396242545</v>
       </c>
       <c r="T19">
         <v>1.13553126934008</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>28.76023954825761</v>
+        <v>29.56072335278168</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08527084139692662</v>
+        <v>0.08505550458396757</v>
       </c>
       <c r="C20">
-        <v>2277.5608022017</v>
+        <v>2288.774641787552</v>
       </c>
       <c r="D20">
-        <v>2322.342802201701</v>
+        <v>2333.556641787553</v>
       </c>
       <c r="E20">
         <v>-1376.418</v>
@@ -2921,37 +2921,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M20">
-        <v>28.8476694</v>
+        <v>28.0664946</v>
       </c>
       <c r="N20">
-        <v>754.7256639333334</v>
+        <v>755.5068387333333</v>
       </c>
       <c r="O20">
-        <v>188.2285805849734</v>
+        <v>188.4234055800933</v>
       </c>
       <c r="P20">
-        <v>566.4970833483601</v>
+        <v>567.08343315324</v>
       </c>
       <c r="Q20">
-        <v>573.7570833483601</v>
+        <v>574.34343315324</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09547043633771538</v>
+        <v>0.09543850266337509</v>
       </c>
       <c r="T20">
         <v>1.14638574280312</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.16244846224331</v>
+        <v>27.91846094429382</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0850945471156056</v>
+        <v>0.08486877027912203</v>
       </c>
       <c r="C21">
-        <v>2256.980951558242</v>
+        <v>2268.929181410343</v>
       </c>
       <c r="D21">
-        <v>2332.761951558243</v>
+        <v>2344.710181410343</v>
       </c>
       <c r="E21">
         <v>-1345.419</v>
@@ -3003,37 +3003,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M21">
-        <v>30.45031770000001</v>
+        <v>29.6257443</v>
       </c>
       <c r="N21">
-        <v>753.1230156333334</v>
+        <v>753.9475890333334</v>
       </c>
       <c r="O21">
-        <v>187.8288800989533</v>
+        <v>188.0345287049134</v>
       </c>
       <c r="P21">
-        <v>565.2941355343801</v>
+        <v>565.9130603284201</v>
       </c>
       <c r="Q21">
-        <v>572.5541355343801</v>
+        <v>573.1730603284201</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09595234977235259</v>
+        <v>0.09592010627052103</v>
       </c>
       <c r="T21">
         <v>1.157508227956606</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.73284591159892</v>
+        <v>26.4490682630152</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.0849182528342846</v>
+        <v>0.0846820359742765</v>
       </c>
       <c r="C22">
-        <v>2236.495012902908</v>
+        <v>2249.190852689995</v>
       </c>
       <c r="D22">
-        <v>2343.275012902908</v>
+        <v>2355.970852689994</v>
       </c>
       <c r="E22">
         <v>-1314.42</v>
@@ -3085,37 +3085,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M22">
-        <v>32.05296600000001</v>
+        <v>31.18499400000001</v>
       </c>
       <c r="N22">
-        <v>751.5203673333334</v>
+        <v>752.3883393333334</v>
       </c>
       <c r="O22">
-        <v>187.4291796129334</v>
+        <v>187.6456518297334</v>
       </c>
       <c r="P22">
-        <v>564.0911877204001</v>
+        <v>564.7426875036001</v>
       </c>
       <c r="Q22">
-        <v>571.3511877204</v>
+        <v>572.0026875036001</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09644631104285575</v>
+        <v>0.09641374996784562</v>
       </c>
       <c r="T22">
         <v>1.168908775238929</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.44620361601897</v>
+        <v>25.12661484986443</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08474195855296363</v>
+        <v>0.08449530166943096</v>
       </c>
       <c r="C23">
-        <v>2216.104261683596</v>
+        <v>2229.561206602047</v>
       </c>
       <c r="D23">
-        <v>2353.883261683596</v>
+        <v>2367.340206602047</v>
       </c>
       <c r="E23">
         <v>-1283.421</v>
@@ -3167,37 +3167,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M23">
-        <v>33.6556143</v>
+        <v>32.7442437</v>
       </c>
       <c r="N23">
-        <v>749.9177190333334</v>
+        <v>750.8290896333334</v>
       </c>
       <c r="O23">
-        <v>187.0294791269133</v>
+        <v>187.2567749545534</v>
       </c>
       <c r="P23">
-        <v>562.88823990642</v>
+        <v>563.57231467878</v>
       </c>
       <c r="Q23">
-        <v>570.14823990642</v>
+        <v>570.83231467878</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09695277766197927</v>
+        <v>0.09691989097396324</v>
       </c>
       <c r="T23">
         <v>1.180597943971437</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.28209868192283</v>
+        <v>23.93010938082327</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08456566427164262</v>
+        <v>0.0843085673645854</v>
       </c>
       <c r="C24">
-        <v>2195.809996549589</v>
+        <v>2210.041824205773</v>
       </c>
       <c r="D24">
-        <v>2364.58799654959</v>
+        <v>2378.819824205773</v>
       </c>
       <c r="E24">
         <v>-1252.422</v>
@@ -3249,37 +3249,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M24">
-        <v>35.25826260000001</v>
+        <v>34.30349340000001</v>
       </c>
       <c r="N24">
-        <v>748.3150707333334</v>
+        <v>749.2698399333334</v>
       </c>
       <c r="O24">
-        <v>186.6297786408934</v>
+        <v>186.8678980793734</v>
       </c>
       <c r="P24">
-        <v>561.68529209244</v>
+        <v>562.40194185396</v>
       </c>
       <c r="Q24">
-        <v>568.94529209244</v>
+        <v>569.66194185396</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09747223060467003</v>
+        <v>0.09743900995459667</v>
       </c>
       <c r="T24">
         <v>1.192586834979138</v>
       </c>
       <c r="U24">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.22382146910816</v>
+        <v>22.84237713624039</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08438936999032162</v>
+        <v>0.08412183305973987</v>
       </c>
       <c r="C25">
-        <v>2175.61353988151</v>
+        <v>2190.63431737713</v>
       </c>
       <c r="D25">
-        <v>2375.39053988151</v>
+        <v>2390.41131737713</v>
       </c>
       <c r="E25">
         <v>-1221.423</v>
@@ -3331,37 +3331,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M25">
-        <v>36.86091090000001</v>
+        <v>35.86274310000001</v>
       </c>
       <c r="N25">
-        <v>746.7124224333334</v>
+        <v>747.7105902333334</v>
       </c>
       <c r="O25">
-        <v>186.2300781548734</v>
+        <v>186.4790212041933</v>
       </c>
       <c r="P25">
-        <v>560.48234427846</v>
+        <v>561.23156902914</v>
       </c>
       <c r="Q25">
-        <v>567.74234427846</v>
+        <v>568.49156902914</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09800517583158652</v>
+        <v>0.09797161254511672</v>
       </c>
       <c r="T25">
         <v>1.204887125753273</v>
       </c>
       <c r="U25">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.25756836175562</v>
+        <v>21.84923030422994</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08421307570900062</v>
+        <v>0.08393509875489433</v>
       </c>
       <c r="C26">
-        <v>2155.516238335899</v>
+        <v>2171.340329563261</v>
       </c>
       <c r="D26">
-        <v>2386.292238335899</v>
+        <v>2402.116329563261</v>
       </c>
       <c r="E26">
         <v>-1190.424</v>
@@ -3413,37 +3413,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M26">
-        <v>38.46355920000001</v>
+        <v>37.42199280000001</v>
       </c>
       <c r="N26">
-        <v>745.1097741333334</v>
+        <v>746.1513405333334</v>
       </c>
       <c r="O26">
-        <v>185.8303776688534</v>
+        <v>186.0901443290134</v>
       </c>
       <c r="P26">
-        <v>559.27939646448</v>
+        <v>560.06119620432</v>
       </c>
       <c r="Q26">
-        <v>566.53939646448</v>
+        <v>567.32119620432</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09855214593289555</v>
+        <v>0.09851823099328201</v>
       </c>
       <c r="T26">
         <v>1.217511108389885</v>
       </c>
       <c r="U26">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.37183634668248</v>
+        <v>20.93884570822036</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08403678142767962</v>
+        <v>0.0837483644500488</v>
       </c>
       <c r="C27">
-        <v>2135.519463404842</v>
+        <v>2152.161536559257</v>
       </c>
       <c r="D27">
-        <v>2397.294463404842</v>
+        <v>2413.936536559258</v>
       </c>
       <c r="E27">
         <v>-1159.425</v>
@@ -3495,37 +3495,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M27">
-        <v>40.06620750000001</v>
+        <v>38.98124250000001</v>
       </c>
       <c r="N27">
-        <v>743.5071258333334</v>
+        <v>744.5920908333334</v>
       </c>
       <c r="O27">
-        <v>185.4306771828333</v>
+        <v>185.7012674538333</v>
       </c>
       <c r="P27">
-        <v>558.0764486505</v>
+        <v>558.8908233795</v>
       </c>
       <c r="Q27">
-        <v>565.3364486505</v>
+        <v>566.1508233795</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09911370190357283</v>
+        <v>0.09907942593339839</v>
       </c>
       <c r="T27">
         <v>1.230471730563473</v>
       </c>
       <c r="U27">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.55696289281518</v>
+        <v>20.10129187989154</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08386048714635863</v>
+        <v>0.08356163014520325</v>
       </c>
       <c r="C28">
-        <v>2115.624611991158</v>
+        <v>2133.099647307981</v>
       </c>
       <c r="D28">
-        <v>2408.398611991158</v>
+        <v>2425.873647307982</v>
       </c>
       <c r="E28">
         <v>-1128.426</v>
@@ -3577,37 +3577,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M28">
-        <v>41.66885580000001</v>
+        <v>40.5404922</v>
       </c>
       <c r="N28">
-        <v>741.9044775333334</v>
+        <v>743.0328411333334</v>
       </c>
       <c r="O28">
-        <v>185.0309766968134</v>
+        <v>185.3123905786533</v>
       </c>
       <c r="P28">
-        <v>556.8735008365201</v>
+        <v>557.72045055468</v>
       </c>
       <c r="Q28">
-        <v>564.1335008365201</v>
+        <v>564.98045055468</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.0996904350626468</v>
+        <v>0.09965578830432871</v>
       </c>
       <c r="T28">
         <v>1.243782639822834</v>
       </c>
       <c r="U28">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.80477201232229</v>
+        <v>19.32816526912649</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08368419286503762</v>
+        <v>0.0833748958403577</v>
       </c>
       <c r="C29">
-        <v>2095.833106999647</v>
+        <v>2114.156404723725</v>
       </c>
       <c r="D29">
-        <v>2419.606106999646</v>
+        <v>2437.929404723725</v>
       </c>
       <c r="E29">
         <v>-1097.427</v>
@@ -3659,37 +3659,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M29">
-        <v>43.27150410000001</v>
+        <v>42.09974190000001</v>
       </c>
       <c r="N29">
-        <v>740.3018292333334</v>
+        <v>741.4735914333334</v>
       </c>
       <c r="O29">
-        <v>184.6312762107933</v>
+        <v>184.9235137034733</v>
       </c>
       <c r="P29">
-        <v>555.67055302254</v>
+        <v>556.55007772986</v>
       </c>
       <c r="Q29">
-        <v>562.93055302254</v>
+        <v>563.81007772986</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1002829691301885</v>
+        <v>0.1002479414251475</v>
       </c>
       <c r="T29">
         <v>1.257458231527657</v>
       </c>
       <c r="U29">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.10829897482887</v>
+        <v>18.61230729619588</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08350789858371663</v>
+        <v>0.08318816153551217</v>
       </c>
       <c r="C30">
-        <v>2076.146397944907</v>
+        <v>2095.333586540559</v>
       </c>
       <c r="D30">
-        <v>2430.918397944907</v>
+        <v>2450.105586540559</v>
       </c>
       <c r="E30">
         <v>-1066.428</v>
@@ -3741,37 +3741,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M30">
-        <v>44.87415240000001</v>
+        <v>43.65899160000001</v>
       </c>
       <c r="N30">
-        <v>738.6991809333333</v>
+        <v>739.9143417333333</v>
       </c>
       <c r="O30">
-        <v>184.2315757247733</v>
+        <v>184.5346368282933</v>
       </c>
       <c r="P30">
-        <v>554.4676052085599</v>
+        <v>555.3797049050399</v>
       </c>
       <c r="Q30">
-        <v>561.7276052085599</v>
+        <v>562.6397049050399</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1008919624773842</v>
+        <v>0.1008565432437669</v>
       </c>
       <c r="T30">
         <v>1.271513700779836</v>
       </c>
       <c r="U30">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.46157401144212</v>
+        <v>17.94758203561745</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08333160430239563</v>
+        <v>0.08300142723066663</v>
       </c>
       <c r="C31">
-        <v>2056.565961576314</v>
+        <v>2076.633006186236</v>
       </c>
       <c r="D31">
-        <v>2442.336961576314</v>
+        <v>2462.404006186236</v>
       </c>
       <c r="E31">
         <v>-1035.429</v>
@@ -3823,37 +3823,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M31">
-        <v>46.47680070000001</v>
+        <v>45.2182413</v>
       </c>
       <c r="N31">
-        <v>737.0965326333334</v>
+        <v>738.3550920333333</v>
       </c>
       <c r="O31">
-        <v>183.8318752387534</v>
+        <v>184.1457599531134</v>
       </c>
       <c r="P31">
-        <v>553.26465739458</v>
+        <v>554.20933208022</v>
       </c>
       <c r="Q31">
-        <v>560.52465739458</v>
+        <v>561.4693320802199</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1015181105667544</v>
+        <v>0.1014822887755868</v>
       </c>
       <c r="T31">
         <v>1.285965098743344</v>
       </c>
       <c r="U31">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.85945076966826</v>
+        <v>17.32869989645823</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08315531002107464</v>
+        <v>0.08281469292582108</v>
       </c>
       <c r="C32">
-        <v>2037.093302520663</v>
+        <v>2058.056513682531</v>
       </c>
       <c r="D32">
-        <v>2453.863302520664</v>
+        <v>2474.826513682531</v>
       </c>
       <c r="E32">
         <v>-1004.43</v>
@@ -3905,37 +3905,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M32">
-        <v>48.07944900000001</v>
+        <v>46.777491</v>
       </c>
       <c r="N32">
-        <v>735.4938843333334</v>
+        <v>736.7958423333333</v>
       </c>
       <c r="O32">
-        <v>183.4321747527334</v>
+        <v>183.7568830779333</v>
       </c>
       <c r="P32">
-        <v>552.0617095806001</v>
+        <v>553.0389592554</v>
       </c>
       <c r="Q32">
-        <v>559.3217095806001</v>
+        <v>560.2989592554</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1021621486015352</v>
+        <v>0.102125912751173</v>
       </c>
       <c r="T32">
         <v>1.300829393791524</v>
       </c>
       <c r="U32">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.29746907734598</v>
+        <v>16.75107656657629</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08297901573975364</v>
+        <v>0.08262795862097555</v>
       </c>
       <c r="C33">
-        <v>2017.729953943121</v>
+        <v>2039.605996572989</v>
       </c>
       <c r="D33">
-        <v>2465.498953943121</v>
+        <v>2487.374996572989</v>
       </c>
       <c r="E33">
         <v>-973.4310000000002</v>
@@ -3987,37 +3987,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M33">
-        <v>49.68209730000001</v>
+        <v>48.33674070000001</v>
       </c>
       <c r="N33">
-        <v>733.8912360333334</v>
+        <v>735.2365926333334</v>
       </c>
       <c r="O33">
-        <v>183.0324742667133</v>
+        <v>183.3680062027534</v>
       </c>
       <c r="P33">
-        <v>550.8587617666201</v>
+        <v>551.8685864305801</v>
       </c>
       <c r="Q33">
-        <v>558.1187617666201</v>
+        <v>559.1285864305801</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1028248544054401</v>
+        <v>0.1027881924941675</v>
       </c>
       <c r="T33">
         <v>1.316124537971535</v>
       </c>
       <c r="U33">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.77174426839934</v>
+        <v>16.21071925797705</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08280272145843263</v>
+        <v>0.08244122431612999</v>
       </c>
       <c r="C34">
-        <v>1998.477478227055</v>
+        <v>2021.283380879034</v>
       </c>
       <c r="D34">
-        <v>2477.245478227055</v>
+        <v>2500.051380879035</v>
       </c>
       <c r="E34">
         <v>-942.4320000000001</v>
@@ -4069,37 +4069,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M34">
-        <v>51.28474560000002</v>
+        <v>49.89599040000001</v>
       </c>
       <c r="N34">
-        <v>732.2885877333333</v>
+        <v>733.6773429333334</v>
       </c>
       <c r="O34">
-        <v>182.6327737806933</v>
+        <v>182.9791293275734</v>
       </c>
       <c r="P34">
-        <v>549.65581395264</v>
+        <v>550.6982136057601</v>
       </c>
       <c r="Q34">
-        <v>556.91581395264</v>
+        <v>557.9582136057601</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1035070515565186</v>
+        <v>0.1034699510531324</v>
       </c>
       <c r="T34">
         <v>1.331869539333311</v>
       </c>
       <c r="U34">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.27887726001186</v>
+        <v>15.70413428116527</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08262642717711163</v>
+        <v>0.08225449001128443</v>
       </c>
       <c r="C35">
-        <v>1979.337467673393</v>
+        <v>2003.09063208546</v>
       </c>
       <c r="D35">
-        <v>2489.104467673394</v>
+        <v>2512.857632085459</v>
       </c>
       <c r="E35">
         <v>-911.4330000000001</v>
@@ -4151,37 +4151,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M35">
-        <v>52.88739390000001</v>
+        <v>51.4552401</v>
       </c>
       <c r="N35">
-        <v>730.6859394333334</v>
+        <v>732.1180932333334</v>
       </c>
       <c r="O35">
-        <v>182.2330732946733</v>
+        <v>182.5902524523934</v>
       </c>
       <c r="P35">
-        <v>548.4528661386601</v>
+        <v>549.5278407809401</v>
       </c>
       <c r="Q35">
-        <v>555.71286613866</v>
+        <v>556.7878407809401</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1042096128016592</v>
+        <v>0.1041720606138574</v>
       </c>
       <c r="T35">
         <v>1.348084540735737</v>
       </c>
       <c r="U35">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.81588097940544</v>
+        <v>15.22825142416026</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08245013289579063</v>
+        <v>0.0820677557064389</v>
       </c>
       <c r="C36">
-        <v>1960.311545220181</v>
+        <v>1985.029756156367</v>
       </c>
       <c r="D36">
-        <v>2501.077545220181</v>
+        <v>2525.795756156367</v>
       </c>
       <c r="E36">
         <v>-880.434</v>
@@ -4233,37 +4233,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M36">
-        <v>54.49004220000002</v>
+        <v>53.01448980000001</v>
       </c>
       <c r="N36">
-        <v>729.0832911333333</v>
+        <v>730.5588435333334</v>
       </c>
       <c r="O36">
-        <v>181.8333728086533</v>
+        <v>182.2013755772134</v>
       </c>
       <c r="P36">
-        <v>547.24991832468</v>
+        <v>548.35746795612</v>
       </c>
       <c r="Q36">
-        <v>554.50991832468</v>
+        <v>555.61746795612</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.104933463781501</v>
+        <v>0.1048954462218771</v>
       </c>
       <c r="T36">
         <v>1.364790905817024</v>
       </c>
       <c r="U36">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.38011977412881</v>
+        <v>14.78036167639084</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08227383861446964</v>
+        <v>0.08188102140159337</v>
       </c>
       <c r="C37">
-        <v>1941.401365182983</v>
+        <v>1967.10280058266</v>
       </c>
       <c r="D37">
-        <v>2513.166365182984</v>
+        <v>2538.86780058266</v>
       </c>
       <c r="E37">
         <v>-849.4349999999999</v>
@@ -4315,37 +4315,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M37">
-        <v>56.09269050000002</v>
+        <v>54.57373950000002</v>
       </c>
       <c r="N37">
-        <v>727.4806428333334</v>
+        <v>728.9995938333334</v>
       </c>
       <c r="O37">
-        <v>181.4336723226334</v>
+        <v>181.8124987020334</v>
       </c>
       <c r="P37">
-        <v>546.0469705107</v>
+        <v>547.1870951313</v>
       </c>
       <c r="Q37">
-        <v>553.3069705107</v>
+        <v>554.4470951313</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1056795870991841</v>
+        <v>0.1056410898486052</v>
       </c>
       <c r="T37">
         <v>1.382011312900813</v>
       </c>
       <c r="U37">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.9692592091537</v>
+        <v>14.35806562849396</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08209754433314864</v>
+        <v>0.08169428709674782</v>
       </c>
       <c r="C38">
-        <v>1922.608614016887</v>
+        <v>1949.31185546222</v>
       </c>
       <c r="D38">
-        <v>2525.372614016887</v>
+        <v>2552.075855462221</v>
       </c>
       <c r="E38">
         <v>-818.4360000000001</v>
@@ -4397,37 +4397,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M38">
-        <v>57.69533880000001</v>
+        <v>56.1329892</v>
       </c>
       <c r="N38">
-        <v>725.8779945333333</v>
+        <v>727.4403441333334</v>
       </c>
       <c r="O38">
-        <v>181.0339718366133</v>
+        <v>181.4236218268533</v>
       </c>
       <c r="P38">
-        <v>544.84402269672</v>
+        <v>546.01672230648</v>
       </c>
       <c r="Q38">
-        <v>552.10402269672</v>
+        <v>553.27672230648</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1064490267705448</v>
+        <v>0.1064100348386685</v>
       </c>
       <c r="T38">
         <v>1.39976985770597</v>
       </c>
       <c r="U38">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.58122423112165</v>
+        <v>13.95923047214691</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08192125005182765</v>
+        <v>0.08150755279190229</v>
       </c>
       <c r="C39">
-        <v>1903.935011100792</v>
+        <v>1931.659054613983</v>
       </c>
       <c r="D39">
-        <v>2537.698011100792</v>
+        <v>2565.422054613983</v>
       </c>
       <c r="E39">
         <v>-787.4370000000001</v>
@@ -4479,37 +4479,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M39">
-        <v>59.29798710000001</v>
+        <v>57.69223890000001</v>
       </c>
       <c r="N39">
-        <v>724.2753462333334</v>
+        <v>725.8810944333334</v>
       </c>
       <c r="O39">
-        <v>180.6342713505934</v>
+        <v>181.0347449516734</v>
       </c>
       <c r="P39">
-        <v>543.64107488274</v>
+        <v>544.84634948166</v>
       </c>
       <c r="Q39">
-        <v>550.90107488274</v>
+        <v>552.10634948166</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1072428930981391</v>
+        <v>0.1072033907807973</v>
       </c>
       <c r="T39">
         <v>1.418092165838275</v>
       </c>
       <c r="U39">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.21416411676701</v>
+        <v>13.58195397289969</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08174495577050665</v>
+        <v>0.08132081848705673</v>
       </c>
       <c r="C40">
-        <v>1885.38230954481</v>
+        <v>1914.146576727159</v>
       </c>
       <c r="D40">
-        <v>2550.14430954481</v>
+        <v>2578.908576727159</v>
       </c>
       <c r="E40">
         <v>-756.4380000000001</v>
@@ -4561,37 +4561,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M40">
-        <v>60.90063540000001</v>
+        <v>59.25148860000001</v>
       </c>
       <c r="N40">
-        <v>722.6726979333333</v>
+        <v>724.3218447333334</v>
       </c>
       <c r="O40">
-        <v>180.2345708645733</v>
+        <v>180.6458680764933</v>
       </c>
       <c r="P40">
-        <v>542.43812706876</v>
+        <v>543.67597665684</v>
       </c>
       <c r="Q40">
-        <v>549.69812706876</v>
+        <v>550.93597665684</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1080623680169462</v>
+        <v>0.1080223388500915</v>
       </c>
       <c r="T40">
         <v>1.437005516168396</v>
       </c>
       <c r="U40">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.86642295579946</v>
+        <v>13.2245341315076</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08189066888918566</v>
+        <v>0.08113408418221121</v>
       </c>
       <c r="C41">
-        <v>1844.087310832062</v>
+        <v>1896.776646546881</v>
       </c>
       <c r="D41">
-        <v>2539.848310832062</v>
+        <v>2592.537646546881</v>
       </c>
       <c r="E41">
         <v>-725.4390000000001</v>
@@ -4643,45 +4643,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M41">
-        <v>63.83314080000001</v>
+        <v>60.81073830000001</v>
       </c>
       <c r="N41">
-        <v>719.7401925333334</v>
+        <v>722.7625950333334</v>
       </c>
       <c r="O41">
-        <v>179.5032040178133</v>
+        <v>180.2569912013134</v>
       </c>
       <c r="P41">
-        <v>540.23698851552</v>
+        <v>542.50560383202</v>
       </c>
       <c r="Q41">
-        <v>547.49698851552</v>
+        <v>549.76560383202</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1089087109658781</v>
+        <v>0.1088681376757561</v>
       </c>
       <c r="T41">
         <v>1.456538976345406</v>
       </c>
       <c r="U41">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.03963168</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>12.27533728582149</v>
+        <v>12.88544351275099</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08172263120786466</v>
+        <v>0.08139770987736568</v>
       </c>
       <c r="C42">
-        <v>1824.96912820843</v>
+        <v>1846.578109789051</v>
       </c>
       <c r="D42">
-        <v>2551.72912820843</v>
+        <v>2573.338109789051</v>
       </c>
       <c r="E42">
         <v>-694.4400000000001</v>
@@ -4725,37 +4725,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M42">
-        <v>65.46988800000001</v>
+        <v>64.22992800000002</v>
       </c>
       <c r="N42">
-        <v>718.1034453333334</v>
+        <v>719.3434053333334</v>
       </c>
       <c r="O42">
-        <v>179.0949992661334</v>
+        <v>179.4042452901334</v>
       </c>
       <c r="P42">
-        <v>539.0084460672001</v>
+        <v>539.9391600432</v>
       </c>
       <c r="Q42">
-        <v>546.2684460672001</v>
+        <v>547.1991600432</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1097832653464411</v>
+        <v>0.1097421297956095</v>
       </c>
       <c r="T42">
         <v>1.47672355186165</v>
       </c>
       <c r="U42">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V42">
         <v>0.2494</v>
       </c>
       <c r="W42">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.96845385367596</v>
+        <v>12.1995050863724</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08155459352654366</v>
+        <v>0.08122223457252013</v>
       </c>
       <c r="C43">
-        <v>1805.962619347928</v>
+        <v>1828.326958555097</v>
       </c>
       <c r="D43">
-        <v>2563.721619347928</v>
+        <v>2586.085958555097</v>
       </c>
       <c r="E43">
         <v>-663.441</v>
@@ -4807,37 +4807,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M43">
-        <v>67.10663520000001</v>
+        <v>65.83567620000001</v>
       </c>
       <c r="N43">
-        <v>716.4666981333334</v>
+        <v>717.7376571333334</v>
       </c>
       <c r="O43">
-        <v>178.6867945144533</v>
+        <v>179.0037716890534</v>
       </c>
       <c r="P43">
-        <v>537.77990361888</v>
+        <v>538.7338854442801</v>
       </c>
       <c r="Q43">
-        <v>545.03990361888</v>
+        <v>545.9938854442801</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1106874656382096</v>
+        <v>0.1106457487669833</v>
       </c>
       <c r="T43">
         <v>1.49759235027675</v>
       </c>
       <c r="U43">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.67654034504971</v>
+        <v>11.90195618182674</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08138655584522267</v>
+        <v>0.0810467592676746</v>
       </c>
       <c r="C44">
-        <v>1787.06936620192</v>
+        <v>1810.202737154967</v>
       </c>
       <c r="D44">
-        <v>2575.82736620192</v>
+        <v>2598.960737154967</v>
       </c>
       <c r="E44">
         <v>-632.4420000000002</v>
@@ -4889,37 +4889,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M44">
-        <v>68.7433824</v>
+        <v>67.4414244</v>
       </c>
       <c r="N44">
-        <v>714.8299509333334</v>
+        <v>716.1319089333334</v>
       </c>
       <c r="O44">
-        <v>178.2785897627734</v>
+        <v>178.6032980879734</v>
       </c>
       <c r="P44">
-        <v>536.5513611705601</v>
+        <v>537.52861084536</v>
       </c>
       <c r="Q44">
-        <v>543.8113611705601</v>
+        <v>544.78861084536</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1116228452503839</v>
+        <v>0.111580527013232</v>
       </c>
       <c r="T44">
         <v>1.519180762430301</v>
       </c>
       <c r="U44">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.39852747969139</v>
+        <v>11.61857627273563</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08121851816390167</v>
+        <v>0.08087128396282905</v>
       </c>
       <c r="C45">
-        <v>1768.290980743069</v>
+        <v>1792.207350826973</v>
       </c>
       <c r="D45">
-        <v>2588.047980743069</v>
+        <v>2611.964350826973</v>
       </c>
       <c r="E45">
         <v>-601.4430000000002</v>
@@ -4971,37 +4971,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M45">
-        <v>70.3801296</v>
+        <v>69.04717260000001</v>
       </c>
       <c r="N45">
-        <v>713.1932037333333</v>
+        <v>714.5261607333334</v>
       </c>
       <c r="O45">
-        <v>177.8703850110933</v>
+        <v>178.2028244868934</v>
       </c>
       <c r="P45">
-        <v>535.3228187222401</v>
+        <v>536.32333624644</v>
       </c>
       <c r="Q45">
-        <v>542.5828187222401</v>
+        <v>543.58333624644</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1125910451998275</v>
+        <v>0.1125481044961913</v>
       </c>
       <c r="T45">
         <v>1.541526662729591</v>
       </c>
       <c r="U45">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.13344544527996</v>
+        <v>11.34837682453247</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08105048048258069</v>
+        <v>0.08069580865798351</v>
       </c>
       <c r="C46">
-        <v>1749.629105680881</v>
+        <v>1774.342743131769</v>
       </c>
       <c r="D46">
-        <v>2600.385105680882</v>
+        <v>2625.09874313177</v>
       </c>
       <c r="E46">
         <v>-570.444</v>
@@ -5053,37 +5053,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M46">
-        <v>72.01687680000002</v>
+        <v>70.65292080000002</v>
       </c>
       <c r="N46">
-        <v>711.5564565333334</v>
+        <v>712.9204125333333</v>
       </c>
       <c r="O46">
-        <v>177.4621802594133</v>
+        <v>177.8023508858133</v>
       </c>
       <c r="P46">
-        <v>534.0942762739201</v>
+        <v>535.11806164752</v>
       </c>
       <c r="Q46">
-        <v>541.35427627392</v>
+        <v>542.37806164752</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1135938237188941</v>
+        <v>0.1135502383178277</v>
       </c>
       <c r="T46">
         <v>1.564670630896713</v>
       </c>
       <c r="U46">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.88041259425087</v>
+        <v>11.09045916942946</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08088244280125967</v>
+        <v>0.08052033335313796</v>
       </c>
       <c r="C47">
-        <v>1731.085415197831</v>
+        <v>1756.610896920748</v>
       </c>
       <c r="D47">
-        <v>2612.840415197831</v>
+        <v>2638.365896920749</v>
       </c>
       <c r="E47">
         <v>-539.4449999999999</v>
@@ -5135,37 +5135,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M47">
-        <v>73.65362400000002</v>
+        <v>72.25866900000001</v>
       </c>
       <c r="N47">
-        <v>709.9197093333333</v>
+        <v>711.3146643333333</v>
       </c>
       <c r="O47">
-        <v>177.0539755077334</v>
+        <v>177.4018772847333</v>
       </c>
       <c r="P47">
-        <v>532.8657338256</v>
+        <v>533.9127870486</v>
       </c>
       <c r="Q47">
-        <v>540.1257338256</v>
+        <v>541.1727870486</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1146330669113812</v>
+        <v>0.1145888133693417</v>
       </c>
       <c r="T47">
         <v>1.588656197906276</v>
       </c>
       <c r="U47">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.63862564771196</v>
+        <v>10.84400452121991</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08071440511993869</v>
+        <v>0.08034485804829242</v>
       </c>
       <c r="C48">
-        <v>1712.661615706713</v>
+        <v>1739.013835333957</v>
       </c>
       <c r="D48">
-        <v>2625.415615706713</v>
+        <v>2651.767835333958</v>
       </c>
       <c r="E48">
         <v>-508.4459999999999</v>
@@ -5217,37 +5217,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M48">
-        <v>75.29037120000002</v>
+        <v>73.86441720000002</v>
       </c>
       <c r="N48">
-        <v>708.2829621333334</v>
+        <v>709.7089161333333</v>
       </c>
       <c r="O48">
-        <v>176.6457707560534</v>
+        <v>177.0014036836533</v>
       </c>
       <c r="P48">
-        <v>531.63719137728</v>
+        <v>532.7075124496801</v>
       </c>
       <c r="Q48">
-        <v>538.89719137728</v>
+        <v>539.96751244968</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.115710800592479</v>
+        <v>0.1156658541635045</v>
       </c>
       <c r="T48">
         <v>1.613530119249526</v>
       </c>
       <c r="U48">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.40735117710953</v>
+        <v>10.60826529249774</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08054636743861769</v>
+        <v>0.08016938274344687</v>
       </c>
       <c r="C49">
-        <v>1694.359446630022</v>
+        <v>1721.553622828579</v>
       </c>
       <c r="D49">
-        <v>2638.112446630022</v>
+        <v>2665.306622828579</v>
       </c>
       <c r="E49">
         <v>-477.4469999999999</v>
@@ -5299,37 +5299,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M49">
-        <v>76.92711840000003</v>
+        <v>75.47016540000003</v>
       </c>
       <c r="N49">
-        <v>706.6462149333333</v>
+        <v>708.1031679333333</v>
       </c>
       <c r="O49">
-        <v>176.2375660043733</v>
+        <v>176.6009300825733</v>
       </c>
       <c r="P49">
-        <v>530.40864892896</v>
+        <v>531.50223785076</v>
       </c>
       <c r="Q49">
-        <v>537.66864892896</v>
+        <v>538.76223785076</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.11682920346909</v>
+        <v>0.1167835380065035</v>
       </c>
       <c r="T49">
         <v>1.639342679134031</v>
       </c>
       <c r="U49">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.18591817334124</v>
+        <v>10.38255752031694</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08037832975729668</v>
+        <v>0.07999390743860132</v>
       </c>
       <c r="C50">
-        <v>1676.180681202001</v>
+        <v>1704.232366239083</v>
       </c>
       <c r="D50">
-        <v>2650.932681202001</v>
+        <v>2678.984366239083</v>
       </c>
       <c r="E50">
         <v>-446.4480000000001</v>
@@ -5381,37 +5381,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M50">
-        <v>78.56386560000001</v>
+        <v>77.07591360000001</v>
       </c>
       <c r="N50">
-        <v>705.0094677333334</v>
+        <v>706.4974197333333</v>
       </c>
       <c r="O50">
-        <v>175.8293612526934</v>
+        <v>176.2004564814933</v>
       </c>
       <c r="P50">
-        <v>529.18010648064</v>
+        <v>530.29696325184</v>
       </c>
       <c r="Q50">
-        <v>536.44010648064</v>
+        <v>537.55696325184</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1179906218409552</v>
+        <v>0.1179442096896179</v>
       </c>
       <c r="T50">
         <v>1.666148029783324</v>
       </c>
       <c r="U50">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.973711544729964</v>
+        <v>10.16625423864367</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08101943887597568</v>
+        <v>0.07981843213375581</v>
       </c>
       <c r="C51">
-        <v>1596.926025542419</v>
+        <v>1687.052215870183</v>
       </c>
       <c r="D51">
-        <v>2602.67702554242</v>
+        <v>2692.803215870184</v>
       </c>
       <c r="E51">
         <v>-415.4490000000001</v>
@@ -5463,45 +5463,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M51">
-        <v>83.54230500000001</v>
+        <v>78.68166180000001</v>
       </c>
       <c r="N51">
-        <v>700.0310283333333</v>
+        <v>704.8916715333334</v>
       </c>
       <c r="O51">
-        <v>174.5877384663333</v>
+        <v>175.7999828804134</v>
       </c>
       <c r="P51">
-        <v>525.443289867</v>
+        <v>529.09168865292</v>
       </c>
       <c r="Q51">
-        <v>532.703289867</v>
+        <v>536.35168865292</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1191975860313249</v>
+        <v>0.1191503979093251</v>
       </c>
       <c r="T51">
         <v>1.694004570654159</v>
       </c>
       <c r="U51">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.04128299999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y51">
-        <v>9.379359754717484</v>
+        <v>9.958779662344819</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08086791439465468</v>
+        <v>0.08028096682891026</v>
       </c>
       <c r="C52">
-        <v>1577.172897820512</v>
+        <v>1619.931406387767</v>
       </c>
       <c r="D52">
-        <v>2613.922897820513</v>
+        <v>2656.681406387767</v>
       </c>
       <c r="E52">
         <v>-384.45</v>
@@ -5545,37 +5545,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M52">
-        <v>85.24725000000002</v>
+        <v>82.92232500000001</v>
       </c>
       <c r="N52">
-        <v>698.3260833333334</v>
+        <v>700.6510083333334</v>
       </c>
       <c r="O52">
-        <v>174.1625251833333</v>
+        <v>174.7423614783334</v>
       </c>
       <c r="P52">
-        <v>524.16355815</v>
+        <v>525.908646855</v>
       </c>
       <c r="Q52">
-        <v>531.42355815</v>
+        <v>533.168646855</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1204528287893094</v>
+        <v>0.1204048336578205</v>
       </c>
       <c r="T52">
         <v>1.722975373159827</v>
       </c>
       <c r="U52">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.191772559623134</v>
+        <v>9.449485808958363</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08071638991333369</v>
+        <v>0.08011825172406473</v>
       </c>
       <c r="C53">
-        <v>1557.517376120773</v>
+        <v>1601.528683058772</v>
       </c>
       <c r="D53">
-        <v>2625.266376120773</v>
+        <v>2669.277683058773</v>
       </c>
       <c r="E53">
         <v>-353.451</v>
@@ -5627,37 +5627,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M53">
-        <v>86.95219500000002</v>
+        <v>84.58077150000001</v>
       </c>
       <c r="N53">
-        <v>696.6211383333334</v>
+        <v>698.9925618333334</v>
       </c>
       <c r="O53">
-        <v>173.7373119003334</v>
+        <v>174.3287449212334</v>
       </c>
       <c r="P53">
-        <v>522.8838264330001</v>
+        <v>524.6638169121001</v>
       </c>
       <c r="Q53">
-        <v>530.1438264330001</v>
+        <v>531.9238169121001</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.121759305945579</v>
+        <v>0.1217104708654382</v>
       </c>
       <c r="T53">
         <v>1.75312865740042</v>
       </c>
       <c r="U53">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.01154172512072</v>
+        <v>9.264201773488592</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08056486543201269</v>
+        <v>0.07995553661921917</v>
       </c>
       <c r="C54">
-        <v>1537.960736706033</v>
+        <v>1583.245975673435</v>
       </c>
       <c r="D54">
-        <v>2636.708736706034</v>
+        <v>2681.993975673436</v>
       </c>
       <c r="E54">
         <v>-322.452</v>
@@ -5709,37 +5709,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M54">
-        <v>88.65714000000001</v>
+        <v>86.23921800000002</v>
       </c>
       <c r="N54">
-        <v>694.9161933333334</v>
+        <v>697.3341153333333</v>
       </c>
       <c r="O54">
-        <v>173.3120986173333</v>
+        <v>173.9151283641334</v>
       </c>
       <c r="P54">
-        <v>521.604094716</v>
+        <v>523.4189869692</v>
       </c>
       <c r="Q54">
-        <v>528.864094716</v>
+        <v>530.6789869692</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1231202196500265</v>
+        <v>0.1230705096233733</v>
       </c>
       <c r="T54">
         <v>1.784538328484371</v>
       </c>
       <c r="U54">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.838242845791475</v>
+        <v>9.086044047075347</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08041334095069171</v>
+        <v>0.07979282151437364</v>
       </c>
       <c r="C55">
-        <v>1518.504278187164</v>
+        <v>1565.08500769035</v>
       </c>
       <c r="D55">
-        <v>2648.251278187165</v>
+        <v>2694.83200769035</v>
       </c>
       <c r="E55">
         <v>-291.453</v>
@@ -5791,37 +5791,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M55">
-        <v>90.36208500000002</v>
+        <v>87.89766450000002</v>
       </c>
       <c r="N55">
-        <v>693.2112483333334</v>
+        <v>695.6756688333334</v>
       </c>
       <c r="O55">
-        <v>172.8868853343334</v>
+        <v>173.5015118070334</v>
       </c>
       <c r="P55">
-        <v>520.3243629990001</v>
+        <v>522.1741570263</v>
       </c>
       <c r="Q55">
-        <v>527.5843629990001</v>
+        <v>529.4341570263</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1245390445759398</v>
+        <v>0.1244884223710077</v>
       </c>
       <c r="T55">
         <v>1.817284581316576</v>
       </c>
       <c r="U55">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.671483546814278</v>
+        <v>8.914609253734305</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08026181646937069</v>
+        <v>0.07963010640952808</v>
       </c>
       <c r="C56">
-        <v>1499.149322014386</v>
+        <v>1547.047535725892</v>
       </c>
       <c r="D56">
-        <v>2659.895322014386</v>
+        <v>2707.793535725893</v>
       </c>
       <c r="E56">
         <v>-260.454</v>
@@ -5873,37 +5873,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M56">
-        <v>92.06703000000002</v>
+        <v>89.55611100000002</v>
       </c>
       <c r="N56">
-        <v>691.5063033333333</v>
+        <v>694.0172223333334</v>
       </c>
       <c r="O56">
-        <v>172.4616720513334</v>
+        <v>173.0878952499334</v>
       </c>
       <c r="P56">
-        <v>519.044631282</v>
+        <v>520.9293270834</v>
       </c>
       <c r="Q56">
-        <v>526.3046312819999</v>
+        <v>528.1893270834</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1260195575421102</v>
+        <v>0.1259679834989741</v>
       </c>
       <c r="T56">
         <v>1.85145458427192</v>
       </c>
       <c r="U56">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V56">
         <v>0.2494</v>
       </c>
       <c r="W56">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.510900518169569</v>
+        <v>8.74952389718367</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.0801102919880497</v>
+        <v>0.07946739130468256</v>
       </c>
       <c r="C57">
-        <v>1479.897212981585</v>
+        <v>1529.135350355466</v>
       </c>
       <c r="D57">
-        <v>2671.642212981585</v>
+        <v>2720.880350355466</v>
       </c>
       <c r="E57">
         <v>-229.4549999999999</v>
@@ -5955,37 +5955,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M57">
-        <v>93.77197500000003</v>
+        <v>91.21455750000001</v>
       </c>
       <c r="N57">
-        <v>689.8013583333334</v>
+        <v>692.3587758333333</v>
       </c>
       <c r="O57">
-        <v>172.0364587683333</v>
+        <v>172.6742786928333</v>
       </c>
       <c r="P57">
-        <v>517.7648995650001</v>
+        <v>519.6844971405</v>
       </c>
       <c r="Q57">
-        <v>525.0248995650001</v>
+        <v>526.9444971404999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1275658710845549</v>
+        <v>0.1275133028992946</v>
       </c>
       <c r="T57">
         <v>1.887143254025279</v>
       </c>
       <c r="U57">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.356156872384666</v>
+        <v>8.590441644507603</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0799587675067287</v>
+        <v>0.079304676199837</v>
       </c>
       <c r="C58">
-        <v>1460.749319744074</v>
+        <v>1511.350276938121</v>
       </c>
       <c r="D58">
-        <v>2683.493319744075</v>
+        <v>2734.094276938122</v>
       </c>
       <c r="E58">
         <v>-198.4559999999999</v>
@@ -6037,37 +6037,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M58">
-        <v>95.47692000000002</v>
+        <v>92.87300400000002</v>
       </c>
       <c r="N58">
-        <v>688.0964133333333</v>
+        <v>690.7003293333333</v>
       </c>
       <c r="O58">
-        <v>171.6112454853333</v>
+        <v>172.2606621357334</v>
       </c>
       <c r="P58">
-        <v>516.4851678479999</v>
+        <v>518.4396671976</v>
       </c>
       <c r="Q58">
-        <v>523.7451678479999</v>
+        <v>525.6996671976</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1291824716062016</v>
+        <v>0.1291288640905387</v>
       </c>
       <c r="T58">
         <v>1.924454136040154</v>
       </c>
       <c r="U58">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V58">
         <v>0.2494</v>
       </c>
       <c r="W58">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.206939785377799</v>
+        <v>8.437040900855681</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0798072430254077</v>
+        <v>0.07914196109499147</v>
       </c>
       <c r="C59">
-        <v>1441.707035350182</v>
+        <v>1493.694176465299</v>
       </c>
       <c r="D59">
-        <v>2695.450035350182</v>
+        <v>2747.4371764653</v>
       </c>
       <c r="E59">
         <v>-167.4569999999999</v>
@@ -6119,37 +6119,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M59">
-        <v>97.18186500000003</v>
+        <v>94.53145050000002</v>
       </c>
       <c r="N59">
-        <v>686.3914683333334</v>
+        <v>689.0418828333334</v>
       </c>
       <c r="O59">
-        <v>171.1860322023333</v>
+        <v>171.8470455786334</v>
       </c>
       <c r="P59">
-        <v>515.2054361310001</v>
+        <v>517.1948372547</v>
       </c>
       <c r="Q59">
-        <v>522.465436131</v>
+        <v>524.4548372547</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1308742628497854</v>
+        <v>0.1308195676627709</v>
       </c>
       <c r="T59">
         <v>1.963500407916186</v>
       </c>
       <c r="U59">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.062958385634328</v>
+        <v>8.28902263943716</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07965571854408671</v>
+        <v>0.07897924599014593</v>
       </c>
       <c r="C60">
-        <v>1422.771777787114</v>
+        <v>1476.168946434571</v>
       </c>
       <c r="D60">
-        <v>2707.513777787114</v>
+        <v>2760.910946434571</v>
       </c>
       <c r="E60">
         <v>-136.4580000000001</v>
@@ -6201,37 +6201,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M60">
-        <v>98.88681000000001</v>
+        <v>96.18989700000002</v>
       </c>
       <c r="N60">
-        <v>684.6865233333334</v>
+        <v>687.3834363333334</v>
       </c>
       <c r="O60">
-        <v>170.7608189193334</v>
+        <v>171.4334290215334</v>
       </c>
       <c r="P60">
-        <v>513.9257044140001</v>
+        <v>515.9500073118001</v>
       </c>
       <c r="Q60">
-        <v>521.185704414</v>
+        <v>523.2100073118</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1326466155811588</v>
+        <v>0.1325907809289189</v>
       </c>
       <c r="T60">
         <v>2.004406026072029</v>
       </c>
       <c r="U60">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.923941861744082</v>
+        <v>8.14610845599859</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07950419406276572</v>
+        <v>0.07881653088530038</v>
       </c>
       <c r="C61">
-        <v>1403.944990541544</v>
+        <v>1458.77652174919</v>
       </c>
       <c r="D61">
-        <v>2719.685990541544</v>
+        <v>2774.517521749191</v>
       </c>
       <c r="E61">
         <v>-105.4590000000001</v>
@@ -6283,37 +6283,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M61">
-        <v>100.591755</v>
+        <v>97.84834350000001</v>
       </c>
       <c r="N61">
-        <v>682.9815783333333</v>
+        <v>685.7249898333333</v>
       </c>
       <c r="O61">
-        <v>170.3356056363334</v>
+        <v>171.0198124644333</v>
       </c>
       <c r="P61">
-        <v>512.6459726969999</v>
+        <v>514.7051773689</v>
       </c>
       <c r="Q61">
-        <v>519.9059726969999</v>
+        <v>521.9651773689</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.134505424543331</v>
+        <v>0.1344483948421961</v>
       </c>
       <c r="T61">
         <v>2.047307040235475</v>
       </c>
       <c r="U61">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.789637762392487</v>
+        <v>8.008038821151153</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08002820958144471</v>
+        <v>0.07865381578045484</v>
       </c>
       <c r="C62">
-        <v>1331.309057660597</v>
+        <v>1441.518875644399</v>
       </c>
       <c r="D62">
-        <v>2678.049057660597</v>
+        <v>2788.258875644399</v>
       </c>
       <c r="E62">
         <v>-74.46000000000004</v>
@@ -6365,45 +6365,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M62">
-        <v>105.08661</v>
+        <v>99.50679000000001</v>
       </c>
       <c r="N62">
-        <v>678.4867233333333</v>
+        <v>684.0665433333334</v>
       </c>
       <c r="O62">
-        <v>169.2145887993333</v>
+        <v>170.6061959073334</v>
       </c>
       <c r="P62">
-        <v>509.272134534</v>
+        <v>513.460347426</v>
       </c>
       <c r="Q62">
-        <v>516.532134534</v>
+        <v>520.720347426</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1364571739536118</v>
+        <v>0.1363988894511371</v>
       </c>
       <c r="T62">
         <v>2.092353105107092</v>
       </c>
       <c r="U62">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.0424089</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>7.456452666360949</v>
+        <v>7.874571507465302</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07988794410012373</v>
+        <v>0.0784911006756093</v>
       </c>
       <c r="C63">
-        <v>1311.329726050414</v>
+        <v>1424.39802064138</v>
       </c>
       <c r="D63">
-        <v>2689.068726050414</v>
+        <v>2802.13702064138</v>
       </c>
       <c r="E63">
         <v>-43.46100000000001</v>
@@ -6447,45 +6447,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M63">
-        <v>106.8380535</v>
+        <v>101.1652365</v>
       </c>
       <c r="N63">
-        <v>676.7352798333334</v>
+        <v>682.4080968333334</v>
       </c>
       <c r="O63">
-        <v>168.7777787904334</v>
+        <v>170.1925793502334</v>
       </c>
       <c r="P63">
-        <v>507.9575010429</v>
+        <v>512.2155174831</v>
       </c>
       <c r="Q63">
-        <v>515.2175010429</v>
+        <v>519.4755174831</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1385090130772403</v>
+        <v>0.1384494094246392</v>
       </c>
       <c r="T63">
         <v>2.139709224587512</v>
       </c>
       <c r="U63">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.0424089</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>7.334215737404214</v>
+        <v>7.745480171277347</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07974767861880273</v>
+        <v>0.07832838557076376</v>
       </c>
       <c r="C64">
-        <v>1291.441456872397</v>
+        <v>1407.416009529849</v>
       </c>
       <c r="D64">
-        <v>2700.179456872397</v>
+        <v>2816.154009529849</v>
       </c>
       <c r="E64">
         <v>-12.46199999999999</v>
@@ -6529,45 +6529,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M64">
-        <v>108.589497</v>
+        <v>102.823683</v>
       </c>
       <c r="N64">
-        <v>674.9838363333333</v>
+        <v>680.7496503333334</v>
       </c>
       <c r="O64">
-        <v>168.3409687815333</v>
+        <v>169.7789627931334</v>
       </c>
       <c r="P64">
-        <v>506.6428675518</v>
+        <v>510.9706875402001</v>
       </c>
       <c r="Q64">
-        <v>513.9028675518</v>
+        <v>518.2306875402001</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1406688437336914</v>
+        <v>0.1406078515020099</v>
       </c>
       <c r="T64">
         <v>2.189557771409005</v>
       </c>
       <c r="U64">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.0424089</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>7.215921935188016</v>
+        <v>7.620553071740615</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07960741313748174</v>
+        <v>0.07854397286591822</v>
       </c>
       <c r="C65">
-        <v>1271.645383568712</v>
+        <v>1357.875367434706</v>
       </c>
       <c r="D65">
-        <v>2711.382383568713</v>
+        <v>2797.612367434706</v>
       </c>
       <c r="E65">
         <v>18.53700000000003</v>
@@ -6611,37 +6611,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M65">
-        <v>110.3409405</v>
+        <v>106.0444791</v>
       </c>
       <c r="N65">
-        <v>673.2323928333334</v>
+        <v>677.5288542333334</v>
       </c>
       <c r="O65">
-        <v>167.9041587726334</v>
+        <v>168.9756962457934</v>
       </c>
       <c r="P65">
-        <v>505.3282340607</v>
+        <v>508.55315798754</v>
       </c>
       <c r="Q65">
-        <v>512.5882340607001</v>
+        <v>515.8131579875401</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1429454219931939</v>
+        <v>0.1428829661241033</v>
       </c>
       <c r="T65">
         <v>2.242100834274903</v>
       </c>
       <c r="U65">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V65">
         <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.101383491772333</v>
+        <v>7.38910068665077</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.07946714765616072</v>
+        <v>0.07838726256107267</v>
       </c>
       <c r="C66">
-        <v>1251.942658470307</v>
+        <v>1340.329927276337</v>
       </c>
       <c r="D66">
-        <v>2722.678658470308</v>
+        <v>2811.065927276337</v>
       </c>
       <c r="E66">
         <v>49.53600000000006</v>
@@ -6693,37 +6693,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M66">
-        <v>112.092384</v>
+        <v>107.7277248</v>
       </c>
       <c r="N66">
-        <v>671.4809493333333</v>
+        <v>675.8456085333333</v>
       </c>
       <c r="O66">
-        <v>167.4673487637334</v>
+        <v>168.5558947682133</v>
       </c>
       <c r="P66">
-        <v>504.0136005696</v>
+        <v>507.28971376512</v>
       </c>
       <c r="Q66">
-        <v>511.2736005696</v>
+        <v>514.54971376512</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1453484768226687</v>
+        <v>0.1452844760029797</v>
       </c>
       <c r="T66">
         <v>2.297562956188907</v>
       </c>
       <c r="U66">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V66">
         <v>0.2494</v>
       </c>
       <c r="W66">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.99042437471339</v>
+        <v>7.273645988421852</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.07932688217483973</v>
+        <v>0.07823055225622713</v>
       </c>
       <c r="C67">
-        <v>1232.334453192023</v>
+        <v>1322.914507195788</v>
       </c>
       <c r="D67">
-        <v>2734.069453192023</v>
+        <v>2824.649507195788</v>
       </c>
       <c r="E67">
         <v>80.53500000000008</v>
@@ -6775,37 +6775,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M67">
-        <v>113.8438275</v>
+        <v>109.4109705</v>
       </c>
       <c r="N67">
-        <v>669.7295058333334</v>
+        <v>674.1623628333334</v>
       </c>
       <c r="O67">
-        <v>167.0305387548333</v>
+        <v>168.1360932906334</v>
       </c>
       <c r="P67">
-        <v>502.6989670785001</v>
+        <v>506.0262695427</v>
       </c>
       <c r="Q67">
-        <v>509.9589670785001</v>
+        <v>513.2862695427001</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1478888490709707</v>
+        <v>0.1478232150177918</v>
       </c>
       <c r="T67">
         <v>2.356194342212282</v>
       </c>
       <c r="U67">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V67">
         <v>0.2494</v>
       </c>
       <c r="W67">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.882879384333184</v>
+        <v>7.161743742446132</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07918661669351874</v>
+        <v>0.07807384195138159</v>
       </c>
       <c r="C68">
-        <v>1212.821959037685</v>
+        <v>1305.631001186906</v>
       </c>
       <c r="D68">
-        <v>2745.555959037685</v>
+        <v>2838.365001186906</v>
       </c>
       <c r="E68">
         <v>111.5340000000001</v>
@@ -6857,37 +6857,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M68">
-        <v>115.595271</v>
+        <v>111.0942162</v>
       </c>
       <c r="N68">
-        <v>667.9780623333334</v>
+        <v>672.4791171333334</v>
       </c>
       <c r="O68">
-        <v>166.5937287459333</v>
+        <v>167.7162918130533</v>
       </c>
       <c r="P68">
-        <v>501.3843335874</v>
+        <v>504.7628253202801</v>
       </c>
       <c r="Q68">
-        <v>508.6443335874</v>
+        <v>512.02282532028</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1505786549809375</v>
+        <v>0.1505112916217106</v>
       </c>
       <c r="T68">
         <v>2.418274633295856</v>
       </c>
       <c r="U68">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V68">
         <v>0.2494</v>
       </c>
       <c r="W68">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.778593333055409</v>
+        <v>7.05323247362119</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07904635121219775</v>
+        <v>0.07791713164653606</v>
       </c>
       <c r="C69">
-        <v>1193.406387415439</v>
+        <v>1288.481340209274</v>
       </c>
       <c r="D69">
-        <v>2757.139387415439</v>
+        <v>2852.214340209274</v>
       </c>
       <c r="E69">
         <v>142.5330000000001</v>
@@ -6939,37 +6939,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M69">
-        <v>117.3467145</v>
+        <v>112.7774619</v>
       </c>
       <c r="N69">
-        <v>666.2266188333333</v>
+        <v>670.7958714333333</v>
       </c>
       <c r="O69">
-        <v>166.1569187370333</v>
+        <v>167.2964903354734</v>
       </c>
       <c r="P69">
-        <v>500.0697000963</v>
+        <v>503.49938109786</v>
       </c>
       <c r="Q69">
-        <v>507.3297000963</v>
+        <v>510.75938109786</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1534314794309023</v>
+        <v>0.1533622819592002</v>
       </c>
       <c r="T69">
         <v>2.484117366263284</v>
       </c>
       <c r="U69">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V69">
         <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.677420298233685</v>
+        <v>6.947960347149231</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07890608573087673</v>
+        <v>0.07776042134169051</v>
       </c>
       <c r="C70">
-        <v>1174.088970263641</v>
+        <v>1271.467493094477</v>
       </c>
       <c r="D70">
-        <v>2768.820970263642</v>
+        <v>2866.199493094477</v>
       </c>
       <c r="E70">
         <v>173.5320000000004</v>
@@ -7021,37 +7021,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M70">
-        <v>119.098158</v>
+        <v>114.4607076</v>
       </c>
       <c r="N70">
-        <v>664.4751753333334</v>
+        <v>669.1126257333333</v>
       </c>
       <c r="O70">
-        <v>165.7201087281333</v>
+        <v>166.8766888578933</v>
       </c>
       <c r="P70">
-        <v>498.7550666052</v>
+        <v>502.23593687544</v>
       </c>
       <c r="Q70">
-        <v>506.0150666052</v>
+        <v>509.49593687544</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1564626054089898</v>
+        <v>0.1563914591927829</v>
       </c>
       <c r="T70">
         <v>2.554075270041175</v>
       </c>
       <c r="U70">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V70">
         <v>0.2494</v>
       </c>
       <c r="W70">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.579222940906719</v>
+        <v>6.845784459691154</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07876582024955574</v>
+        <v>0.07760371103684496</v>
       </c>
       <c r="C71">
-        <v>1154.870960487628</v>
+        <v>1254.591467479152</v>
       </c>
       <c r="D71">
-        <v>2780.601960487628</v>
+        <v>2880.322467479153</v>
       </c>
       <c r="E71">
         <v>204.5310000000002</v>
@@ -7103,37 +7103,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M71">
-        <v>120.8496015</v>
+        <v>116.1439533</v>
       </c>
       <c r="N71">
-        <v>662.7237318333333</v>
+        <v>667.4293800333334</v>
       </c>
       <c r="O71">
-        <v>165.2832987192333</v>
+        <v>166.4568873803133</v>
       </c>
       <c r="P71">
-        <v>497.4404331141</v>
+        <v>500.97249265302</v>
       </c>
       <c r="Q71">
-        <v>504.7004331141</v>
+        <v>508.23249265302</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1596892879017927</v>
+        <v>0.159616067215629</v>
       </c>
       <c r="T71">
         <v>2.628546586966027</v>
       </c>
       <c r="U71">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V71">
         <v>0.2494</v>
       </c>
       <c r="W71">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.483871883792129</v>
+        <v>6.746570192159398</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07862555476823474</v>
+        <v>0.07744700073199942</v>
       </c>
       <c r="C72">
-        <v>1135.75363240768</v>
+        <v>1237.855310765774</v>
       </c>
       <c r="D72">
-        <v>2792.483632407681</v>
+        <v>2894.585310765774</v>
       </c>
       <c r="E72">
         <v>235.5300000000004</v>
@@ -7185,37 +7185,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M72">
-        <v>122.601045</v>
+        <v>117.827199</v>
       </c>
       <c r="N72">
-        <v>660.9722883333334</v>
+        <v>665.7461343333333</v>
       </c>
       <c r="O72">
-        <v>164.8464887103333</v>
+        <v>166.0370859027333</v>
       </c>
       <c r="P72">
-        <v>496.125799623</v>
+        <v>499.7090484306</v>
       </c>
       <c r="Q72">
-        <v>503.385799623</v>
+        <v>506.9690484306</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1631310825607825</v>
+        <v>0.1630556491066648</v>
       </c>
       <c r="T72">
         <v>2.707982658352536</v>
       </c>
       <c r="U72">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V72">
         <v>0.2494</v>
       </c>
       <c r="W72">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.391245142595099</v>
+        <v>6.650190617985692</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07848528928691376</v>
+        <v>0.07729029042715389</v>
       </c>
       <c r="C73">
-        <v>1116.738282218529</v>
+        <v>1221.261111112117</v>
       </c>
       <c r="D73">
-        <v>2804.467282218529</v>
+        <v>2908.990111112117</v>
       </c>
       <c r="E73">
         <v>266.5289999999998</v>
@@ -7267,37 +7267,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M73">
-        <v>124.3524885</v>
+        <v>119.5104447</v>
       </c>
       <c r="N73">
-        <v>659.2208448333333</v>
+        <v>664.0628886333334</v>
       </c>
       <c r="O73">
-        <v>164.4096787014333</v>
+        <v>165.6172844251533</v>
       </c>
       <c r="P73">
-        <v>494.8111661319</v>
+        <v>498.44560420818</v>
       </c>
       <c r="Q73">
-        <v>502.0711661319</v>
+        <v>505.70560420818</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1668102423686681</v>
+        <v>0.16673244354191</v>
       </c>
       <c r="T73">
         <v>2.792897079489838</v>
       </c>
       <c r="U73">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V73">
         <v>0.2494</v>
       </c>
       <c r="W73">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.301227605375451</v>
+        <v>6.556525961394346</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07834502380559276</v>
+        <v>0.07713358012230835</v>
       </c>
       <c r="C74">
-        <v>1097.82622846073</v>
+        <v>1204.810998450417</v>
       </c>
       <c r="D74">
-        <v>2816.554228460731</v>
+        <v>2923.538998450417</v>
       </c>
       <c r="E74">
         <v>297.528</v>
@@ -7349,37 +7349,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M74">
-        <v>126.103932</v>
+        <v>121.1936904</v>
       </c>
       <c r="N74">
-        <v>657.4694013333334</v>
+        <v>662.3796429333333</v>
       </c>
       <c r="O74">
-        <v>163.9728686925334</v>
+        <v>165.1974829475733</v>
       </c>
       <c r="P74">
-        <v>493.4965326408001</v>
+        <v>497.18215998576</v>
       </c>
       <c r="Q74">
-        <v>500.7565326408001</v>
+        <v>504.44215998576</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1707521993056884</v>
+        <v>0.1706718661511012</v>
       </c>
       <c r="T74">
         <v>2.883876816422662</v>
       </c>
       <c r="U74">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V74">
         <v>0.2494</v>
       </c>
       <c r="W74">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.213710555300792</v>
+        <v>6.465463100819424</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07897187152427175</v>
+        <v>0.0769768698174628</v>
       </c>
       <c r="C75">
-        <v>1013.602899789542</v>
+        <v>1188.507145537261</v>
       </c>
       <c r="D75">
-        <v>2763.329899789543</v>
+        <v>2938.234145537262</v>
       </c>
       <c r="E75">
         <v>328.5269999999998</v>
@@ -7431,45 +7431,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M75">
-        <v>131.0234733</v>
+        <v>122.8769361</v>
       </c>
       <c r="N75">
-        <v>652.5498600333334</v>
+        <v>660.6963972333334</v>
       </c>
       <c r="O75">
-        <v>162.7459350923133</v>
+        <v>164.7776814699934</v>
       </c>
       <c r="P75">
-        <v>489.8039249410201</v>
+        <v>495.9187157633401</v>
       </c>
       <c r="Q75">
-        <v>497.06392494102</v>
+        <v>503.1787157633401</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1749861530528583</v>
+        <v>0.1749030978424548</v>
       </c>
       <c r="T75">
         <v>2.981595793128287</v>
       </c>
       <c r="U75">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V75">
         <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.04345974</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y75">
-        <v>5.980404225273529</v>
+        <v>6.376895113136967</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.07884211444295075</v>
+        <v>0.07682015951261725</v>
       </c>
       <c r="C76">
-        <v>993.4555546720658</v>
+        <v>1172.351769035311</v>
       </c>
       <c r="D76">
-        <v>2774.181554672066</v>
+        <v>2953.077769035311</v>
       </c>
       <c r="E76">
         <v>359.5260000000001</v>
@@ -7513,45 +7513,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M76">
-        <v>132.8183154</v>
+        <v>124.5601818</v>
       </c>
       <c r="N76">
-        <v>650.7550179333334</v>
+        <v>659.0131515333334</v>
       </c>
       <c r="O76">
-        <v>162.2983014725734</v>
+        <v>164.3578799924134</v>
       </c>
       <c r="P76">
-        <v>488.45671646076</v>
+        <v>494.65527154092</v>
       </c>
       <c r="Q76">
-        <v>495.71671646076</v>
+        <v>501.91527154092</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1795457955498106</v>
+        <v>0.1794598088946818</v>
       </c>
       <c r="T76">
         <v>3.086831614195884</v>
       </c>
       <c r="U76">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V76">
         <v>0.2494</v>
       </c>
       <c r="W76">
-        <v>0.04345974</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y76">
-        <v>5.899587951959021</v>
+        <v>6.290720854851331</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.07871235736162976</v>
+        <v>0.07666344920777173</v>
       </c>
       <c r="C77">
-        <v>973.393774927471</v>
+        <v>1156.347130627973</v>
       </c>
       <c r="D77">
-        <v>2785.118774927471</v>
+        <v>2968.072130627973</v>
       </c>
       <c r="E77">
         <v>390.5249999999999</v>
@@ -7595,45 +7595,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M77">
-        <v>134.6131575</v>
+        <v>126.2434275</v>
       </c>
       <c r="N77">
-        <v>648.9601758333333</v>
+        <v>657.3299058333333</v>
       </c>
       <c r="O77">
-        <v>161.8506678528333</v>
+        <v>163.9380785148333</v>
       </c>
       <c r="P77">
-        <v>487.1095079805</v>
+        <v>493.3918273185</v>
       </c>
       <c r="Q77">
-        <v>494.3695079805</v>
+        <v>500.6518273185</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1844702094465191</v>
+        <v>0.1843810568310869</v>
       </c>
       <c r="T77">
         <v>3.20048630094889</v>
       </c>
       <c r="U77">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V77">
         <v>0.2494</v>
       </c>
       <c r="W77">
-        <v>0.04345974</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y77">
-        <v>5.820926779266234</v>
+        <v>6.206844576786647</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07858260028030876</v>
+        <v>0.07650673890292618</v>
       </c>
       <c r="C78">
-        <v>953.4185765867919</v>
+        <v>1140.495538168209</v>
       </c>
       <c r="D78">
-        <v>2796.142576586792</v>
+        <v>2983.21953816821</v>
       </c>
       <c r="E78">
         <v>421.5240000000001</v>
@@ -7677,45 +7677,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M78">
-        <v>136.4079996</v>
+        <v>127.9266732</v>
       </c>
       <c r="N78">
-        <v>647.1653337333333</v>
+        <v>655.6466601333334</v>
       </c>
       <c r="O78">
-        <v>161.4030342330933</v>
+        <v>163.5182770372534</v>
       </c>
       <c r="P78">
-        <v>485.76229950024</v>
+        <v>492.12838309608</v>
       </c>
       <c r="Q78">
-        <v>493.02229950024</v>
+        <v>499.38838309608</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1898049911679532</v>
+        <v>0.1897124087621924</v>
       </c>
       <c r="T78">
         <v>3.323612211597978</v>
       </c>
       <c r="U78">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V78">
         <v>0.2494</v>
       </c>
       <c r="W78">
-        <v>0.04345974</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y78">
-        <v>5.744335637433783</v>
+        <v>6.125175569197349</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.07845284319898777</v>
+        <v>0.07692799059808064</v>
       </c>
       <c r="C79">
-        <v>933.5309918312241</v>
+        <v>1069.124954158904</v>
       </c>
       <c r="D79">
-        <v>2807.253991831225</v>
+        <v>2942.847954158905</v>
       </c>
       <c r="E79">
         <v>452.5230000000004</v>
@@ -7759,37 +7759,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M79">
-        <v>138.2028417000001</v>
+        <v>131.9968419</v>
       </c>
       <c r="N79">
-        <v>645.3704916333334</v>
+        <v>651.5764914333333</v>
       </c>
       <c r="O79">
-        <v>160.9554006133533</v>
+        <v>162.5031769634734</v>
       </c>
       <c r="P79">
-        <v>484.41509101998</v>
+        <v>489.07331446986</v>
       </c>
       <c r="Q79">
-        <v>491.67509101998</v>
+        <v>496.3333144698599</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1956036669521208</v>
+        <v>0.1955073565133941</v>
       </c>
       <c r="T79">
         <v>3.457444723173074</v>
       </c>
       <c r="U79">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V79">
         <v>0.2494</v>
       </c>
       <c r="W79">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.669733875908668</v>
+        <v>5.936303642226255</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.07832308611766678</v>
+        <v>0.07677878629323509</v>
       </c>
       <c r="C80">
-        <v>913.732069314302</v>
+        <v>1052.299704515364</v>
       </c>
       <c r="D80">
-        <v>2818.454069314303</v>
+        <v>2957.021704515364</v>
       </c>
       <c r="E80">
         <v>483.5220000000002</v>
@@ -7841,37 +7841,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M80">
-        <v>139.9976838</v>
+        <v>133.7110866</v>
       </c>
       <c r="N80">
-        <v>643.5756495333334</v>
+        <v>649.8622467333333</v>
       </c>
       <c r="O80">
-        <v>160.5077669936134</v>
+        <v>162.0756443352933</v>
       </c>
       <c r="P80">
-        <v>483.06788253972</v>
+        <v>487.78660239804</v>
       </c>
       <c r="Q80">
-        <v>490.32788253972</v>
+        <v>495.04660239804</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2019294950803035</v>
+        <v>0.2018291176965232</v>
       </c>
       <c r="T80">
         <v>3.603443826709543</v>
       </c>
       <c r="U80">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V80">
         <v>0.2494</v>
       </c>
       <c r="W80">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.597044980063686</v>
+        <v>5.860197185274636</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.07819332903634577</v>
+        <v>0.07662958198838957</v>
       </c>
       <c r="C81">
-        <v>894.0228744918199</v>
+        <v>1035.611646778594</v>
       </c>
       <c r="D81">
-        <v>2829.74387449182</v>
+        <v>2971.332646778594</v>
       </c>
       <c r="E81">
         <v>514.5210000000004</v>
@@ -7923,37 +7923,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M81">
-        <v>141.7925259</v>
+        <v>135.4253313</v>
       </c>
       <c r="N81">
-        <v>641.7808074333334</v>
+        <v>648.1480020333333</v>
       </c>
       <c r="O81">
-        <v>160.0601333738734</v>
+        <v>161.6481117071133</v>
       </c>
       <c r="P81">
-        <v>481.7206740594601</v>
+        <v>486.49989032622</v>
       </c>
       <c r="Q81">
-        <v>488.9806740594601</v>
+        <v>493.75989032622</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.208857783030218</v>
+        <v>0.2087529513732837</v>
       </c>
       <c r="T81">
         <v>3.763347606773295</v>
       </c>
       <c r="U81">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V81">
         <v>0.2494</v>
       </c>
       <c r="W81">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.526196309429968</v>
+        <v>5.786017474068628</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.07806357195502478</v>
+        <v>0.07648037768354402</v>
       </c>
       <c r="C82">
-        <v>874.404489959687</v>
+        <v>1019.062782516827</v>
       </c>
       <c r="D82">
-        <v>2841.124489959687</v>
+        <v>2985.782782516828</v>
       </c>
       <c r="E82">
         <v>545.5200000000002</v>
@@ -8005,37 +8005,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M82">
-        <v>143.587368</v>
+        <v>137.139576</v>
       </c>
       <c r="N82">
-        <v>639.9859653333333</v>
+        <v>646.4337573333333</v>
       </c>
       <c r="O82">
-        <v>159.6124997541333</v>
+        <v>161.2205790789334</v>
       </c>
       <c r="P82">
-        <v>480.3734655792</v>
+        <v>485.2131782544</v>
       </c>
       <c r="Q82">
-        <v>487.6334655792</v>
+        <v>492.4731782544</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2164788997751239</v>
+        <v>0.2163691684177201</v>
       </c>
       <c r="T82">
         <v>3.939241764843421</v>
       </c>
       <c r="U82">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V82">
         <v>0.2494</v>
       </c>
       <c r="W82">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.457118855562094</v>
+        <v>5.713692255642771</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07793381487370377</v>
+        <v>0.07633117337869846</v>
       </c>
       <c r="C83">
-        <v>854.8780158000127</v>
+        <v>1002.655152424544</v>
       </c>
       <c r="D83">
-        <v>2852.597015800013</v>
+        <v>3000.374152424545</v>
       </c>
       <c r="E83">
         <v>576.5190000000005</v>
@@ -8087,37 +8087,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M83">
-        <v>145.3822101</v>
+        <v>138.8538207000001</v>
       </c>
       <c r="N83">
-        <v>638.1911232333333</v>
+        <v>644.7195126333334</v>
       </c>
       <c r="O83">
-        <v>159.1648661343933</v>
+        <v>160.7930464507533</v>
       </c>
       <c r="P83">
-        <v>479.02625709894</v>
+        <v>483.92646618258</v>
       </c>
       <c r="Q83">
-        <v>486.28625709894</v>
+        <v>491.18646618258</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2249022393352831</v>
+        <v>0.2247870925194657</v>
       </c>
       <c r="T83">
         <v>4.133651097447245</v>
       </c>
       <c r="U83">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V83">
         <v>0.2494</v>
       </c>
       <c r="W83">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.389747017839104</v>
+        <v>5.643152845079279</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07780405779238278</v>
+        <v>0.07618196907385294</v>
       </c>
       <c r="C84">
-        <v>835.4445699355656</v>
+        <v>986.3908372832111</v>
       </c>
       <c r="D84">
-        <v>2864.162569935566</v>
+        <v>3015.108837283212</v>
       </c>
       <c r="E84">
         <v>607.5180000000003</v>
@@ -8169,37 +8169,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M84">
-        <v>147.1770522</v>
+        <v>140.5680654</v>
       </c>
       <c r="N84">
-        <v>636.3962811333333</v>
+        <v>643.0052679333334</v>
       </c>
       <c r="O84">
-        <v>158.7172325146533</v>
+        <v>160.3655138225733</v>
       </c>
       <c r="P84">
-        <v>477.67904861868</v>
+        <v>482.63975411076</v>
       </c>
       <c r="Q84">
-        <v>484.93904861868</v>
+        <v>489.89975411076</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2342615055132377</v>
+        <v>0.2341403415214053</v>
       </c>
       <c r="T84">
         <v>4.34966146700705</v>
       </c>
       <c r="U84">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V84">
         <v>0.2494</v>
       </c>
       <c r="W84">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.324018395670335</v>
+        <v>5.574333907944167</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07767430071106178</v>
+        <v>0.07603276476900739</v>
       </c>
       <c r="C85">
-        <v>816.1052884929263</v>
+        <v>970.2719589504727</v>
       </c>
       <c r="D85">
-        <v>2875.822288492927</v>
+        <v>3029.988958950473</v>
       </c>
       <c r="E85">
         <v>638.5170000000005</v>
@@ -8251,37 +8251,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M85">
-        <v>148.9718943000001</v>
+        <v>142.2823101</v>
       </c>
       <c r="N85">
-        <v>634.6014390333333</v>
+        <v>641.2910232333334</v>
       </c>
       <c r="O85">
-        <v>158.2695988949133</v>
+        <v>159.9379811943934</v>
       </c>
       <c r="P85">
-        <v>476.33184013842</v>
+        <v>481.35304203894</v>
       </c>
       <c r="Q85">
-        <v>483.59184013842</v>
+        <v>488.61304203894</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2447218618297753</v>
+        <v>0.2445939727588671</v>
       </c>
       <c r="T85">
         <v>4.591084821220949</v>
       </c>
       <c r="U85">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V85">
         <v>0.2494</v>
       </c>
       <c r="W85">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.2598735957225</v>
+        <v>5.507173258450863</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.07754454362974078</v>
+        <v>0.07588356046416185</v>
       </c>
       <c r="C86">
-        <v>796.8613261745249</v>
+        <v>954.3006813787551</v>
       </c>
       <c r="D86">
-        <v>2887.577326174525</v>
+        <v>3045.016681378755</v>
       </c>
       <c r="E86">
         <v>669.5159999999998</v>
@@ -8333,37 +8333,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M86">
-        <v>150.7667364</v>
+        <v>143.9965548</v>
       </c>
       <c r="N86">
-        <v>632.8065969333334</v>
+        <v>639.5767785333334</v>
       </c>
       <c r="O86">
-        <v>157.8219652751733</v>
+        <v>159.5104485662133</v>
       </c>
       <c r="P86">
-        <v>474.98463165816</v>
+        <v>480.0663299671201</v>
       </c>
       <c r="Q86">
-        <v>482.24463165816</v>
+        <v>487.32632996712</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2564897626858799</v>
+        <v>0.2563543079010115</v>
       </c>
       <c r="T86">
         <v>4.862686094711584</v>
       </c>
       <c r="U86">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V86">
         <v>0.2494</v>
       </c>
       <c r="W86">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.197256052916281</v>
+        <v>5.441611672040735</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.0774147865484198</v>
+        <v>0.07573435615931631</v>
       </c>
       <c r="C87">
-        <v>777.7138566398412</v>
+        <v>938.4792116643625</v>
       </c>
       <c r="D87">
-        <v>2899.428856639841</v>
+        <v>3060.194211664363</v>
       </c>
       <c r="E87">
         <v>700.5150000000001</v>
@@ -8415,37 +8415,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M87">
-        <v>152.5615785</v>
+        <v>145.7107995</v>
       </c>
       <c r="N87">
-        <v>631.0117548333334</v>
+        <v>637.8625338333334</v>
       </c>
       <c r="O87">
-        <v>157.3743316554334</v>
+        <v>159.0829159380334</v>
       </c>
       <c r="P87">
-        <v>473.6374231779</v>
+        <v>478.7796178953</v>
       </c>
       <c r="Q87">
-        <v>480.8974231779</v>
+        <v>486.0396178953</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2698267169894653</v>
+        <v>0.2696826877287754</v>
       </c>
       <c r="T87">
         <v>5.170500871334306</v>
       </c>
       <c r="U87">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V87">
         <v>0.2494</v>
       </c>
       <c r="W87">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.136111864058441</v>
+        <v>5.377592711193196</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.07728502946709878</v>
+        <v>0.07558515185447078</v>
       </c>
       <c r="C88">
-        <v>758.6640728960506</v>
+        <v>922.8098011280867</v>
       </c>
       <c r="D88">
-        <v>2911.378072896051</v>
+        <v>3075.523801128087</v>
       </c>
       <c r="E88">
         <v>731.5139999999999</v>
@@ -8497,37 +8497,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M88">
-        <v>154.3564206</v>
+        <v>147.4250442</v>
       </c>
       <c r="N88">
-        <v>629.2169127333334</v>
+        <v>636.1482891333334</v>
       </c>
       <c r="O88">
-        <v>156.9266980356934</v>
+        <v>158.6553833098534</v>
       </c>
       <c r="P88">
-        <v>472.2902146976401</v>
+        <v>477.49290582348</v>
       </c>
       <c r="Q88">
-        <v>479.5502146976401</v>
+        <v>484.75290582348</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2850689504792771</v>
+        <v>0.2849151218176484</v>
       </c>
       <c r="T88">
         <v>5.522289187474558</v>
       </c>
       <c r="U88">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V88">
         <v>0.2494</v>
       </c>
       <c r="W88">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.076389633081019</v>
+        <v>5.315062563388624</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.0771552723857778</v>
+        <v>0.07543594754962524</v>
       </c>
       <c r="C89">
-        <v>739.7131876983403</v>
+        <v>907.2947464284625</v>
       </c>
       <c r="D89">
-        <v>2923.426187698341</v>
+        <v>3091.007746428463</v>
       </c>
       <c r="E89">
         <v>762.5130000000001</v>
@@ -8579,37 +8579,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M89">
-        <v>156.1512627</v>
+        <v>149.1392889</v>
       </c>
       <c r="N89">
-        <v>627.4220706333333</v>
+        <v>634.4340444333334</v>
       </c>
       <c r="O89">
-        <v>156.4790644159533</v>
+        <v>158.2278506816733</v>
       </c>
       <c r="P89">
-        <v>470.94300621738</v>
+        <v>476.2061937516601</v>
       </c>
       <c r="Q89">
-        <v>478.20300621738</v>
+        <v>483.4661937516601</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3026561429675215</v>
+        <v>0.3024910073048094</v>
       </c>
       <c r="T89">
         <v>5.928198783021004</v>
       </c>
       <c r="U89">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V89">
         <v>0.2494</v>
       </c>
       <c r="W89">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.01804032695365</v>
+        <v>5.253969890246227</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.07702551530445681</v>
+        <v>0.07528674324477969</v>
       </c>
       <c r="C90">
-        <v>720.8624339602343</v>
+        <v>891.9363907088286</v>
       </c>
       <c r="D90">
-        <v>2935.574433960235</v>
+        <v>3106.648390708829</v>
       </c>
       <c r="E90">
         <v>793.5120000000004</v>
@@ -8661,37 +8661,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M90">
-        <v>157.9461048</v>
+        <v>150.8535336</v>
       </c>
       <c r="N90">
-        <v>625.6272285333333</v>
+        <v>632.7197997333333</v>
       </c>
       <c r="O90">
-        <v>156.0314307962133</v>
+        <v>157.8003180534933</v>
       </c>
       <c r="P90">
-        <v>469.59579773712</v>
+        <v>474.9194816798399</v>
       </c>
       <c r="Q90">
-        <v>476.85579773712</v>
+        <v>482.1794816798399</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3231745342038067</v>
+        <v>0.3229962070398308</v>
       </c>
       <c r="T90">
         <v>6.401759977825192</v>
       </c>
       <c r="U90">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V90">
         <v>0.2494</v>
       </c>
       <c r="W90">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.961017141420085</v>
+        <v>5.194265686947973</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.0768957582231358</v>
+        <v>0.07513753893993413</v>
       </c>
       <c r="C91">
-        <v>702.1130651741746</v>
+        <v>876.7371247793749</v>
       </c>
       <c r="D91">
-        <v>2947.824065174175</v>
+        <v>3122.448124779375</v>
       </c>
       <c r="E91">
         <v>824.5110000000002</v>
@@ -8743,37 +8743,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M91">
-        <v>159.7409469</v>
+        <v>152.5677783</v>
       </c>
       <c r="N91">
-        <v>623.8323864333333</v>
+        <v>631.0055550333334</v>
       </c>
       <c r="O91">
-        <v>155.5837971764734</v>
+        <v>157.3727854253134</v>
       </c>
       <c r="P91">
-        <v>468.24858925686</v>
+        <v>473.63276960802</v>
       </c>
       <c r="Q91">
-        <v>475.50858925686</v>
+        <v>480.89276960802</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3474235420285073</v>
+        <v>0.3472296249084923</v>
       </c>
       <c r="T91">
         <v>6.961423208048322</v>
       </c>
       <c r="U91">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V91">
         <v>0.2494</v>
       </c>
       <c r="W91">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.905275375786152</v>
+        <v>5.135903151139569</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.07676600114181481</v>
+        <v>0.07498833463508861</v>
       </c>
       <c r="C92">
-        <v>683.4663558426728</v>
+        <v>861.6993883354617</v>
       </c>
       <c r="D92">
-        <v>2960.176355842674</v>
+        <v>3138.409388335463</v>
       </c>
       <c r="E92">
         <v>855.5100000000004</v>
@@ -8825,37 +8825,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M92">
-        <v>161.5357890000001</v>
+        <v>154.282023</v>
       </c>
       <c r="N92">
-        <v>622.0375443333334</v>
+        <v>629.2913103333333</v>
       </c>
       <c r="O92">
-        <v>155.1361635567334</v>
+        <v>156.9452527971333</v>
       </c>
       <c r="P92">
-        <v>466.9013807766</v>
+        <v>472.3460575362</v>
       </c>
       <c r="Q92">
-        <v>474.1613807766</v>
+        <v>479.6060575362</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3765223514181481</v>
+        <v>0.3763097263508862</v>
       </c>
       <c r="T92">
         <v>7.633019084316078</v>
       </c>
       <c r="U92">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V92">
         <v>0.2494</v>
       </c>
       <c r="W92">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.850772316055194</v>
+        <v>5.078837560571351</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.0766362440604938</v>
+        <v>0.07483913033024306</v>
       </c>
       <c r="C93">
-        <v>664.9236019203763</v>
+        <v>846.8256712134989</v>
       </c>
       <c r="D93">
-        <v>2972.632601920377</v>
+        <v>3154.534671213499</v>
       </c>
       <c r="E93">
         <v>886.5090000000002</v>
@@ -8907,37 +8907,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M93">
-        <v>163.3306311</v>
+        <v>155.9962677</v>
       </c>
       <c r="N93">
-        <v>620.2427022333334</v>
+        <v>627.5770656333334</v>
       </c>
       <c r="O93">
-        <v>154.6885299369933</v>
+        <v>156.5177201689534</v>
       </c>
       <c r="P93">
-        <v>465.55417229634</v>
+        <v>471.05934546438</v>
       </c>
       <c r="Q93">
-        <v>472.81417229634</v>
+        <v>478.31934546438</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4120875628943757</v>
+        <v>0.4118520725582563</v>
       </c>
       <c r="T93">
         <v>8.453858488643334</v>
       </c>
       <c r="U93">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V93">
         <v>0.2494</v>
       </c>
       <c r="W93">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.797467125768874</v>
+        <v>5.023026158806832</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.07650648697917281</v>
+        <v>0.07468992602539754</v>
       </c>
       <c r="C94">
-        <v>646.4861212672954</v>
+        <v>832.1185146857083</v>
       </c>
       <c r="D94">
-        <v>2985.194121267296</v>
+        <v>3170.826514685709</v>
       </c>
       <c r="E94">
         <v>917.5080000000005</v>
@@ -8989,37 +8989,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M94">
-        <v>165.1254732</v>
+        <v>157.7105124000001</v>
       </c>
       <c r="N94">
-        <v>618.4478601333333</v>
+        <v>625.8628209333333</v>
       </c>
       <c r="O94">
-        <v>154.2408963172533</v>
+        <v>156.0901875407733</v>
       </c>
       <c r="P94">
-        <v>464.20696381608</v>
+        <v>469.77263339256</v>
       </c>
       <c r="Q94">
-        <v>471.46696381608</v>
+        <v>477.0326333925599</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4565440772396604</v>
+        <v>0.4562800053174693</v>
       </c>
       <c r="T94">
         <v>9.47990774405241</v>
       </c>
       <c r="U94">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V94">
         <v>0.2494</v>
       </c>
       <c r="W94">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.745320743967037</v>
+        <v>4.968428048385017</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.07637672989785181</v>
+        <v>0.07454072172055198</v>
       </c>
       <c r="C95">
-        <v>628.155254113623</v>
+        <v>817.5805127952731</v>
       </c>
       <c r="D95">
-        <v>2997.862254113623</v>
+        <v>3187.287512795274</v>
       </c>
       <c r="E95">
         <v>948.5070000000003</v>
@@ -9071,37 +9071,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M95">
-        <v>166.9203153</v>
+        <v>159.4247571000001</v>
       </c>
       <c r="N95">
-        <v>616.6530180333334</v>
+        <v>624.1485762333333</v>
       </c>
       <c r="O95">
-        <v>153.7932626975134</v>
+        <v>155.6626549125933</v>
       </c>
       <c r="P95">
-        <v>462.8597553358201</v>
+        <v>468.48592132074</v>
       </c>
       <c r="Q95">
-        <v>470.1197553358201</v>
+        <v>475.74592132074</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5137024528264548</v>
+        <v>0.5134016331507429</v>
       </c>
       <c r="T95">
         <v>10.79911392957836</v>
       </c>
       <c r="U95">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V95">
         <v>0.2494</v>
       </c>
       <c r="W95">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.694295789730834</v>
+        <v>4.915004090875501</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07624697281653081</v>
+        <v>0.07439151741570643</v>
       </c>
       <c r="C96">
-        <v>609.9323635363953</v>
+        <v>803.2143137332287</v>
       </c>
       <c r="D96">
-        <v>3010.638363536396</v>
+        <v>3203.920313733229</v>
       </c>
       <c r="E96">
         <v>979.5060000000005</v>
@@ -9153,37 +9153,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M96">
-        <v>168.7151574</v>
+        <v>161.1390018</v>
       </c>
       <c r="N96">
-        <v>614.8581759333333</v>
+        <v>622.4343315333333</v>
       </c>
       <c r="O96">
-        <v>153.3456290777733</v>
+        <v>155.2351222844133</v>
       </c>
       <c r="P96">
-        <v>461.51254685556</v>
+        <v>467.1992092489199</v>
       </c>
       <c r="Q96">
-        <v>468.77254685556</v>
+        <v>474.4592092489199</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.589913620275514</v>
+        <v>0.5895638035951078</v>
       </c>
       <c r="T96">
         <v>12.55805551027963</v>
       </c>
       <c r="U96">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V96">
         <v>0.2494</v>
       </c>
       <c r="W96">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.644356472818803</v>
+        <v>4.862716813312996</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07611721573520983</v>
+        <v>0.07424231311086091</v>
       </c>
       <c r="C97">
-        <v>591.8188359484202</v>
+        <v>789.0226212587368</v>
       </c>
       <c r="D97">
-        <v>3023.523835948421</v>
+        <v>3220.727621258737</v>
       </c>
       <c r="E97">
         <v>1010.505</v>
@@ -9235,37 +9235,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M97">
-        <v>170.5099995</v>
+        <v>162.8532465</v>
       </c>
       <c r="N97">
-        <v>613.0633338333333</v>
+        <v>620.7200868333333</v>
       </c>
       <c r="O97">
-        <v>152.8979954580333</v>
+        <v>154.8075896562333</v>
       </c>
       <c r="P97">
-        <v>460.1653383753</v>
+        <v>465.9124971771</v>
       </c>
       <c r="Q97">
-        <v>467.4253383753</v>
+        <v>473.1724971771</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6966092547041972</v>
+        <v>0.6961908422172189</v>
       </c>
       <c r="T97">
         <v>15.02057372326141</v>
       </c>
       <c r="U97">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V97">
         <v>0.2494</v>
       </c>
       <c r="W97">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.595468509947025</v>
+        <v>4.81153032054128</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.07598745865388881</v>
+        <v>0.07409310880601536</v>
       </c>
       <c r="C98">
-        <v>573.8160815998126</v>
+        <v>775.0081961642909</v>
       </c>
       <c r="D98">
-        <v>3036.520081599813</v>
+        <v>3237.712196164291</v>
       </c>
       <c r="E98">
         <v>1041.504</v>
@@ -9317,37 +9317,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M98">
-        <v>172.3048416</v>
+        <v>164.5674912</v>
       </c>
       <c r="N98">
-        <v>611.2684917333333</v>
+        <v>619.0058421333333</v>
       </c>
       <c r="O98">
-        <v>152.4503618382933</v>
+        <v>154.3800570280533</v>
       </c>
       <c r="P98">
-        <v>458.81812989504</v>
+        <v>464.62578510528</v>
       </c>
       <c r="Q98">
-        <v>466.07812989504</v>
+        <v>471.88578510528</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8566527063472198</v>
+        <v>0.8561314001503832</v>
       </c>
       <c r="T98">
         <v>18.71435104273403</v>
       </c>
       <c r="U98">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V98">
         <v>0.2494</v>
       </c>
       <c r="W98">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.547599046301745</v>
+        <v>4.761410213035642</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.07585770157256783</v>
+        <v>0.07394390450116983</v>
       </c>
       <c r="C99">
-        <v>555.9255350924959</v>
+        <v>761.173857787503</v>
       </c>
       <c r="D99">
-        <v>3049.628535092496</v>
+        <v>3254.876857787503</v>
       </c>
       <c r="E99">
         <v>1072.503</v>
@@ -9399,37 +9399,37 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M99">
-        <v>174.0996837</v>
+        <v>166.2817359</v>
       </c>
       <c r="N99">
-        <v>609.4736496333334</v>
+        <v>617.2915974333333</v>
       </c>
       <c r="O99">
-        <v>152.0027282185534</v>
+        <v>153.9525243998733</v>
       </c>
       <c r="P99">
-        <v>457.47092141478</v>
+        <v>463.33907303346</v>
       </c>
       <c r="Q99">
-        <v>464.73092141478</v>
+        <v>470.5990730334599</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.123391792418927</v>
+        <v>1.12269899670566</v>
       </c>
       <c r="T99">
         <v>24.87064657518845</v>
       </c>
       <c r="U99">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V99">
         <v>0.2494</v>
       </c>
       <c r="W99">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.500716581906882</v>
+        <v>4.712323509808471</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.07764047329124682</v>
+        <v>0.07379470019632428</v>
       </c>
       <c r="C100">
-        <v>354.1755712136405</v>
+        <v>747.5224855712727</v>
       </c>
       <c r="D100">
-        <v>2878.877571213641</v>
+        <v>3272.224485571273</v>
       </c>
       <c r="E100">
         <v>1103.502</v>
@@ -9481,45 +9481,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M100">
-        <v>183.793071</v>
+        <v>167.9959806</v>
       </c>
       <c r="N100">
-        <v>599.7802623333333</v>
+        <v>615.5773527333333</v>
       </c>
       <c r="O100">
-        <v>149.5851974259333</v>
+        <v>153.5249917716934</v>
       </c>
       <c r="P100">
-        <v>450.1950649074</v>
+        <v>462.05236096164</v>
       </c>
       <c r="Q100">
-        <v>457.4550649074</v>
+        <v>469.31236096164</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.65686996456234</v>
+        <v>1.655834189816213</v>
       </c>
       <c r="T100">
         <v>37.18323764009729</v>
       </c>
       <c r="U100">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V100">
         <v>0.2494</v>
       </c>
       <c r="W100">
-        <v>0.04541129999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>4.263345343053402</v>
+        <v>4.664238576034915</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.07753023180992583</v>
+        <v>0.07364549589147873</v>
       </c>
       <c r="C101">
-        <v>333.1787587139884</v>
+        <v>734.0570206740781</v>
       </c>
       <c r="D101">
-        <v>2888.879758713988</v>
+        <v>3289.758020674078</v>
       </c>
       <c r="E101">
         <v>1134.501</v>
@@ -9563,45 +9563,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M101">
-        <v>185.6685105</v>
+        <v>169.7102253</v>
       </c>
       <c r="N101">
-        <v>597.9048228333334</v>
+        <v>613.8631080333333</v>
       </c>
       <c r="O101">
-        <v>149.1174628146333</v>
+        <v>153.0974591435133</v>
       </c>
       <c r="P101">
-        <v>448.7873600187</v>
+        <v>460.76564888982</v>
       </c>
       <c r="Q101">
-        <v>456.0473600187</v>
+        <v>468.02564888982</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.25730448099258</v>
+        <v>3.255239769147871</v>
       </c>
       <c r="T101">
         <v>74.12101083482381</v>
       </c>
       <c r="U101">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V101">
         <v>0.2494</v>
       </c>
       <c r="W101">
-        <v>0.04541129999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y101">
-        <v>4.220281248679125</v>
+        <v>4.617125055064866</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_metals_mining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08841672207118731</v>
+        <v>0.08822998776634178</v>
       </c>
       <c r="C2">
-        <v>2662.70702439342</v>
+        <v>2641.168001194996</v>
       </c>
       <c r="D2">
-        <v>2149.50702439342</v>
+        <v>2158.967001194995</v>
       </c>
       <c r="E2">
-        <v>-1934.4</v>
+        <v>-1903.401</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.99900000000001</v>
       </c>
       <c r="G2">
         <v>513.2</v>
@@ -1445,28 +1445,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.5592497</v>
       </c>
       <c r="N2">
-        <v>783.5733333333334</v>
+        <v>782.0140836333334</v>
       </c>
       <c r="O2">
-        <v>195.4231893333333</v>
+        <v>195.0343124581534</v>
       </c>
       <c r="P2">
-        <v>588.1501440000001</v>
+        <v>586.9797711751801</v>
       </c>
       <c r="Q2">
-        <v>595.4101440000001</v>
+        <v>594.2397711751801</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08841672207118731</v>
+        <v>0.08873983430943613</v>
       </c>
       <c r="T2">
-        <v>0.984219909265296</v>
+        <v>0.991682085668271</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>502.5322969972887</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08822998776634178</v>
+        <v>0.08804325346149623</v>
       </c>
       <c r="C3">
-        <v>2641.168001194996</v>
+        <v>2619.712612757019</v>
       </c>
       <c r="D3">
-        <v>2158.967001194995</v>
+        <v>2168.510612757018</v>
       </c>
       <c r="E3">
-        <v>-1903.401</v>
+        <v>-1872.402</v>
       </c>
       <c r="F3">
-        <v>30.99900000000001</v>
+        <v>61.99800000000001</v>
       </c>
       <c r="G3">
         <v>513.2</v>
@@ -1527,28 +1527,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M3">
-        <v>1.5592497</v>
+        <v>3.118499400000001</v>
       </c>
       <c r="N3">
-        <v>782.0140836333334</v>
+        <v>780.4548339333334</v>
       </c>
       <c r="O3">
-        <v>195.0343124581534</v>
+        <v>194.6454355829733</v>
       </c>
       <c r="P3">
-        <v>586.9797711751801</v>
+        <v>585.80939835036</v>
       </c>
       <c r="Q3">
-        <v>594.2397711751801</v>
+        <v>593.06939835036</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08873983430943613</v>
+        <v>0.08906954067499616</v>
       </c>
       <c r="T3">
-        <v>0.991682085668271</v>
+        <v>0.9992965513855926</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>502.5322969972887</v>
+        <v>251.2661484986443</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08804325346149623</v>
+        <v>0.08785651915665069</v>
       </c>
       <c r="C4">
-        <v>2619.712612757019</v>
+        <v>2598.341973114544</v>
       </c>
       <c r="D4">
-        <v>2168.510612757018</v>
+        <v>2178.138973114543</v>
       </c>
       <c r="E4">
-        <v>-1872.402</v>
+        <v>-1841.403</v>
       </c>
       <c r="F4">
-        <v>61.99800000000001</v>
+        <v>92.99700000000001</v>
       </c>
       <c r="G4">
         <v>513.2</v>
@@ -1609,28 +1609,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M4">
-        <v>3.118499400000001</v>
+        <v>4.677749100000001</v>
       </c>
       <c r="N4">
-        <v>780.4548339333334</v>
+        <v>778.8955842333334</v>
       </c>
       <c r="O4">
-        <v>194.6454355829733</v>
+        <v>194.2565587077933</v>
       </c>
       <c r="P4">
-        <v>585.80939835036</v>
+        <v>584.63902552554</v>
       </c>
       <c r="Q4">
-        <v>593.06939835036</v>
+        <v>591.89902552554</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08906954067499616</v>
+        <v>0.08940604510994916</v>
       </c>
       <c r="T4">
-        <v>0.9992965513855926</v>
+        <v>1.007068016396055</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>251.2661484986443</v>
+        <v>167.5107656657629</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08785651915665069</v>
+        <v>0.08766978485180515</v>
       </c>
       <c r="C5">
-        <v>2598.341973114544</v>
+        <v>2577.057216176481</v>
       </c>
       <c r="D5">
-        <v>2178.138973114543</v>
+        <v>2187.853216176482</v>
       </c>
       <c r="E5">
-        <v>-1841.403</v>
+        <v>-1810.404</v>
       </c>
       <c r="F5">
-        <v>92.99700000000001</v>
+        <v>123.996</v>
       </c>
       <c r="G5">
         <v>513.2</v>
@@ -1691,28 +1691,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M5">
-        <v>4.677749100000001</v>
+        <v>6.236998800000001</v>
       </c>
       <c r="N5">
-        <v>778.8955842333334</v>
+        <v>777.3363345333333</v>
       </c>
       <c r="O5">
-        <v>194.2565587077933</v>
+        <v>193.8676818326134</v>
       </c>
       <c r="P5">
-        <v>584.63902552554</v>
+        <v>583.46865270072</v>
       </c>
       <c r="Q5">
-        <v>591.89902552554</v>
+        <v>590.72865270072</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08940604510994916</v>
+        <v>0.0897495600539637</v>
       </c>
       <c r="T5">
-        <v>1.007068016396055</v>
+        <v>1.015001386927568</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>167.5107656657629</v>
+        <v>125.6330742493222</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08766978485180515</v>
+        <v>0.08748305054695961</v>
       </c>
       <c r="C6">
-        <v>2577.057216176481</v>
+        <v>2555.859496170769</v>
       </c>
       <c r="D6">
-        <v>2187.853216176482</v>
+        <v>2197.65449617077</v>
       </c>
       <c r="E6">
-        <v>-1810.404</v>
+        <v>-1779.405</v>
       </c>
       <c r="F6">
-        <v>123.996</v>
+        <v>154.995</v>
       </c>
       <c r="G6">
         <v>513.2</v>
@@ -1773,28 +1773,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M6">
-        <v>6.236998800000001</v>
+        <v>7.796248500000002</v>
       </c>
       <c r="N6">
-        <v>777.3363345333333</v>
+        <v>775.7770848333333</v>
       </c>
       <c r="O6">
-        <v>193.8676818326134</v>
+        <v>193.4788049574333</v>
       </c>
       <c r="P6">
-        <v>583.46865270072</v>
+        <v>582.2982798759</v>
       </c>
       <c r="Q6">
-        <v>590.72865270072</v>
+        <v>589.5582798759</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0897495600539637</v>
+        <v>0.09010030689153643</v>
       </c>
       <c r="T6">
-        <v>1.015001386927568</v>
+        <v>1.023101775786061</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>125.6330742493222</v>
+        <v>100.5064593994577</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08748305054695961</v>
+        <v>0.08729631624211405</v>
       </c>
       <c r="C7">
-        <v>2555.859496170769</v>
+        <v>2534.749988101541</v>
       </c>
       <c r="D7">
-        <v>2197.65449617077</v>
+        <v>2207.543988101542</v>
       </c>
       <c r="E7">
-        <v>-1779.405</v>
+        <v>-1748.406</v>
       </c>
       <c r="F7">
-        <v>154.995</v>
+        <v>185.9940000000001</v>
       </c>
       <c r="G7">
         <v>513.2</v>
@@ -1855,28 +1855,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M7">
-        <v>7.796248500000002</v>
+        <v>9.355498200000003</v>
       </c>
       <c r="N7">
-        <v>775.7770848333333</v>
+        <v>774.2178351333333</v>
       </c>
       <c r="O7">
-        <v>193.4788049574333</v>
+        <v>193.0899280822534</v>
       </c>
       <c r="P7">
-        <v>582.2982798759</v>
+        <v>581.12790705108</v>
       </c>
       <c r="Q7">
-        <v>589.5582798759</v>
+        <v>588.38790705108</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09010030689153643</v>
+        <v>0.09045851642778091</v>
       </c>
       <c r="T7">
-        <v>1.023101775786061</v>
+        <v>1.03137451334367</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>100.5064593994577</v>
+        <v>83.75538283288142</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08729631624211405</v>
+        <v>0.08710958193726853</v>
       </c>
       <c r="C8">
-        <v>2534.749988101541</v>
+        <v>2513.729888218712</v>
       </c>
       <c r="D8">
-        <v>2207.543988101542</v>
+        <v>2217.522888218712</v>
       </c>
       <c r="E8">
-        <v>-1748.406</v>
+        <v>-1717.407</v>
       </c>
       <c r="F8">
-        <v>185.994</v>
+        <v>216.993</v>
       </c>
       <c r="G8">
         <v>513.2</v>
@@ -1937,28 +1937,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M8">
-        <v>9.355498200000001</v>
+        <v>10.9147479</v>
       </c>
       <c r="N8">
-        <v>774.2178351333333</v>
+        <v>772.6585854333334</v>
       </c>
       <c r="O8">
-        <v>193.0899280822534</v>
+        <v>192.7010512070734</v>
       </c>
       <c r="P8">
-        <v>581.12790705108</v>
+        <v>579.9575342262601</v>
       </c>
       <c r="Q8">
-        <v>588.38790705108</v>
+        <v>587.2175342262601</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09045851642778091</v>
+        <v>0.09082442939491239</v>
       </c>
       <c r="T8">
-        <v>1.03137451334367</v>
+        <v>1.039825159235852</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>83.75538283288144</v>
+        <v>71.79032814246983</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08710958193726852</v>
+        <v>0.086922847632423</v>
       </c>
       <c r="C9">
-        <v>2513.729888218712</v>
+        <v>2492.800414500352</v>
       </c>
       <c r="D9">
-        <v>2217.522888218712</v>
+        <v>2227.592414500352</v>
       </c>
       <c r="E9">
-        <v>-1717.407</v>
+        <v>-1686.408</v>
       </c>
       <c r="F9">
-        <v>216.9930000000001</v>
+        <v>247.992</v>
       </c>
       <c r="G9">
         <v>513.2</v>
@@ -2019,28 +2019,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M9">
-        <v>10.9147479</v>
+        <v>12.4739976</v>
       </c>
       <c r="N9">
-        <v>772.6585854333334</v>
+        <v>771.0993357333334</v>
       </c>
       <c r="O9">
-        <v>192.7010512070734</v>
+        <v>192.3121743318934</v>
       </c>
       <c r="P9">
-        <v>579.9575342262601</v>
+        <v>578.78716140144</v>
       </c>
       <c r="Q9">
-        <v>587.2175342262601</v>
+        <v>586.04716140144</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09082442939491239</v>
+        <v>0.09119829699176413</v>
       </c>
       <c r="T9">
-        <v>1.039825159235852</v>
+        <v>1.048459514821342</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>71.79032814246982</v>
+        <v>62.81653712466108</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.086922847632423</v>
+        <v>0.08673611332757745</v>
       </c>
       <c r="C10">
-        <v>2492.800414500352</v>
+        <v>2471.962807148264</v>
       </c>
       <c r="D10">
-        <v>2227.592414500352</v>
+        <v>2237.753807148264</v>
       </c>
       <c r="E10">
-        <v>-1686.408</v>
+        <v>-1655.409</v>
       </c>
       <c r="F10">
-        <v>247.992</v>
+        <v>278.991</v>
       </c>
       <c r="G10">
         <v>513.2</v>
@@ -2101,28 +2101,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M10">
-        <v>12.4739976</v>
+        <v>14.0332473</v>
       </c>
       <c r="N10">
-        <v>771.0993357333334</v>
+        <v>769.5400860333334</v>
       </c>
       <c r="O10">
-        <v>192.3121743318934</v>
+        <v>191.9232974567134</v>
       </c>
       <c r="P10">
-        <v>578.78716140144</v>
+        <v>577.61678857662</v>
       </c>
       <c r="Q10">
-        <v>586.04716140144</v>
+        <v>584.87678857662</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09119829699176413</v>
+        <v>0.09158038145887631</v>
       </c>
       <c r="T10">
-        <v>1.048459514821342</v>
+        <v>1.057283636463656</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.81653712466108</v>
+        <v>55.83692188858764</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08673611332757745</v>
+        <v>0.08654937902273192</v>
       </c>
       <c r="C11">
-        <v>2471.962807148264</v>
+        <v>2451.21832909718</v>
       </c>
       <c r="D11">
-        <v>2237.753807148264</v>
+        <v>2248.008329097179</v>
       </c>
       <c r="E11">
-        <v>-1655.409</v>
+        <v>-1624.41</v>
       </c>
       <c r="F11">
-        <v>278.991</v>
+        <v>309.99</v>
       </c>
       <c r="G11">
         <v>513.2</v>
@@ -2183,28 +2183,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M11">
-        <v>14.0332473</v>
+        <v>15.592497</v>
       </c>
       <c r="N11">
-        <v>769.5400860333334</v>
+        <v>767.9808363333334</v>
       </c>
       <c r="O11">
-        <v>191.9232974567134</v>
+        <v>191.5344205815334</v>
       </c>
       <c r="P11">
-        <v>577.61678857662</v>
+        <v>576.4464157518</v>
       </c>
       <c r="Q11">
-        <v>584.87678857662</v>
+        <v>583.7064157518</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09158038145887631</v>
+        <v>0.09197095669192434</v>
       </c>
       <c r="T11">
-        <v>1.057283636463656</v>
+        <v>1.066303849698022</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.83692188858764</v>
+        <v>50.25322969972888</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08654937902273192</v>
+        <v>0.08636264471788635</v>
       </c>
       <c r="C12">
-        <v>2451.218329097179</v>
+        <v>2430.568266538034</v>
       </c>
       <c r="D12">
-        <v>2248.008329097179</v>
+        <v>2258.357266538034</v>
       </c>
       <c r="E12">
-        <v>-1624.41</v>
+        <v>-1593.411</v>
       </c>
       <c r="F12">
-        <v>309.9900000000001</v>
+        <v>340.9890000000001</v>
       </c>
       <c r="G12">
         <v>513.2</v>
@@ -2265,28 +2265,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M12">
-        <v>15.592497</v>
+        <v>17.1517467</v>
       </c>
       <c r="N12">
-        <v>767.9808363333334</v>
+        <v>766.4215866333334</v>
       </c>
       <c r="O12">
-        <v>191.5344205815334</v>
+        <v>191.1455437063534</v>
       </c>
       <c r="P12">
-        <v>576.4464157518</v>
+        <v>575.27604292698</v>
       </c>
       <c r="Q12">
-        <v>583.7064157518</v>
+        <v>582.53604292698</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09197095669192434</v>
+        <v>0.09237030889650152</v>
       </c>
       <c r="T12">
-        <v>1.066303849698022</v>
+        <v>1.075526764353384</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>50.25322969972886</v>
+        <v>45.68475427248079</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08636264471788635</v>
+        <v>0.0861759104130408</v>
       </c>
       <c r="C13">
-        <v>2430.568266538034</v>
+        <v>2410.013929455744</v>
       </c>
       <c r="D13">
-        <v>2258.357266538034</v>
+        <v>2268.801929455744</v>
       </c>
       <c r="E13">
-        <v>-1593.411</v>
+        <v>-1562.412</v>
       </c>
       <c r="F13">
-        <v>340.9890000000001</v>
+        <v>371.9880000000001</v>
       </c>
       <c r="G13">
         <v>513.2</v>
@@ -2347,28 +2347,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M13">
-        <v>17.1517467</v>
+        <v>18.7109964</v>
       </c>
       <c r="N13">
-        <v>766.4215866333334</v>
+        <v>764.8623369333334</v>
       </c>
       <c r="O13">
-        <v>191.1455437063534</v>
+        <v>190.7566668311734</v>
       </c>
       <c r="P13">
-        <v>575.27604292698</v>
+        <v>574.10567010216</v>
       </c>
       <c r="Q13">
-        <v>582.53604292698</v>
+        <v>581.36567010216</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09237030889650152</v>
+        <v>0.09277873728754638</v>
       </c>
       <c r="T13">
-        <v>1.075526764353384</v>
+        <v>1.084959290705459</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.68475427248079</v>
+        <v>41.87769141644073</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0861759104130408</v>
+        <v>0.08598917610819527</v>
       </c>
       <c r="C14">
-        <v>2410.013929455744</v>
+        <v>2389.556652181996</v>
       </c>
       <c r="D14">
-        <v>2268.801929455744</v>
+        <v>2279.343652181996</v>
       </c>
       <c r="E14">
-        <v>-1562.412</v>
+        <v>-1531.413</v>
       </c>
       <c r="F14">
-        <v>371.9880000000001</v>
+        <v>402.9870000000001</v>
       </c>
       <c r="G14">
         <v>513.2</v>
@@ -2429,28 +2429,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M14">
-        <v>18.7109964</v>
+        <v>20.2702461</v>
       </c>
       <c r="N14">
-        <v>764.8623369333334</v>
+        <v>763.3030872333334</v>
       </c>
       <c r="O14">
-        <v>190.7566668311734</v>
+        <v>190.3677899559933</v>
       </c>
       <c r="P14">
-        <v>574.10567010216</v>
+        <v>572.9352972773401</v>
       </c>
       <c r="Q14">
-        <v>581.36567010216</v>
+        <v>580.19529727734</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09277873728754638</v>
+        <v>0.09319655483700606</v>
       </c>
       <c r="T14">
-        <v>1.084959290705459</v>
+        <v>1.094608656743789</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.87769141644073</v>
+        <v>38.65633053825298</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08598917610819527</v>
+        <v>0.08580244180334973</v>
       </c>
       <c r="C15">
-        <v>2389.556652181996</v>
+        <v>2369.197793963508</v>
       </c>
       <c r="D15">
-        <v>2279.343652181996</v>
+        <v>2289.983793963508</v>
       </c>
       <c r="E15">
-        <v>-1531.413</v>
+        <v>-1500.414</v>
       </c>
       <c r="F15">
-        <v>402.9870000000001</v>
+        <v>433.9860000000001</v>
       </c>
       <c r="G15">
         <v>513.2</v>
@@ -2511,28 +2511,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M15">
-        <v>20.2702461</v>
+        <v>21.8294958</v>
       </c>
       <c r="N15">
-        <v>763.3030872333334</v>
+        <v>761.7438375333334</v>
       </c>
       <c r="O15">
-        <v>190.3677899559933</v>
+        <v>189.9789130808134</v>
       </c>
       <c r="P15">
-        <v>572.9352972773401</v>
+        <v>571.7649244525201</v>
       </c>
       <c r="Q15">
-        <v>580.19529727734</v>
+        <v>579.0249244525201</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09319655483700606</v>
+        <v>0.09362408907366249</v>
       </c>
       <c r="T15">
-        <v>1.094608656743789</v>
+        <v>1.104482426643476</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.65633053825298</v>
+        <v>35.8951640712349</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08580244180334973</v>
+        <v>0.0856157074985042</v>
       </c>
       <c r="C16">
-        <v>2369.197793963508</v>
+        <v>2348.938739546275</v>
       </c>
       <c r="D16">
-        <v>2289.983793963508</v>
+        <v>2300.723739546275</v>
       </c>
       <c r="E16">
-        <v>-1500.414</v>
+        <v>-1469.415</v>
       </c>
       <c r="F16">
-        <v>433.9860000000001</v>
+        <v>464.9850000000001</v>
       </c>
       <c r="G16">
         <v>513.2</v>
@@ -2593,28 +2593,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M16">
-        <v>21.8294958</v>
+        <v>23.38874550000001</v>
       </c>
       <c r="N16">
-        <v>761.7438375333334</v>
+        <v>760.1845878333334</v>
       </c>
       <c r="O16">
-        <v>189.9789130808134</v>
+        <v>189.5900362056333</v>
       </c>
       <c r="P16">
-        <v>571.7649244525201</v>
+        <v>570.5945516277</v>
       </c>
       <c r="Q16">
-        <v>579.0249244525201</v>
+        <v>577.8545516276999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09362408907366249</v>
+        <v>0.0940616829394167</v>
       </c>
       <c r="T16">
-        <v>1.104482426643476</v>
+        <v>1.114588520540801</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.8951640712349</v>
+        <v>33.50215313315258</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0856157074985042</v>
+        <v>0.08542897319365865</v>
       </c>
       <c r="C17">
-        <v>2348.938739546275</v>
+        <v>2328.780899776351</v>
       </c>
       <c r="D17">
-        <v>2300.723739546275</v>
+        <v>2311.564899776351</v>
       </c>
       <c r="E17">
-        <v>-1469.415</v>
+        <v>-1438.416</v>
       </c>
       <c r="F17">
-        <v>464.9850000000001</v>
+        <v>495.9840000000001</v>
       </c>
       <c r="G17">
         <v>513.2</v>
@@ -2675,28 +2675,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M17">
-        <v>23.3887455</v>
+        <v>24.9479952</v>
       </c>
       <c r="N17">
-        <v>760.1845878333334</v>
+        <v>758.6253381333333</v>
       </c>
       <c r="O17">
-        <v>189.5900362056333</v>
+        <v>189.2011593304534</v>
       </c>
       <c r="P17">
-        <v>570.5945516277</v>
+        <v>569.42417880288</v>
       </c>
       <c r="Q17">
-        <v>577.8545516276999</v>
+        <v>576.68417880288</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0940616829394167</v>
+        <v>0.09450969570673649</v>
       </c>
       <c r="T17">
-        <v>1.114588520540801</v>
+        <v>1.124935235721397</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.50215313315258</v>
+        <v>31.40826856233054</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08542897319365865</v>
+        <v>0.08524223888881312</v>
       </c>
       <c r="C18">
-        <v>2328.780899776351</v>
+        <v>2308.725712217674</v>
       </c>
       <c r="D18">
-        <v>2311.564899776351</v>
+        <v>2322.508712217675</v>
       </c>
       <c r="E18">
-        <v>-1438.416</v>
+        <v>-1407.417</v>
       </c>
       <c r="F18">
-        <v>495.9840000000001</v>
+        <v>526.9830000000002</v>
       </c>
       <c r="G18">
         <v>513.2</v>
@@ -2757,28 +2757,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M18">
-        <v>24.9479952</v>
+        <v>26.50724490000001</v>
       </c>
       <c r="N18">
-        <v>758.6253381333333</v>
+        <v>757.0660884333333</v>
       </c>
       <c r="O18">
-        <v>189.2011593304534</v>
+        <v>188.8122824552733</v>
       </c>
       <c r="P18">
-        <v>569.42417880288</v>
+        <v>568.25380597806</v>
       </c>
       <c r="Q18">
-        <v>576.68417880288</v>
+        <v>575.51380597806</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09450969570673649</v>
+        <v>0.09496850396242545</v>
       </c>
       <c r="T18">
-        <v>1.124935235721397</v>
+        <v>1.13553126934008</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.40826856233054</v>
+        <v>29.56072335278168</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08524223888881312</v>
+        <v>0.08505550458396756</v>
       </c>
       <c r="C19">
-        <v>2308.725712217674</v>
+        <v>2288.774641787553</v>
       </c>
       <c r="D19">
-        <v>2322.508712217675</v>
+        <v>2333.556641787553</v>
       </c>
       <c r="E19">
-        <v>-1407.417</v>
+        <v>-1376.418</v>
       </c>
       <c r="F19">
-        <v>526.9830000000002</v>
+        <v>557.9820000000002</v>
       </c>
       <c r="G19">
         <v>513.2</v>
@@ -2839,28 +2839,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M19">
-        <v>26.50724490000001</v>
+        <v>28.06649460000001</v>
       </c>
       <c r="N19">
-        <v>757.0660884333333</v>
+        <v>755.5068387333333</v>
       </c>
       <c r="O19">
-        <v>188.8122824552733</v>
+        <v>188.4234055800933</v>
       </c>
       <c r="P19">
-        <v>568.25380597806</v>
+        <v>567.08343315324</v>
       </c>
       <c r="Q19">
-        <v>575.51380597806</v>
+        <v>574.34343315324</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09496850396242545</v>
+        <v>0.09543850266337509</v>
       </c>
       <c r="T19">
-        <v>1.13553126934008</v>
+        <v>1.14638574280312</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.56072335278168</v>
+        <v>27.91846094429381</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08505550458396757</v>
+        <v>0.08486877027912203</v>
       </c>
       <c r="C20">
-        <v>2288.774641787552</v>
+        <v>2268.929181410343</v>
       </c>
       <c r="D20">
-        <v>2333.556641787553</v>
+        <v>2344.710181410343</v>
       </c>
       <c r="E20">
-        <v>-1376.418</v>
+        <v>-1345.419</v>
       </c>
       <c r="F20">
-        <v>557.9820000000001</v>
+        <v>588.9810000000001</v>
       </c>
       <c r="G20">
         <v>513.2</v>
@@ -2921,28 +2921,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M20">
-        <v>28.0664946</v>
+        <v>29.6257443</v>
       </c>
       <c r="N20">
-        <v>755.5068387333333</v>
+        <v>753.9475890333334</v>
       </c>
       <c r="O20">
-        <v>188.4234055800933</v>
+        <v>188.0345287049134</v>
       </c>
       <c r="P20">
-        <v>567.08343315324</v>
+        <v>565.9130603284201</v>
       </c>
       <c r="Q20">
-        <v>574.34343315324</v>
+        <v>573.1730603284201</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09543850266337509</v>
+        <v>0.09592010627052103</v>
       </c>
       <c r="T20">
-        <v>1.14638574280312</v>
+        <v>1.157508227956606</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.91846094429382</v>
+        <v>26.4490682630152</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08486877027912203</v>
+        <v>0.0846820359742765</v>
       </c>
       <c r="C21">
-        <v>2268.929181410343</v>
+        <v>2249.190852689995</v>
       </c>
       <c r="D21">
-        <v>2344.710181410343</v>
+        <v>2355.970852689994</v>
       </c>
       <c r="E21">
-        <v>-1345.419</v>
+        <v>-1314.42</v>
       </c>
       <c r="F21">
-        <v>588.9810000000001</v>
+        <v>619.9800000000001</v>
       </c>
       <c r="G21">
         <v>513.2</v>
@@ -3003,28 +3003,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M21">
-        <v>29.6257443</v>
+        <v>31.18499400000001</v>
       </c>
       <c r="N21">
-        <v>753.9475890333334</v>
+        <v>752.3883393333334</v>
       </c>
       <c r="O21">
-        <v>188.0345287049134</v>
+        <v>187.6456518297334</v>
       </c>
       <c r="P21">
-        <v>565.9130603284201</v>
+        <v>564.7426875036001</v>
       </c>
       <c r="Q21">
-        <v>573.1730603284201</v>
+        <v>572.0026875036001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09592010627052103</v>
+        <v>0.09641374996784562</v>
       </c>
       <c r="T21">
-        <v>1.157508227956606</v>
+        <v>1.168908775238929</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.4490682630152</v>
+        <v>25.12661484986443</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0846820359742765</v>
+        <v>0.08449530166943096</v>
       </c>
       <c r="C22">
-        <v>2249.190852689995</v>
+        <v>2229.561206602047</v>
       </c>
       <c r="D22">
-        <v>2355.970852689994</v>
+        <v>2367.340206602047</v>
       </c>
       <c r="E22">
-        <v>-1314.42</v>
+        <v>-1283.421</v>
       </c>
       <c r="F22">
-        <v>619.9800000000001</v>
+        <v>650.9790000000002</v>
       </c>
       <c r="G22">
         <v>513.2</v>
@@ -3085,28 +3085,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M22">
-        <v>31.18499400000001</v>
+        <v>32.74424370000001</v>
       </c>
       <c r="N22">
-        <v>752.3883393333334</v>
+        <v>750.8290896333334</v>
       </c>
       <c r="O22">
-        <v>187.6456518297334</v>
+        <v>187.2567749545534</v>
       </c>
       <c r="P22">
-        <v>564.7426875036001</v>
+        <v>563.57231467878</v>
       </c>
       <c r="Q22">
-        <v>572.0026875036001</v>
+        <v>570.83231467878</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09641374996784562</v>
+        <v>0.09691989097396324</v>
       </c>
       <c r="T22">
-        <v>1.168908775238929</v>
+        <v>1.180597943971437</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.12661484986443</v>
+        <v>23.93010938082327</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08449530166943096</v>
+        <v>0.0843085673645854</v>
       </c>
       <c r="C23">
-        <v>2229.561206602047</v>
+        <v>2210.041824205773</v>
       </c>
       <c r="D23">
-        <v>2367.340206602047</v>
+        <v>2378.819824205773</v>
       </c>
       <c r="E23">
-        <v>-1283.421</v>
+        <v>-1252.422</v>
       </c>
       <c r="F23">
-        <v>650.979</v>
+        <v>681.9780000000002</v>
       </c>
       <c r="G23">
         <v>513.2</v>
@@ -3167,28 +3167,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M23">
-        <v>32.7442437</v>
+        <v>34.30349340000001</v>
       </c>
       <c r="N23">
-        <v>750.8290896333334</v>
+        <v>749.2698399333334</v>
       </c>
       <c r="O23">
-        <v>187.2567749545534</v>
+        <v>186.8678980793734</v>
       </c>
       <c r="P23">
-        <v>563.57231467878</v>
+        <v>562.40194185396</v>
       </c>
       <c r="Q23">
-        <v>570.83231467878</v>
+        <v>569.66194185396</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09691989097396324</v>
+        <v>0.09743900995459667</v>
       </c>
       <c r="T23">
-        <v>1.180597943971437</v>
+        <v>1.192586834979138</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.93010938082327</v>
+        <v>22.84237713624039</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0843085673645854</v>
+        <v>0.08412183305973987</v>
       </c>
       <c r="C24">
-        <v>2210.041824205773</v>
+        <v>2190.63431737713</v>
       </c>
       <c r="D24">
-        <v>2378.819824205773</v>
+        <v>2390.41131737713</v>
       </c>
       <c r="E24">
-        <v>-1252.422</v>
+        <v>-1221.423</v>
       </c>
       <c r="F24">
-        <v>681.9780000000002</v>
+        <v>712.9770000000002</v>
       </c>
       <c r="G24">
         <v>513.2</v>
@@ -3249,28 +3249,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M24">
-        <v>34.30349340000001</v>
+        <v>35.86274310000001</v>
       </c>
       <c r="N24">
-        <v>749.2698399333334</v>
+        <v>747.7105902333334</v>
       </c>
       <c r="O24">
-        <v>186.8678980793734</v>
+        <v>186.4790212041933</v>
       </c>
       <c r="P24">
-        <v>562.40194185396</v>
+        <v>561.23156902914</v>
       </c>
       <c r="Q24">
-        <v>569.66194185396</v>
+        <v>568.49156902914</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09743900995459667</v>
+        <v>0.09797161254511672</v>
       </c>
       <c r="T24">
-        <v>1.192586834979138</v>
+        <v>1.204887125753273</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.84237713624039</v>
+        <v>21.84923030422994</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08412183305973987</v>
+        <v>0.08393509875489433</v>
       </c>
       <c r="C25">
-        <v>2190.63431737713</v>
+        <v>2171.340329563261</v>
       </c>
       <c r="D25">
-        <v>2390.41131737713</v>
+        <v>2402.116329563261</v>
       </c>
       <c r="E25">
-        <v>-1221.423</v>
+        <v>-1190.424</v>
       </c>
       <c r="F25">
-        <v>712.9770000000002</v>
+        <v>743.9760000000002</v>
       </c>
       <c r="G25">
         <v>513.2</v>
@@ -3331,28 +3331,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M25">
-        <v>35.86274310000001</v>
+        <v>37.42199280000001</v>
       </c>
       <c r="N25">
-        <v>747.7105902333334</v>
+        <v>746.1513405333334</v>
       </c>
       <c r="O25">
-        <v>186.4790212041933</v>
+        <v>186.0901443290134</v>
       </c>
       <c r="P25">
-        <v>561.23156902914</v>
+        <v>560.06119620432</v>
       </c>
       <c r="Q25">
-        <v>568.49156902914</v>
+        <v>567.32119620432</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09797161254511672</v>
+        <v>0.09851823099328201</v>
       </c>
       <c r="T25">
-        <v>1.204887125753273</v>
+        <v>1.217511108389885</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.84923030422994</v>
+        <v>20.93884570822036</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08393509875489433</v>
+        <v>0.0837483644500488</v>
       </c>
       <c r="C26">
-        <v>2171.340329563261</v>
+        <v>2152.161536559257</v>
       </c>
       <c r="D26">
-        <v>2402.116329563261</v>
+        <v>2413.936536559258</v>
       </c>
       <c r="E26">
-        <v>-1190.424</v>
+        <v>-1159.425</v>
       </c>
       <c r="F26">
-        <v>743.9760000000001</v>
+        <v>774.9750000000001</v>
       </c>
       <c r="G26">
         <v>513.2</v>
@@ -3413,28 +3413,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M26">
-        <v>37.42199280000001</v>
+        <v>38.98124250000001</v>
       </c>
       <c r="N26">
-        <v>746.1513405333334</v>
+        <v>744.5920908333334</v>
       </c>
       <c r="O26">
-        <v>186.0901443290134</v>
+        <v>185.7012674538333</v>
       </c>
       <c r="P26">
-        <v>560.06119620432</v>
+        <v>558.8908233795</v>
       </c>
       <c r="Q26">
-        <v>567.32119620432</v>
+        <v>566.1508233795</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09851823099328201</v>
+        <v>0.09907942593339839</v>
       </c>
       <c r="T26">
-        <v>1.217511108389885</v>
+        <v>1.230471730563473</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.93884570822036</v>
+        <v>20.10129187989154</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0837483644500488</v>
+        <v>0.08356163014520325</v>
       </c>
       <c r="C27">
-        <v>2152.161536559257</v>
+        <v>2133.099647307981</v>
       </c>
       <c r="D27">
-        <v>2413.936536559258</v>
+        <v>2425.873647307982</v>
       </c>
       <c r="E27">
-        <v>-1159.425</v>
+        <v>-1128.426</v>
       </c>
       <c r="F27">
-        <v>774.9750000000001</v>
+        <v>805.9740000000002</v>
       </c>
       <c r="G27">
         <v>513.2</v>
@@ -3495,28 +3495,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M27">
-        <v>38.98124250000001</v>
+        <v>40.5404922</v>
       </c>
       <c r="N27">
-        <v>744.5920908333334</v>
+        <v>743.0328411333334</v>
       </c>
       <c r="O27">
-        <v>185.7012674538333</v>
+        <v>185.3123905786533</v>
       </c>
       <c r="P27">
-        <v>558.8908233795</v>
+        <v>557.72045055468</v>
       </c>
       <c r="Q27">
-        <v>566.1508233795</v>
+        <v>564.98045055468</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09907942593339839</v>
+        <v>0.09965578830432871</v>
       </c>
       <c r="T27">
-        <v>1.230471730563473</v>
+        <v>1.243782639822834</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.10129187989154</v>
+        <v>19.32816526912649</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08356163014520325</v>
+        <v>0.0833748958403577</v>
       </c>
       <c r="C28">
-        <v>2133.099647307981</v>
+        <v>2114.156404723725</v>
       </c>
       <c r="D28">
-        <v>2425.873647307982</v>
+        <v>2437.929404723725</v>
       </c>
       <c r="E28">
-        <v>-1128.426</v>
+        <v>-1097.427</v>
       </c>
       <c r="F28">
-        <v>805.9740000000002</v>
+        <v>836.9730000000002</v>
       </c>
       <c r="G28">
         <v>513.2</v>
@@ -3577,28 +3577,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M28">
-        <v>40.5404922</v>
+        <v>42.09974190000001</v>
       </c>
       <c r="N28">
-        <v>743.0328411333334</v>
+        <v>741.4735914333334</v>
       </c>
       <c r="O28">
-        <v>185.3123905786533</v>
+        <v>184.9235137034733</v>
       </c>
       <c r="P28">
-        <v>557.72045055468</v>
+        <v>556.55007772986</v>
       </c>
       <c r="Q28">
-        <v>564.98045055468</v>
+        <v>563.81007772986</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09965578830432871</v>
+        <v>0.1002479414251475</v>
       </c>
       <c r="T28">
-        <v>1.243782639822834</v>
+        <v>1.257458231527657</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.32816526912649</v>
+        <v>18.61230729619588</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0833748958403577</v>
+        <v>0.08318816153551217</v>
       </c>
       <c r="C29">
-        <v>2114.156404723725</v>
+        <v>2095.333586540559</v>
       </c>
       <c r="D29">
-        <v>2437.929404723725</v>
+        <v>2450.105586540559</v>
       </c>
       <c r="E29">
-        <v>-1097.427</v>
+        <v>-1066.428</v>
       </c>
       <c r="F29">
-        <v>836.9730000000002</v>
+        <v>867.9720000000002</v>
       </c>
       <c r="G29">
         <v>513.2</v>
@@ -3659,28 +3659,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M29">
-        <v>42.09974190000001</v>
+        <v>43.65899160000001</v>
       </c>
       <c r="N29">
-        <v>741.4735914333334</v>
+        <v>739.9143417333333</v>
       </c>
       <c r="O29">
-        <v>184.9235137034733</v>
+        <v>184.5346368282933</v>
       </c>
       <c r="P29">
-        <v>556.55007772986</v>
+        <v>555.3797049050399</v>
       </c>
       <c r="Q29">
-        <v>563.81007772986</v>
+        <v>562.6397049050399</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1002479414251475</v>
+        <v>0.1008565432437669</v>
       </c>
       <c r="T29">
-        <v>1.257458231527657</v>
+        <v>1.271513700779836</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.61230729619588</v>
+        <v>17.94758203561745</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08318816153551217</v>
+        <v>0.08300142723066663</v>
       </c>
       <c r="C30">
-        <v>2095.333586540559</v>
+        <v>2076.633006186235</v>
       </c>
       <c r="D30">
-        <v>2450.105586540559</v>
+        <v>2462.404006186236</v>
       </c>
       <c r="E30">
-        <v>-1066.428</v>
+        <v>-1035.429</v>
       </c>
       <c r="F30">
-        <v>867.9720000000002</v>
+        <v>898.9710000000002</v>
       </c>
       <c r="G30">
         <v>513.2</v>
@@ -3741,28 +3741,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M30">
-        <v>43.65899160000001</v>
+        <v>45.21824130000001</v>
       </c>
       <c r="N30">
-        <v>739.9143417333333</v>
+        <v>738.3550920333333</v>
       </c>
       <c r="O30">
-        <v>184.5346368282933</v>
+        <v>184.1457599531134</v>
       </c>
       <c r="P30">
-        <v>555.3797049050399</v>
+        <v>554.20933208022</v>
       </c>
       <c r="Q30">
-        <v>562.6397049050399</v>
+        <v>561.4693320802199</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1008565432437669</v>
+        <v>0.1014822887755868</v>
       </c>
       <c r="T30">
-        <v>1.271513700779836</v>
+        <v>1.285965098743344</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.94758203561745</v>
+        <v>17.32869989645823</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08300142723066663</v>
+        <v>0.08281469292582108</v>
       </c>
       <c r="C31">
-        <v>2076.633006186236</v>
+        <v>2058.056513682531</v>
       </c>
       <c r="D31">
-        <v>2462.404006186236</v>
+        <v>2474.826513682531</v>
       </c>
       <c r="E31">
-        <v>-1035.429</v>
+        <v>-1004.43</v>
       </c>
       <c r="F31">
-        <v>898.9710000000001</v>
+        <v>929.9700000000001</v>
       </c>
       <c r="G31">
         <v>513.2</v>
@@ -3823,28 +3823,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M31">
-        <v>45.2182413</v>
+        <v>46.777491</v>
       </c>
       <c r="N31">
-        <v>738.3550920333333</v>
+        <v>736.7958423333333</v>
       </c>
       <c r="O31">
-        <v>184.1457599531134</v>
+        <v>183.7568830779333</v>
       </c>
       <c r="P31">
-        <v>554.20933208022</v>
+        <v>553.0389592554</v>
       </c>
       <c r="Q31">
-        <v>561.4693320802199</v>
+        <v>560.2989592554</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1014822887755868</v>
+        <v>0.102125912751173</v>
       </c>
       <c r="T31">
-        <v>1.285965098743344</v>
+        <v>1.300829393791524</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.32869989645823</v>
+        <v>16.75107656657629</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08281469292582108</v>
+        <v>0.08262795862097555</v>
       </c>
       <c r="C32">
-        <v>2058.056513682531</v>
+        <v>2039.605996572989</v>
       </c>
       <c r="D32">
-        <v>2474.826513682531</v>
+        <v>2487.374996572989</v>
       </c>
       <c r="E32">
-        <v>-1004.43</v>
+        <v>-973.4310000000002</v>
       </c>
       <c r="F32">
-        <v>929.9700000000001</v>
+        <v>960.9690000000002</v>
       </c>
       <c r="G32">
         <v>513.2</v>
@@ -3905,28 +3905,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M32">
-        <v>46.777491</v>
+        <v>48.33674070000001</v>
       </c>
       <c r="N32">
-        <v>736.7958423333333</v>
+        <v>735.2365926333334</v>
       </c>
       <c r="O32">
-        <v>183.7568830779333</v>
+        <v>183.3680062027534</v>
       </c>
       <c r="P32">
-        <v>553.0389592554</v>
+        <v>551.8685864305801</v>
       </c>
       <c r="Q32">
-        <v>560.2989592554</v>
+        <v>559.1285864305801</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.102125912751173</v>
+        <v>0.1027881924941675</v>
       </c>
       <c r="T32">
-        <v>1.300829393791524</v>
+        <v>1.316124537971535</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.75107656657629</v>
+        <v>16.21071925797705</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08262795862097555</v>
+        <v>0.08244122431612999</v>
       </c>
       <c r="C33">
-        <v>2039.605996572989</v>
+        <v>2021.283380879034</v>
       </c>
       <c r="D33">
-        <v>2487.374996572989</v>
+        <v>2500.051380879035</v>
       </c>
       <c r="E33">
-        <v>-973.4310000000002</v>
+        <v>-942.4320000000001</v>
       </c>
       <c r="F33">
-        <v>960.9690000000002</v>
+        <v>991.9680000000002</v>
       </c>
       <c r="G33">
         <v>513.2</v>
@@ -3987,28 +3987,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M33">
-        <v>48.33674070000001</v>
+        <v>49.89599040000001</v>
       </c>
       <c r="N33">
-        <v>735.2365926333334</v>
+        <v>733.6773429333334</v>
       </c>
       <c r="O33">
-        <v>183.3680062027534</v>
+        <v>182.9791293275734</v>
       </c>
       <c r="P33">
-        <v>551.8685864305801</v>
+        <v>550.6982136057601</v>
       </c>
       <c r="Q33">
-        <v>559.1285864305801</v>
+        <v>557.9582136057601</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1027881924941675</v>
+        <v>0.1034699510531324</v>
       </c>
       <c r="T33">
-        <v>1.316124537971535</v>
+        <v>1.331869539333311</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.21071925797705</v>
+        <v>15.70413428116527</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08244122431612999</v>
+        <v>0.08225449001128443</v>
       </c>
       <c r="C34">
-        <v>2021.283380879034</v>
+        <v>2003.09063208546</v>
       </c>
       <c r="D34">
-        <v>2500.051380879035</v>
+        <v>2512.857632085459</v>
       </c>
       <c r="E34">
-        <v>-942.4320000000001</v>
+        <v>-911.4330000000001</v>
       </c>
       <c r="F34">
-        <v>991.9680000000002</v>
+        <v>1022.967</v>
       </c>
       <c r="G34">
         <v>513.2</v>
@@ -4069,28 +4069,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M34">
-        <v>49.89599040000001</v>
+        <v>51.4552401</v>
       </c>
       <c r="N34">
-        <v>733.6773429333334</v>
+        <v>732.1180932333334</v>
       </c>
       <c r="O34">
-        <v>182.9791293275734</v>
+        <v>182.5902524523934</v>
       </c>
       <c r="P34">
-        <v>550.6982136057601</v>
+        <v>549.5278407809401</v>
       </c>
       <c r="Q34">
-        <v>557.9582136057601</v>
+        <v>556.7878407809401</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1034699510531324</v>
+        <v>0.1041720606138574</v>
       </c>
       <c r="T34">
-        <v>1.331869539333311</v>
+        <v>1.348084540735737</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.70413428116527</v>
+        <v>15.22825142416026</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08225449001128443</v>
+        <v>0.0820677557064389</v>
       </c>
       <c r="C35">
-        <v>2003.09063208546</v>
+        <v>1985.029756156367</v>
       </c>
       <c r="D35">
-        <v>2512.857632085459</v>
+        <v>2525.795756156367</v>
       </c>
       <c r="E35">
-        <v>-911.4330000000001</v>
+        <v>-880.434</v>
       </c>
       <c r="F35">
-        <v>1022.967</v>
+        <v>1053.966</v>
       </c>
       <c r="G35">
         <v>513.2</v>
@@ -4151,28 +4151,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M35">
-        <v>51.4552401</v>
+        <v>53.01448980000001</v>
       </c>
       <c r="N35">
-        <v>732.1180932333334</v>
+        <v>730.5588435333334</v>
       </c>
       <c r="O35">
-        <v>182.5902524523934</v>
+        <v>182.2013755772134</v>
       </c>
       <c r="P35">
-        <v>549.5278407809401</v>
+        <v>548.35746795612</v>
       </c>
       <c r="Q35">
-        <v>556.7878407809401</v>
+        <v>555.61746795612</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1041720606138574</v>
+        <v>0.1048954462218771</v>
       </c>
       <c r="T35">
-        <v>1.348084540735737</v>
+        <v>1.364790905817024</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.22825142416026</v>
+        <v>14.78036167639084</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0820677557064389</v>
+        <v>0.08188102140159337</v>
       </c>
       <c r="C36">
-        <v>1985.029756156367</v>
+        <v>1967.10280058266</v>
       </c>
       <c r="D36">
-        <v>2525.795756156367</v>
+        <v>2538.86780058266</v>
       </c>
       <c r="E36">
-        <v>-880.434</v>
+        <v>-849.4349999999999</v>
       </c>
       <c r="F36">
-        <v>1053.966</v>
+        <v>1084.965</v>
       </c>
       <c r="G36">
         <v>513.2</v>
@@ -4233,28 +4233,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M36">
-        <v>53.01448980000001</v>
+        <v>54.57373950000002</v>
       </c>
       <c r="N36">
-        <v>730.5588435333334</v>
+        <v>728.9995938333334</v>
       </c>
       <c r="O36">
-        <v>182.2013755772134</v>
+        <v>181.8124987020334</v>
       </c>
       <c r="P36">
-        <v>548.35746795612</v>
+        <v>547.1870951313</v>
       </c>
       <c r="Q36">
-        <v>555.61746795612</v>
+        <v>554.4470951313</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1048954462218771</v>
+        <v>0.1056410898486052</v>
       </c>
       <c r="T36">
-        <v>1.364790905817024</v>
+        <v>1.382011312900813</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.78036167639084</v>
+        <v>14.35806562849396</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08188102140159337</v>
+        <v>0.08169428709674781</v>
       </c>
       <c r="C37">
-        <v>1967.10280058266</v>
+        <v>1949.311855462221</v>
       </c>
       <c r="D37">
-        <v>2538.86780058266</v>
+        <v>2552.075855462221</v>
       </c>
       <c r="E37">
-        <v>-849.4349999999999</v>
+        <v>-818.4359999999999</v>
       </c>
       <c r="F37">
-        <v>1084.965</v>
+        <v>1115.964</v>
       </c>
       <c r="G37">
         <v>513.2</v>
@@ -4315,28 +4315,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M37">
-        <v>54.57373950000002</v>
+        <v>56.13298920000002</v>
       </c>
       <c r="N37">
-        <v>728.9995938333334</v>
+        <v>727.4403441333334</v>
       </c>
       <c r="O37">
-        <v>181.8124987020334</v>
+        <v>181.4236218268533</v>
       </c>
       <c r="P37">
-        <v>547.1870951313</v>
+        <v>546.01672230648</v>
       </c>
       <c r="Q37">
-        <v>554.4470951313</v>
+        <v>553.27672230648</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1056410898486052</v>
+        <v>0.1064100348386685</v>
       </c>
       <c r="T37">
-        <v>1.382011312900813</v>
+        <v>1.39976985770597</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.35806562849396</v>
+        <v>13.95923047214691</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08169428709674782</v>
+        <v>0.08150755279190229</v>
       </c>
       <c r="C38">
-        <v>1949.31185546222</v>
+        <v>1931.659054613983</v>
       </c>
       <c r="D38">
-        <v>2552.075855462221</v>
+        <v>2565.422054613983</v>
       </c>
       <c r="E38">
-        <v>-818.4360000000001</v>
+        <v>-787.4370000000001</v>
       </c>
       <c r="F38">
-        <v>1115.964</v>
+        <v>1146.963</v>
       </c>
       <c r="G38">
         <v>513.2</v>
@@ -4397,28 +4397,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M38">
-        <v>56.1329892</v>
+        <v>57.69223890000001</v>
       </c>
       <c r="N38">
-        <v>727.4403441333334</v>
+        <v>725.8810944333334</v>
       </c>
       <c r="O38">
-        <v>181.4236218268533</v>
+        <v>181.0347449516734</v>
       </c>
       <c r="P38">
-        <v>546.01672230648</v>
+        <v>544.84634948166</v>
       </c>
       <c r="Q38">
-        <v>553.27672230648</v>
+        <v>552.10634948166</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1064100348386685</v>
+        <v>0.1072033907807973</v>
       </c>
       <c r="T38">
-        <v>1.39976985770597</v>
+        <v>1.418092165838275</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.95923047214691</v>
+        <v>13.58195397289969</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08150755279190229</v>
+        <v>0.08132081848705673</v>
       </c>
       <c r="C39">
-        <v>1931.659054613983</v>
+        <v>1914.146576727159</v>
       </c>
       <c r="D39">
-        <v>2565.422054613983</v>
+        <v>2578.908576727159</v>
       </c>
       <c r="E39">
-        <v>-787.4370000000001</v>
+        <v>-756.4380000000001</v>
       </c>
       <c r="F39">
-        <v>1146.963</v>
+        <v>1177.962</v>
       </c>
       <c r="G39">
         <v>513.2</v>
@@ -4479,28 +4479,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M39">
-        <v>57.69223890000001</v>
+        <v>59.25148860000001</v>
       </c>
       <c r="N39">
-        <v>725.8810944333334</v>
+        <v>724.3218447333334</v>
       </c>
       <c r="O39">
-        <v>181.0347449516734</v>
+        <v>180.6458680764933</v>
       </c>
       <c r="P39">
-        <v>544.84634948166</v>
+        <v>543.67597665684</v>
       </c>
       <c r="Q39">
-        <v>552.10634948166</v>
+        <v>550.93597665684</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1072033907807973</v>
+        <v>0.1080223388500915</v>
       </c>
       <c r="T39">
-        <v>1.418092165838275</v>
+        <v>1.437005516168396</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.58195397289969</v>
+        <v>13.2245341315076</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08132081848705673</v>
+        <v>0.08113408418221121</v>
       </c>
       <c r="C40">
-        <v>1914.146576727159</v>
+        <v>1896.776646546881</v>
       </c>
       <c r="D40">
-        <v>2578.908576727159</v>
+        <v>2592.537646546881</v>
       </c>
       <c r="E40">
-        <v>-756.4380000000001</v>
+        <v>-725.4390000000001</v>
       </c>
       <c r="F40">
-        <v>1177.962</v>
+        <v>1208.961</v>
       </c>
       <c r="G40">
         <v>513.2</v>
@@ -4561,28 +4561,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M40">
-        <v>59.25148860000001</v>
+        <v>60.81073830000001</v>
       </c>
       <c r="N40">
-        <v>724.3218447333334</v>
+        <v>722.7625950333334</v>
       </c>
       <c r="O40">
-        <v>180.6458680764933</v>
+        <v>180.2569912013134</v>
       </c>
       <c r="P40">
-        <v>543.67597665684</v>
+        <v>542.50560383202</v>
       </c>
       <c r="Q40">
-        <v>550.93597665684</v>
+        <v>549.76560383202</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1080223388500915</v>
+        <v>0.1088681376757561</v>
       </c>
       <c r="T40">
-        <v>1.437005516168396</v>
+        <v>1.456538976345406</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.2245341315076</v>
+        <v>12.88544351275099</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08113408418221121</v>
+        <v>0.08139770987736568</v>
       </c>
       <c r="C41">
-        <v>1896.776646546881</v>
+        <v>1846.578109789051</v>
       </c>
       <c r="D41">
-        <v>2592.537646546881</v>
+        <v>2573.338109789051</v>
       </c>
       <c r="E41">
-        <v>-725.4390000000001</v>
+        <v>-694.4400000000001</v>
       </c>
       <c r="F41">
-        <v>1208.961</v>
+        <v>1239.96</v>
       </c>
       <c r="G41">
         <v>513.2</v>
@@ -4643,45 +4643,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M41">
-        <v>60.81073830000001</v>
+        <v>64.22992800000002</v>
       </c>
       <c r="N41">
-        <v>722.7625950333334</v>
+        <v>719.3434053333334</v>
       </c>
       <c r="O41">
-        <v>180.2569912013134</v>
+        <v>179.4042452901334</v>
       </c>
       <c r="P41">
-        <v>542.50560383202</v>
+        <v>539.9391600432</v>
       </c>
       <c r="Q41">
-        <v>549.76560383202</v>
+        <v>547.1991600432</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1088681376757561</v>
+        <v>0.1097421297956095</v>
       </c>
       <c r="T41">
-        <v>1.456538976345406</v>
+        <v>1.47672355186165</v>
       </c>
       <c r="U41">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>12.88544351275099</v>
+        <v>12.1995050863724</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08139770987736568</v>
+        <v>0.08122223457252013</v>
       </c>
       <c r="C42">
-        <v>1846.578109789051</v>
+        <v>1828.326958555097</v>
       </c>
       <c r="D42">
-        <v>2573.338109789051</v>
+        <v>2586.085958555097</v>
       </c>
       <c r="E42">
-        <v>-694.4400000000001</v>
+        <v>-663.441</v>
       </c>
       <c r="F42">
-        <v>1239.96</v>
+        <v>1270.959</v>
       </c>
       <c r="G42">
         <v>513.2</v>
@@ -4725,28 +4725,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M42">
-        <v>64.22992800000002</v>
+        <v>65.83567620000001</v>
       </c>
       <c r="N42">
-        <v>719.3434053333334</v>
+        <v>717.7376571333334</v>
       </c>
       <c r="O42">
-        <v>179.4042452901334</v>
+        <v>179.0037716890534</v>
       </c>
       <c r="P42">
-        <v>539.9391600432</v>
+        <v>538.7338854442801</v>
       </c>
       <c r="Q42">
-        <v>547.1991600432</v>
+        <v>545.9938854442801</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1097421297956095</v>
+        <v>0.1106457487669833</v>
       </c>
       <c r="T42">
-        <v>1.47672355186165</v>
+        <v>1.49759235027675</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.1995050863724</v>
+        <v>11.90195618182674</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08122223457252013</v>
+        <v>0.08104675926767459</v>
       </c>
       <c r="C43">
-        <v>1828.326958555097</v>
+        <v>1810.202737154968</v>
       </c>
       <c r="D43">
-        <v>2586.085958555097</v>
+        <v>2598.960737154968</v>
       </c>
       <c r="E43">
-        <v>-663.441</v>
+        <v>-632.442</v>
       </c>
       <c r="F43">
-        <v>1270.959</v>
+        <v>1301.958</v>
       </c>
       <c r="G43">
         <v>513.2</v>
@@ -4807,28 +4807,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M43">
-        <v>65.83567620000001</v>
+        <v>67.44142440000002</v>
       </c>
       <c r="N43">
-        <v>717.7376571333334</v>
+        <v>716.1319089333333</v>
       </c>
       <c r="O43">
-        <v>179.0037716890534</v>
+        <v>178.6032980879733</v>
       </c>
       <c r="P43">
-        <v>538.7338854442801</v>
+        <v>537.5286108453599</v>
       </c>
       <c r="Q43">
-        <v>545.9938854442801</v>
+        <v>544.7886108453599</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1106457487669833</v>
+        <v>0.111580527013232</v>
       </c>
       <c r="T43">
-        <v>1.49759235027675</v>
+        <v>1.519180762430301</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.90195618182674</v>
+        <v>11.61857627273562</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0810467592676746</v>
+        <v>0.08087128396282905</v>
       </c>
       <c r="C44">
-        <v>1810.202737154967</v>
+        <v>1792.207350826973</v>
       </c>
       <c r="D44">
-        <v>2598.960737154967</v>
+        <v>2611.964350826973</v>
       </c>
       <c r="E44">
-        <v>-632.4420000000002</v>
+        <v>-601.4430000000002</v>
       </c>
       <c r="F44">
-        <v>1301.958</v>
+        <v>1332.957</v>
       </c>
       <c r="G44">
         <v>513.2</v>
@@ -4889,28 +4889,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M44">
-        <v>67.4414244</v>
+        <v>69.04717260000001</v>
       </c>
       <c r="N44">
-        <v>716.1319089333334</v>
+        <v>714.5261607333334</v>
       </c>
       <c r="O44">
-        <v>178.6032980879734</v>
+        <v>178.2028244868934</v>
       </c>
       <c r="P44">
-        <v>537.52861084536</v>
+        <v>536.32333624644</v>
       </c>
       <c r="Q44">
-        <v>544.78861084536</v>
+        <v>543.58333624644</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.111580527013232</v>
+        <v>0.1125481044961913</v>
       </c>
       <c r="T44">
-        <v>1.519180762430301</v>
+        <v>1.541526662729591</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.61857627273563</v>
+        <v>11.34837682453247</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08087128396282905</v>
+        <v>0.08069580865798351</v>
       </c>
       <c r="C45">
-        <v>1792.207350826973</v>
+        <v>1774.342743131769</v>
       </c>
       <c r="D45">
-        <v>2611.964350826973</v>
+        <v>2625.09874313177</v>
       </c>
       <c r="E45">
-        <v>-601.4430000000002</v>
+        <v>-570.444</v>
       </c>
       <c r="F45">
-        <v>1332.957</v>
+        <v>1363.956</v>
       </c>
       <c r="G45">
         <v>513.2</v>
@@ -4971,28 +4971,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M45">
-        <v>69.04717260000001</v>
+        <v>70.65292080000002</v>
       </c>
       <c r="N45">
-        <v>714.5261607333334</v>
+        <v>712.9204125333333</v>
       </c>
       <c r="O45">
-        <v>178.2028244868934</v>
+        <v>177.8023508858133</v>
       </c>
       <c r="P45">
-        <v>536.32333624644</v>
+        <v>535.11806164752</v>
       </c>
       <c r="Q45">
-        <v>543.58333624644</v>
+        <v>542.37806164752</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1125481044961913</v>
+        <v>0.1135502383178277</v>
       </c>
       <c r="T45">
-        <v>1.541526662729591</v>
+        <v>1.564670630896713</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.34837682453247</v>
+        <v>11.09045916942946</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08069580865798351</v>
+        <v>0.08052033335313796</v>
       </c>
       <c r="C46">
-        <v>1774.342743131769</v>
+        <v>1756.610896920748</v>
       </c>
       <c r="D46">
-        <v>2625.09874313177</v>
+        <v>2638.365896920749</v>
       </c>
       <c r="E46">
-        <v>-570.444</v>
+        <v>-539.4449999999999</v>
       </c>
       <c r="F46">
-        <v>1363.956</v>
+        <v>1394.955</v>
       </c>
       <c r="G46">
         <v>513.2</v>
@@ -5053,28 +5053,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M46">
-        <v>70.65292080000002</v>
+        <v>72.25866900000001</v>
       </c>
       <c r="N46">
-        <v>712.9204125333333</v>
+        <v>711.3146643333333</v>
       </c>
       <c r="O46">
-        <v>177.8023508858133</v>
+        <v>177.4018772847333</v>
       </c>
       <c r="P46">
-        <v>535.11806164752</v>
+        <v>533.9127870486</v>
       </c>
       <c r="Q46">
-        <v>542.37806164752</v>
+        <v>541.1727870486</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1135502383178277</v>
+        <v>0.1145888133693417</v>
       </c>
       <c r="T46">
-        <v>1.564670630896713</v>
+        <v>1.588656197906276</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.09045916942946</v>
+        <v>10.84400452121991</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08052033335313796</v>
+        <v>0.08034485804829242</v>
       </c>
       <c r="C47">
-        <v>1756.610896920748</v>
+        <v>1739.013835333957</v>
       </c>
       <c r="D47">
-        <v>2638.365896920749</v>
+        <v>2651.767835333958</v>
       </c>
       <c r="E47">
-        <v>-539.4449999999999</v>
+        <v>-508.4459999999999</v>
       </c>
       <c r="F47">
-        <v>1394.955</v>
+        <v>1425.954</v>
       </c>
       <c r="G47">
         <v>513.2</v>
@@ -5135,28 +5135,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M47">
-        <v>72.25866900000001</v>
+        <v>73.86441720000002</v>
       </c>
       <c r="N47">
-        <v>711.3146643333333</v>
+        <v>709.7089161333333</v>
       </c>
       <c r="O47">
-        <v>177.4018772847333</v>
+        <v>177.0014036836533</v>
       </c>
       <c r="P47">
-        <v>533.9127870486</v>
+        <v>532.7075124496801</v>
       </c>
       <c r="Q47">
-        <v>541.1727870486</v>
+        <v>539.96751244968</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1145888133693417</v>
+        <v>0.1156658541635045</v>
       </c>
       <c r="T47">
-        <v>1.588656197906276</v>
+        <v>1.613530119249526</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.84400452121991</v>
+        <v>10.60826529249774</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08034485804829242</v>
+        <v>0.08016938274344687</v>
       </c>
       <c r="C48">
-        <v>1739.013835333957</v>
+        <v>1721.553622828579</v>
       </c>
       <c r="D48">
-        <v>2651.767835333958</v>
+        <v>2665.306622828579</v>
       </c>
       <c r="E48">
-        <v>-508.4459999999999</v>
+        <v>-477.4469999999999</v>
       </c>
       <c r="F48">
-        <v>1425.954</v>
+        <v>1456.953</v>
       </c>
       <c r="G48">
         <v>513.2</v>
@@ -5217,28 +5217,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M48">
-        <v>73.86441720000002</v>
+        <v>75.47016540000003</v>
       </c>
       <c r="N48">
-        <v>709.7089161333333</v>
+        <v>708.1031679333333</v>
       </c>
       <c r="O48">
-        <v>177.0014036836533</v>
+        <v>176.6009300825733</v>
       </c>
       <c r="P48">
-        <v>532.7075124496801</v>
+        <v>531.50223785076</v>
       </c>
       <c r="Q48">
-        <v>539.96751244968</v>
+        <v>538.76223785076</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1156658541635045</v>
+        <v>0.1167835380065035</v>
       </c>
       <c r="T48">
-        <v>1.613530119249526</v>
+        <v>1.639342679134031</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.60826529249774</v>
+        <v>10.38255752031694</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08016938274344687</v>
+        <v>0.07999390743860135</v>
       </c>
       <c r="C49">
-        <v>1721.553622828579</v>
+        <v>1704.232366239081</v>
       </c>
       <c r="D49">
-        <v>2665.306622828579</v>
+        <v>2678.984366239081</v>
       </c>
       <c r="E49">
-        <v>-477.4469999999999</v>
+        <v>-446.4479999999999</v>
       </c>
       <c r="F49">
-        <v>1456.953</v>
+        <v>1487.952</v>
       </c>
       <c r="G49">
         <v>513.2</v>
@@ -5299,28 +5299,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M49">
-        <v>75.47016540000003</v>
+        <v>77.07591360000002</v>
       </c>
       <c r="N49">
-        <v>708.1031679333333</v>
+        <v>706.4974197333333</v>
       </c>
       <c r="O49">
-        <v>176.6009300825733</v>
+        <v>176.2004564814933</v>
       </c>
       <c r="P49">
-        <v>531.50223785076</v>
+        <v>530.29696325184</v>
       </c>
       <c r="Q49">
-        <v>538.76223785076</v>
+        <v>537.55696325184</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1167835380065035</v>
+        <v>0.117944209689618</v>
       </c>
       <c r="T49">
-        <v>1.639342679134031</v>
+        <v>1.666148029783325</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.38255752031694</v>
+        <v>10.16625423864367</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07999390743860132</v>
+        <v>0.07981843213375581</v>
       </c>
       <c r="C50">
-        <v>1704.232366239083</v>
+        <v>1687.052215870183</v>
       </c>
       <c r="D50">
-        <v>2678.984366239083</v>
+        <v>2692.803215870184</v>
       </c>
       <c r="E50">
-        <v>-446.4480000000001</v>
+        <v>-415.4490000000001</v>
       </c>
       <c r="F50">
-        <v>1487.952</v>
+        <v>1518.951</v>
       </c>
       <c r="G50">
         <v>513.2</v>
@@ -5381,28 +5381,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M50">
-        <v>77.07591360000001</v>
+        <v>78.68166180000001</v>
       </c>
       <c r="N50">
-        <v>706.4974197333333</v>
+        <v>704.8916715333334</v>
       </c>
       <c r="O50">
-        <v>176.2004564814933</v>
+        <v>175.7999828804134</v>
       </c>
       <c r="P50">
-        <v>530.29696325184</v>
+        <v>529.09168865292</v>
       </c>
       <c r="Q50">
-        <v>537.55696325184</v>
+        <v>536.35168865292</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1179442096896179</v>
+        <v>0.1191503979093251</v>
       </c>
       <c r="T50">
-        <v>1.666148029783324</v>
+        <v>1.694004570654159</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.16625423864367</v>
+        <v>9.958779662344819</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07981843213375581</v>
+        <v>0.08028096682891026</v>
       </c>
       <c r="C51">
-        <v>1687.052215870183</v>
+        <v>1619.931406387767</v>
       </c>
       <c r="D51">
-        <v>2692.803215870184</v>
+        <v>2656.681406387767</v>
       </c>
       <c r="E51">
-        <v>-415.4490000000001</v>
+        <v>-384.45</v>
       </c>
       <c r="F51">
-        <v>1518.951</v>
+        <v>1549.95</v>
       </c>
       <c r="G51">
         <v>513.2</v>
@@ -5463,45 +5463,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M51">
-        <v>78.68166180000001</v>
+        <v>82.92232500000001</v>
       </c>
       <c r="N51">
-        <v>704.8916715333334</v>
+        <v>700.6510083333334</v>
       </c>
       <c r="O51">
-        <v>175.7999828804134</v>
+        <v>174.7423614783334</v>
       </c>
       <c r="P51">
-        <v>529.09168865292</v>
+        <v>525.908646855</v>
       </c>
       <c r="Q51">
-        <v>536.35168865292</v>
+        <v>533.168646855</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1191503979093251</v>
+        <v>0.1204048336578205</v>
       </c>
       <c r="T51">
-        <v>1.694004570654159</v>
+        <v>1.722975373159827</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>9.958779662344819</v>
+        <v>9.449485808958363</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08028096682891026</v>
+        <v>0.08011825172406473</v>
       </c>
       <c r="C52">
-        <v>1619.931406387767</v>
+        <v>1601.528683058772</v>
       </c>
       <c r="D52">
-        <v>2656.681406387767</v>
+        <v>2669.277683058773</v>
       </c>
       <c r="E52">
-        <v>-384.45</v>
+        <v>-353.451</v>
       </c>
       <c r="F52">
-        <v>1549.95</v>
+        <v>1580.949</v>
       </c>
       <c r="G52">
         <v>513.2</v>
@@ -5545,28 +5545,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M52">
-        <v>82.92232500000001</v>
+        <v>84.58077150000001</v>
       </c>
       <c r="N52">
-        <v>700.6510083333334</v>
+        <v>698.9925618333334</v>
       </c>
       <c r="O52">
-        <v>174.7423614783334</v>
+        <v>174.3287449212334</v>
       </c>
       <c r="P52">
-        <v>525.908646855</v>
+        <v>524.6638169121001</v>
       </c>
       <c r="Q52">
-        <v>533.168646855</v>
+        <v>531.9238169121001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1204048336578205</v>
+        <v>0.1217104708654382</v>
       </c>
       <c r="T52">
-        <v>1.722975373159827</v>
+        <v>1.75312865740042</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.449485808958363</v>
+        <v>9.264201773488592</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08011825172406473</v>
+        <v>0.07995553661921917</v>
       </c>
       <c r="C53">
-        <v>1601.528683058772</v>
+        <v>1583.245975673435</v>
       </c>
       <c r="D53">
-        <v>2669.277683058773</v>
+        <v>2681.993975673436</v>
       </c>
       <c r="E53">
-        <v>-353.451</v>
+        <v>-322.452</v>
       </c>
       <c r="F53">
-        <v>1580.949</v>
+        <v>1611.948</v>
       </c>
       <c r="G53">
         <v>513.2</v>
@@ -5627,28 +5627,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M53">
-        <v>84.58077150000001</v>
+        <v>86.23921800000002</v>
       </c>
       <c r="N53">
-        <v>698.9925618333334</v>
+        <v>697.3341153333333</v>
       </c>
       <c r="O53">
-        <v>174.3287449212334</v>
+        <v>173.9151283641334</v>
       </c>
       <c r="P53">
-        <v>524.6638169121001</v>
+        <v>523.4189869692</v>
       </c>
       <c r="Q53">
-        <v>531.9238169121001</v>
+        <v>530.6789869692</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1217104708654382</v>
+        <v>0.1230705096233733</v>
       </c>
       <c r="T53">
-        <v>1.75312865740042</v>
+        <v>1.784538328484371</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.264201773488592</v>
+        <v>9.086044047075347</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07995553661921917</v>
+        <v>0.07979282151437364</v>
       </c>
       <c r="C54">
-        <v>1583.245975673435</v>
+        <v>1565.08500769035</v>
       </c>
       <c r="D54">
-        <v>2681.993975673436</v>
+        <v>2694.83200769035</v>
       </c>
       <c r="E54">
-        <v>-322.452</v>
+        <v>-291.453</v>
       </c>
       <c r="F54">
-        <v>1611.948</v>
+        <v>1642.947</v>
       </c>
       <c r="G54">
         <v>513.2</v>
@@ -5709,28 +5709,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M54">
-        <v>86.23921800000002</v>
+        <v>87.89766450000002</v>
       </c>
       <c r="N54">
-        <v>697.3341153333333</v>
+        <v>695.6756688333334</v>
       </c>
       <c r="O54">
-        <v>173.9151283641334</v>
+        <v>173.5015118070334</v>
       </c>
       <c r="P54">
-        <v>523.4189869692</v>
+        <v>522.1741570263</v>
       </c>
       <c r="Q54">
-        <v>530.6789869692</v>
+        <v>529.4341570263</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1230705096233733</v>
+        <v>0.1244884223710077</v>
       </c>
       <c r="T54">
-        <v>1.784538328484371</v>
+        <v>1.817284581316576</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.086044047075347</v>
+        <v>8.914609253734305</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07979282151437364</v>
+        <v>0.07963010640952808</v>
       </c>
       <c r="C55">
-        <v>1565.08500769035</v>
+        <v>1547.047535725892</v>
       </c>
       <c r="D55">
-        <v>2694.83200769035</v>
+        <v>2707.793535725893</v>
       </c>
       <c r="E55">
-        <v>-291.453</v>
+        <v>-260.454</v>
       </c>
       <c r="F55">
-        <v>1642.947</v>
+        <v>1673.946</v>
       </c>
       <c r="G55">
         <v>513.2</v>
@@ -5791,28 +5791,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M55">
-        <v>87.89766450000002</v>
+        <v>89.55611100000002</v>
       </c>
       <c r="N55">
-        <v>695.6756688333334</v>
+        <v>694.0172223333334</v>
       </c>
       <c r="O55">
-        <v>173.5015118070334</v>
+        <v>173.0878952499334</v>
       </c>
       <c r="P55">
-        <v>522.1741570263</v>
+        <v>520.9293270834</v>
       </c>
       <c r="Q55">
-        <v>529.4341570263</v>
+        <v>528.1893270834</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1244884223710077</v>
+        <v>0.1259679834989741</v>
       </c>
       <c r="T55">
-        <v>1.817284581316576</v>
+        <v>1.85145458427192</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.914609253734305</v>
+        <v>8.74952389718367</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07963010640952808</v>
+        <v>0.07946739130468256</v>
       </c>
       <c r="C56">
-        <v>1547.047535725892</v>
+        <v>1529.135350355466</v>
       </c>
       <c r="D56">
-        <v>2707.793535725893</v>
+        <v>2720.880350355466</v>
       </c>
       <c r="E56">
-        <v>-260.454</v>
+        <v>-229.4549999999999</v>
       </c>
       <c r="F56">
-        <v>1673.946</v>
+        <v>1704.945</v>
       </c>
       <c r="G56">
         <v>513.2</v>
@@ -5873,28 +5873,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M56">
-        <v>89.55611100000002</v>
+        <v>91.21455750000001</v>
       </c>
       <c r="N56">
-        <v>694.0172223333334</v>
+        <v>692.3587758333333</v>
       </c>
       <c r="O56">
-        <v>173.0878952499334</v>
+        <v>172.6742786928333</v>
       </c>
       <c r="P56">
-        <v>520.9293270834</v>
+        <v>519.6844971405</v>
       </c>
       <c r="Q56">
-        <v>528.1893270834</v>
+        <v>526.9444971404999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1259679834989741</v>
+        <v>0.1275133028992946</v>
       </c>
       <c r="T56">
-        <v>1.85145458427192</v>
+        <v>1.887143254025279</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.74952389718367</v>
+        <v>8.590441644507603</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07946739130468256</v>
+        <v>0.079304676199837</v>
       </c>
       <c r="C57">
-        <v>1529.135350355466</v>
+        <v>1511.350276938121</v>
       </c>
       <c r="D57">
-        <v>2720.880350355466</v>
+        <v>2734.094276938122</v>
       </c>
       <c r="E57">
-        <v>-229.4549999999999</v>
+        <v>-198.4559999999999</v>
       </c>
       <c r="F57">
-        <v>1704.945</v>
+        <v>1735.944</v>
       </c>
       <c r="G57">
         <v>513.2</v>
@@ -5955,28 +5955,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M57">
-        <v>91.21455750000001</v>
+        <v>92.87300400000002</v>
       </c>
       <c r="N57">
-        <v>692.3587758333333</v>
+        <v>690.7003293333333</v>
       </c>
       <c r="O57">
-        <v>172.6742786928333</v>
+        <v>172.2606621357334</v>
       </c>
       <c r="P57">
-        <v>519.6844971405</v>
+        <v>518.4396671976</v>
       </c>
       <c r="Q57">
-        <v>526.9444971404999</v>
+        <v>525.6996671976</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1275133028992946</v>
+        <v>0.1291288640905387</v>
       </c>
       <c r="T57">
-        <v>1.887143254025279</v>
+        <v>1.924454136040154</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.590441644507603</v>
+        <v>8.437040900855681</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.079304676199837</v>
+        <v>0.07914196109499147</v>
       </c>
       <c r="C58">
-        <v>1511.350276938121</v>
+        <v>1493.694176465299</v>
       </c>
       <c r="D58">
-        <v>2734.094276938122</v>
+        <v>2747.4371764653</v>
       </c>
       <c r="E58">
-        <v>-198.4559999999999</v>
+        <v>-167.4569999999999</v>
       </c>
       <c r="F58">
-        <v>1735.944</v>
+        <v>1766.943</v>
       </c>
       <c r="G58">
         <v>513.2</v>
@@ -6037,28 +6037,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M58">
-        <v>92.87300400000002</v>
+        <v>94.53145050000002</v>
       </c>
       <c r="N58">
-        <v>690.7003293333333</v>
+        <v>689.0418828333334</v>
       </c>
       <c r="O58">
-        <v>172.2606621357334</v>
+        <v>171.8470455786334</v>
       </c>
       <c r="P58">
-        <v>518.4396671976</v>
+        <v>517.1948372547</v>
       </c>
       <c r="Q58">
-        <v>525.6996671976</v>
+        <v>524.4548372547</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1291288640905387</v>
+        <v>0.1308195676627709</v>
       </c>
       <c r="T58">
-        <v>1.924454136040154</v>
+        <v>1.963500407916186</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.437040900855681</v>
+        <v>8.28902263943716</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07914196109499147</v>
+        <v>0.07897924599014591</v>
       </c>
       <c r="C59">
-        <v>1493.694176465299</v>
+        <v>1476.168946434571</v>
       </c>
       <c r="D59">
-        <v>2747.4371764653</v>
+        <v>2760.910946434572</v>
       </c>
       <c r="E59">
-        <v>-167.4569999999999</v>
+        <v>-136.4579999999999</v>
       </c>
       <c r="F59">
-        <v>1766.943</v>
+        <v>1797.942</v>
       </c>
       <c r="G59">
         <v>513.2</v>
@@ -6119,28 +6119,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M59">
-        <v>94.53145050000002</v>
+        <v>96.18989700000002</v>
       </c>
       <c r="N59">
-        <v>689.0418828333334</v>
+        <v>687.3834363333334</v>
       </c>
       <c r="O59">
-        <v>171.8470455786334</v>
+        <v>171.4334290215334</v>
       </c>
       <c r="P59">
-        <v>517.1948372547</v>
+        <v>515.9500073118001</v>
       </c>
       <c r="Q59">
-        <v>524.4548372547</v>
+        <v>523.2100073118</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1308195676627709</v>
+        <v>0.1325907809289189</v>
       </c>
       <c r="T59">
-        <v>1.963500407916186</v>
+        <v>2.00440602607203</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.28902263943716</v>
+        <v>8.14610845599859</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07897924599014593</v>
+        <v>0.07881653088530038</v>
       </c>
       <c r="C60">
-        <v>1476.168946434571</v>
+        <v>1458.77652174919</v>
       </c>
       <c r="D60">
-        <v>2760.910946434571</v>
+        <v>2774.517521749191</v>
       </c>
       <c r="E60">
-        <v>-136.4580000000001</v>
+        <v>-105.4590000000001</v>
       </c>
       <c r="F60">
-        <v>1797.942</v>
+        <v>1828.941</v>
       </c>
       <c r="G60">
         <v>513.2</v>
@@ -6201,28 +6201,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M60">
-        <v>96.18989700000002</v>
+        <v>97.84834350000001</v>
       </c>
       <c r="N60">
-        <v>687.3834363333334</v>
+        <v>685.7249898333333</v>
       </c>
       <c r="O60">
-        <v>171.4334290215334</v>
+        <v>171.0198124644333</v>
       </c>
       <c r="P60">
-        <v>515.9500073118001</v>
+        <v>514.7051773689</v>
       </c>
       <c r="Q60">
-        <v>523.2100073118</v>
+        <v>521.9651773689</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1325907809289189</v>
+        <v>0.1344483948421961</v>
       </c>
       <c r="T60">
-        <v>2.004406026072029</v>
+        <v>2.047307040235475</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.14610845599859</v>
+        <v>8.008038821151153</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07881653088530038</v>
+        <v>0.07865381578045484</v>
       </c>
       <c r="C61">
-        <v>1458.77652174919</v>
+        <v>1441.518875644399</v>
       </c>
       <c r="D61">
-        <v>2774.517521749191</v>
+        <v>2788.258875644399</v>
       </c>
       <c r="E61">
-        <v>-105.4590000000001</v>
+        <v>-74.46000000000004</v>
       </c>
       <c r="F61">
-        <v>1828.941</v>
+        <v>1859.94</v>
       </c>
       <c r="G61">
         <v>513.2</v>
@@ -6283,28 +6283,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M61">
-        <v>97.84834350000001</v>
+        <v>99.50679000000001</v>
       </c>
       <c r="N61">
-        <v>685.7249898333333</v>
+        <v>684.0665433333334</v>
       </c>
       <c r="O61">
-        <v>171.0198124644333</v>
+        <v>170.6061959073334</v>
       </c>
       <c r="P61">
-        <v>514.7051773689</v>
+        <v>513.460347426</v>
       </c>
       <c r="Q61">
-        <v>521.9651773689</v>
+        <v>520.720347426</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1344483948421961</v>
+        <v>0.1363988894511371</v>
       </c>
       <c r="T61">
-        <v>2.047307040235475</v>
+        <v>2.092353105107092</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.008038821151153</v>
+        <v>7.874571507465302</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07865381578045484</v>
+        <v>0.0784911006756093</v>
       </c>
       <c r="C62">
-        <v>1441.518875644399</v>
+        <v>1424.39802064138</v>
       </c>
       <c r="D62">
-        <v>2788.258875644399</v>
+        <v>2802.13702064138</v>
       </c>
       <c r="E62">
-        <v>-74.46000000000004</v>
+        <v>-43.46100000000001</v>
       </c>
       <c r="F62">
-        <v>1859.94</v>
+        <v>1890.939</v>
       </c>
       <c r="G62">
         <v>513.2</v>
@@ -6365,28 +6365,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M62">
-        <v>99.50679000000001</v>
+        <v>101.1652365</v>
       </c>
       <c r="N62">
-        <v>684.0665433333334</v>
+        <v>682.4080968333334</v>
       </c>
       <c r="O62">
-        <v>170.6061959073334</v>
+        <v>170.1925793502334</v>
       </c>
       <c r="P62">
-        <v>513.460347426</v>
+        <v>512.2155174831</v>
       </c>
       <c r="Q62">
-        <v>520.720347426</v>
+        <v>519.4755174831</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1363988894511371</v>
+        <v>0.1384494094246392</v>
       </c>
       <c r="T62">
-        <v>2.092353105107092</v>
+        <v>2.139709224587512</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.874571507465302</v>
+        <v>7.745480171277347</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0784911006756093</v>
+        <v>0.07832838557076376</v>
       </c>
       <c r="C63">
-        <v>1424.39802064138</v>
+        <v>1407.416009529849</v>
       </c>
       <c r="D63">
-        <v>2802.13702064138</v>
+        <v>2816.154009529849</v>
       </c>
       <c r="E63">
-        <v>-43.46100000000001</v>
+        <v>-12.46199999999999</v>
       </c>
       <c r="F63">
-        <v>1890.939</v>
+        <v>1921.938</v>
       </c>
       <c r="G63">
         <v>513.2</v>
@@ -6447,28 +6447,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M63">
-        <v>101.1652365</v>
+        <v>102.823683</v>
       </c>
       <c r="N63">
-        <v>682.4080968333334</v>
+        <v>680.7496503333334</v>
       </c>
       <c r="O63">
-        <v>170.1925793502334</v>
+        <v>169.7789627931334</v>
       </c>
       <c r="P63">
-        <v>512.2155174831</v>
+        <v>510.9706875402001</v>
       </c>
       <c r="Q63">
-        <v>519.4755174831</v>
+        <v>518.2306875402001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1384494094246392</v>
+        <v>0.1406078515020099</v>
       </c>
       <c r="T63">
-        <v>2.139709224587512</v>
+        <v>2.189557771409005</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.745480171277347</v>
+        <v>7.620553071740615</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07832838557076376</v>
+        <v>0.07854397286591822</v>
       </c>
       <c r="C64">
-        <v>1407.416009529849</v>
+        <v>1357.875367434706</v>
       </c>
       <c r="D64">
-        <v>2816.154009529849</v>
+        <v>2797.612367434706</v>
       </c>
       <c r="E64">
-        <v>-12.46199999999999</v>
+        <v>18.53700000000003</v>
       </c>
       <c r="F64">
-        <v>1921.938</v>
+        <v>1952.937</v>
       </c>
       <c r="G64">
         <v>513.2</v>
@@ -6529,45 +6529,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M64">
-        <v>102.823683</v>
+        <v>106.0444791</v>
       </c>
       <c r="N64">
-        <v>680.7496503333334</v>
+        <v>677.5288542333334</v>
       </c>
       <c r="O64">
-        <v>169.7789627931334</v>
+        <v>168.9756962457934</v>
       </c>
       <c r="P64">
-        <v>510.9706875402001</v>
+        <v>508.55315798754</v>
       </c>
       <c r="Q64">
-        <v>518.2306875402001</v>
+        <v>515.8131579875401</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1406078515020099</v>
+        <v>0.1428829661241033</v>
       </c>
       <c r="T64">
-        <v>2.189557771409005</v>
+        <v>2.242100834274903</v>
       </c>
       <c r="U64">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y64">
-        <v>7.620553071740615</v>
+        <v>7.38910068665077</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07854397286591822</v>
+        <v>0.07838726256107267</v>
       </c>
       <c r="C65">
-        <v>1357.875367434706</v>
+        <v>1340.329927276337</v>
       </c>
       <c r="D65">
-        <v>2797.612367434706</v>
+        <v>2811.065927276337</v>
       </c>
       <c r="E65">
-        <v>18.53700000000003</v>
+        <v>49.53600000000006</v>
       </c>
       <c r="F65">
-        <v>1952.937</v>
+        <v>1983.936</v>
       </c>
       <c r="G65">
         <v>513.2</v>
@@ -6611,28 +6611,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M65">
-        <v>106.0444791</v>
+        <v>107.7277248</v>
       </c>
       <c r="N65">
-        <v>677.5288542333334</v>
+        <v>675.8456085333333</v>
       </c>
       <c r="O65">
-        <v>168.9756962457934</v>
+        <v>168.5558947682133</v>
       </c>
       <c r="P65">
-        <v>508.55315798754</v>
+        <v>507.28971376512</v>
       </c>
       <c r="Q65">
-        <v>515.8131579875401</v>
+        <v>514.54971376512</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1428829661241033</v>
+        <v>0.1452844760029797</v>
       </c>
       <c r="T65">
-        <v>2.242100834274903</v>
+        <v>2.297562956188907</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.38910068665077</v>
+        <v>7.273645988421852</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07838726256107267</v>
+        <v>0.07823055225622713</v>
       </c>
       <c r="C66">
-        <v>1340.329927276337</v>
+        <v>1322.914507195788</v>
       </c>
       <c r="D66">
-        <v>2811.065927276337</v>
+        <v>2824.649507195788</v>
       </c>
       <c r="E66">
-        <v>49.53600000000006</v>
+        <v>80.53500000000008</v>
       </c>
       <c r="F66">
-        <v>1983.936</v>
+        <v>2014.935</v>
       </c>
       <c r="G66">
         <v>513.2</v>
@@ -6693,28 +6693,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M66">
-        <v>107.7277248</v>
+        <v>109.4109705</v>
       </c>
       <c r="N66">
-        <v>675.8456085333333</v>
+        <v>674.1623628333334</v>
       </c>
       <c r="O66">
-        <v>168.5558947682133</v>
+        <v>168.1360932906334</v>
       </c>
       <c r="P66">
-        <v>507.28971376512</v>
+        <v>506.0262695427</v>
       </c>
       <c r="Q66">
-        <v>514.54971376512</v>
+        <v>513.2862695427001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1452844760029797</v>
+        <v>0.1478232150177918</v>
       </c>
       <c r="T66">
-        <v>2.297562956188907</v>
+        <v>2.356194342212282</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.273645988421852</v>
+        <v>7.161743742446132</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07823055225622713</v>
+        <v>0.07807384195138159</v>
       </c>
       <c r="C67">
-        <v>1322.914507195788</v>
+        <v>1305.631001186906</v>
       </c>
       <c r="D67">
-        <v>2824.649507195788</v>
+        <v>2838.365001186906</v>
       </c>
       <c r="E67">
-        <v>80.53500000000008</v>
+        <v>111.5340000000001</v>
       </c>
       <c r="F67">
-        <v>2014.935</v>
+        <v>2045.934</v>
       </c>
       <c r="G67">
         <v>513.2</v>
@@ -6775,28 +6775,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M67">
-        <v>109.4109705</v>
+        <v>111.0942162</v>
       </c>
       <c r="N67">
-        <v>674.1623628333334</v>
+        <v>672.4791171333334</v>
       </c>
       <c r="O67">
-        <v>168.1360932906334</v>
+        <v>167.7162918130533</v>
       </c>
       <c r="P67">
-        <v>506.0262695427</v>
+        <v>504.7628253202801</v>
       </c>
       <c r="Q67">
-        <v>513.2862695427001</v>
+        <v>512.02282532028</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1478232150177918</v>
+        <v>0.1505112916217106</v>
       </c>
       <c r="T67">
-        <v>2.356194342212282</v>
+        <v>2.418274633295856</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.161743742446132</v>
+        <v>7.05323247362119</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07807384195138159</v>
+        <v>0.07791713164653606</v>
       </c>
       <c r="C68">
-        <v>1305.631001186906</v>
+        <v>1288.481340209274</v>
       </c>
       <c r="D68">
-        <v>2838.365001186906</v>
+        <v>2852.214340209274</v>
       </c>
       <c r="E68">
-        <v>111.5340000000001</v>
+        <v>142.5330000000001</v>
       </c>
       <c r="F68">
-        <v>2045.934</v>
+        <v>2076.933</v>
       </c>
       <c r="G68">
         <v>513.2</v>
@@ -6857,28 +6857,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M68">
-        <v>111.0942162</v>
+        <v>112.7774619</v>
       </c>
       <c r="N68">
-        <v>672.4791171333334</v>
+        <v>670.7958714333333</v>
       </c>
       <c r="O68">
-        <v>167.7162918130533</v>
+        <v>167.2964903354734</v>
       </c>
       <c r="P68">
-        <v>504.7628253202801</v>
+        <v>503.49938109786</v>
       </c>
       <c r="Q68">
-        <v>512.02282532028</v>
+        <v>510.75938109786</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1505112916217106</v>
+        <v>0.1533622819592002</v>
       </c>
       <c r="T68">
-        <v>2.418274633295856</v>
+        <v>2.484117366263284</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.05323247362119</v>
+        <v>6.947960347149231</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07791713164653606</v>
+        <v>0.07776042134169051</v>
       </c>
       <c r="C69">
-        <v>1288.481340209274</v>
+        <v>1271.467493094477</v>
       </c>
       <c r="D69">
-        <v>2852.214340209274</v>
+        <v>2866.199493094477</v>
       </c>
       <c r="E69">
-        <v>142.5330000000001</v>
+        <v>173.5320000000004</v>
       </c>
       <c r="F69">
-        <v>2076.933</v>
+        <v>2107.932000000001</v>
       </c>
       <c r="G69">
         <v>513.2</v>
@@ -6939,28 +6939,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M69">
-        <v>112.7774619</v>
+        <v>114.4607076</v>
       </c>
       <c r="N69">
-        <v>670.7958714333333</v>
+        <v>669.1126257333333</v>
       </c>
       <c r="O69">
-        <v>167.2964903354734</v>
+        <v>166.8766888578933</v>
       </c>
       <c r="P69">
-        <v>503.49938109786</v>
+        <v>502.23593687544</v>
       </c>
       <c r="Q69">
-        <v>510.75938109786</v>
+        <v>509.49593687544</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1533622819592002</v>
+        <v>0.1563914591927829</v>
       </c>
       <c r="T69">
-        <v>2.484117366263284</v>
+        <v>2.554075270041175</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.947960347149231</v>
+        <v>6.845784459691154</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07776042134169051</v>
+        <v>0.07760371103684496</v>
       </c>
       <c r="C70">
-        <v>1271.467493094477</v>
+        <v>1254.591467479152</v>
       </c>
       <c r="D70">
-        <v>2866.199493094477</v>
+        <v>2880.322467479153</v>
       </c>
       <c r="E70">
-        <v>173.5320000000004</v>
+        <v>204.5310000000002</v>
       </c>
       <c r="F70">
-        <v>2107.932000000001</v>
+        <v>2138.931</v>
       </c>
       <c r="G70">
         <v>513.2</v>
@@ -7021,28 +7021,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M70">
-        <v>114.4607076</v>
+        <v>116.1439533</v>
       </c>
       <c r="N70">
-        <v>669.1126257333333</v>
+        <v>667.4293800333334</v>
       </c>
       <c r="O70">
-        <v>166.8766888578933</v>
+        <v>166.4568873803133</v>
       </c>
       <c r="P70">
-        <v>502.23593687544</v>
+        <v>500.97249265302</v>
       </c>
       <c r="Q70">
-        <v>509.49593687544</v>
+        <v>508.23249265302</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1563914591927829</v>
+        <v>0.159616067215629</v>
       </c>
       <c r="T70">
-        <v>2.554075270041175</v>
+        <v>2.628546586966027</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.845784459691154</v>
+        <v>6.746570192159398</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07760371103684496</v>
+        <v>0.07744700073199942</v>
       </c>
       <c r="C71">
-        <v>1254.591467479152</v>
+        <v>1237.855310765774</v>
       </c>
       <c r="D71">
-        <v>2880.322467479153</v>
+        <v>2894.585310765774</v>
       </c>
       <c r="E71">
-        <v>204.5310000000002</v>
+        <v>235.5300000000004</v>
       </c>
       <c r="F71">
-        <v>2138.931</v>
+        <v>2169.930000000001</v>
       </c>
       <c r="G71">
         <v>513.2</v>
@@ -7103,28 +7103,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M71">
-        <v>116.1439533</v>
+        <v>117.827199</v>
       </c>
       <c r="N71">
-        <v>667.4293800333334</v>
+        <v>665.7461343333333</v>
       </c>
       <c r="O71">
-        <v>166.4568873803133</v>
+        <v>166.0370859027333</v>
       </c>
       <c r="P71">
-        <v>500.97249265302</v>
+        <v>499.7090484306</v>
       </c>
       <c r="Q71">
-        <v>508.23249265302</v>
+        <v>506.9690484306</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.159616067215629</v>
+        <v>0.1630556491066648</v>
       </c>
       <c r="T71">
-        <v>2.628546586966027</v>
+        <v>2.707982658352536</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.746570192159398</v>
+        <v>6.650190617985692</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07744700073199942</v>
+        <v>0.07729029042715388</v>
       </c>
       <c r="C72">
-        <v>1237.855310765774</v>
+        <v>1221.261111112117</v>
       </c>
       <c r="D72">
-        <v>2894.585310765774</v>
+        <v>2908.990111112118</v>
       </c>
       <c r="E72">
-        <v>235.5300000000004</v>
+        <v>266.5290000000002</v>
       </c>
       <c r="F72">
-        <v>2169.930000000001</v>
+        <v>2200.929000000001</v>
       </c>
       <c r="G72">
         <v>513.2</v>
@@ -7185,28 +7185,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M72">
-        <v>117.827199</v>
+        <v>119.5104447</v>
       </c>
       <c r="N72">
-        <v>665.7461343333333</v>
+        <v>664.0628886333334</v>
       </c>
       <c r="O72">
-        <v>166.0370859027333</v>
+        <v>165.6172844251533</v>
       </c>
       <c r="P72">
-        <v>499.7090484306</v>
+        <v>498.44560420818</v>
       </c>
       <c r="Q72">
-        <v>506.9690484306</v>
+        <v>505.70560420818</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1630556491066648</v>
+        <v>0.16673244354191</v>
       </c>
       <c r="T72">
-        <v>2.707982658352536</v>
+        <v>2.792897079489839</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.650190617985692</v>
+        <v>6.556525961394345</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07729029042715389</v>
+        <v>0.07713358012230835</v>
       </c>
       <c r="C73">
-        <v>1221.261111112117</v>
+        <v>1204.810998450417</v>
       </c>
       <c r="D73">
-        <v>2908.990111112117</v>
+        <v>2923.538998450417</v>
       </c>
       <c r="E73">
-        <v>266.5289999999998</v>
+        <v>297.528</v>
       </c>
       <c r="F73">
-        <v>2200.929</v>
+        <v>2231.928</v>
       </c>
       <c r="G73">
         <v>513.2</v>
@@ -7267,28 +7267,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M73">
-        <v>119.5104447</v>
+        <v>121.1936904</v>
       </c>
       <c r="N73">
-        <v>664.0628886333334</v>
+        <v>662.3796429333333</v>
       </c>
       <c r="O73">
-        <v>165.6172844251533</v>
+        <v>165.1974829475733</v>
       </c>
       <c r="P73">
-        <v>498.44560420818</v>
+        <v>497.18215998576</v>
       </c>
       <c r="Q73">
-        <v>505.70560420818</v>
+        <v>504.44215998576</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.16673244354191</v>
+        <v>0.1706718661511012</v>
       </c>
       <c r="T73">
-        <v>2.792897079489838</v>
+        <v>2.883876816422662</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.556525961394346</v>
+        <v>6.465463100819424</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07713358012230835</v>
+        <v>0.0769768698174628</v>
       </c>
       <c r="C74">
-        <v>1204.810998450417</v>
+        <v>1188.507145537261</v>
       </c>
       <c r="D74">
-        <v>2923.538998450417</v>
+        <v>2938.234145537262</v>
       </c>
       <c r="E74">
-        <v>297.528</v>
+        <v>328.5269999999998</v>
       </c>
       <c r="F74">
-        <v>2231.928</v>
+        <v>2262.927</v>
       </c>
       <c r="G74">
         <v>513.2</v>
@@ -7349,28 +7349,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M74">
-        <v>121.1936904</v>
+        <v>122.8769361</v>
       </c>
       <c r="N74">
-        <v>662.3796429333333</v>
+        <v>660.6963972333334</v>
       </c>
       <c r="O74">
-        <v>165.1974829475733</v>
+        <v>164.7776814699934</v>
       </c>
       <c r="P74">
-        <v>497.18215998576</v>
+        <v>495.9187157633401</v>
       </c>
       <c r="Q74">
-        <v>504.44215998576</v>
+        <v>503.1787157633401</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1706718661511012</v>
+        <v>0.1749030978424548</v>
       </c>
       <c r="T74">
-        <v>2.883876816422662</v>
+        <v>2.981595793128287</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.465463100819424</v>
+        <v>6.376895113136967</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0769768698174628</v>
+        <v>0.07682015951261725</v>
       </c>
       <c r="C75">
-        <v>1188.507145537261</v>
+        <v>1172.351769035311</v>
       </c>
       <c r="D75">
-        <v>2938.234145537262</v>
+        <v>2953.077769035311</v>
       </c>
       <c r="E75">
-        <v>328.5269999999998</v>
+        <v>359.5260000000001</v>
       </c>
       <c r="F75">
-        <v>2262.927</v>
+        <v>2293.926</v>
       </c>
       <c r="G75">
         <v>513.2</v>
@@ -7431,28 +7431,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M75">
-        <v>122.8769361</v>
+        <v>124.5601818</v>
       </c>
       <c r="N75">
-        <v>660.6963972333334</v>
+        <v>659.0131515333334</v>
       </c>
       <c r="O75">
-        <v>164.7776814699934</v>
+        <v>164.3578799924134</v>
       </c>
       <c r="P75">
-        <v>495.9187157633401</v>
+        <v>494.65527154092</v>
       </c>
       <c r="Q75">
-        <v>503.1787157633401</v>
+        <v>501.91527154092</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1749030978424548</v>
+        <v>0.1794598088946818</v>
       </c>
       <c r="T75">
-        <v>2.981595793128287</v>
+        <v>3.086831614195884</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.376895113136967</v>
+        <v>6.290720854851331</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07682015951261725</v>
+        <v>0.07666344920777173</v>
       </c>
       <c r="C76">
-        <v>1172.351769035311</v>
+        <v>1156.347130627973</v>
       </c>
       <c r="D76">
-        <v>2953.077769035311</v>
+        <v>2968.072130627973</v>
       </c>
       <c r="E76">
-        <v>359.5260000000001</v>
+        <v>390.5249999999999</v>
       </c>
       <c r="F76">
-        <v>2293.926</v>
+        <v>2324.925</v>
       </c>
       <c r="G76">
         <v>513.2</v>
@@ -7513,28 +7513,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M76">
-        <v>124.5601818</v>
+        <v>126.2434275</v>
       </c>
       <c r="N76">
-        <v>659.0131515333334</v>
+        <v>657.3299058333333</v>
       </c>
       <c r="O76">
-        <v>164.3578799924134</v>
+        <v>163.9380785148333</v>
       </c>
       <c r="P76">
-        <v>494.65527154092</v>
+        <v>493.3918273185</v>
       </c>
       <c r="Q76">
-        <v>501.91527154092</v>
+        <v>500.6518273185</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1794598088946818</v>
+        <v>0.1843810568310869</v>
       </c>
       <c r="T76">
-        <v>3.086831614195884</v>
+        <v>3.20048630094889</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.290720854851331</v>
+        <v>6.206844576786647</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07666344920777173</v>
+        <v>0.07650673890292618</v>
       </c>
       <c r="C77">
-        <v>1156.347130627973</v>
+        <v>1140.495538168209</v>
       </c>
       <c r="D77">
-        <v>2968.072130627973</v>
+        <v>2983.21953816821</v>
       </c>
       <c r="E77">
-        <v>390.5249999999999</v>
+        <v>421.5240000000001</v>
       </c>
       <c r="F77">
-        <v>2324.925</v>
+        <v>2355.924</v>
       </c>
       <c r="G77">
         <v>513.2</v>
@@ -7595,28 +7595,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M77">
-        <v>126.2434275</v>
+        <v>127.9266732</v>
       </c>
       <c r="N77">
-        <v>657.3299058333333</v>
+        <v>655.6466601333334</v>
       </c>
       <c r="O77">
-        <v>163.9380785148333</v>
+        <v>163.5182770372534</v>
       </c>
       <c r="P77">
-        <v>493.3918273185</v>
+        <v>492.12838309608</v>
       </c>
       <c r="Q77">
-        <v>500.6518273185</v>
+        <v>499.38838309608</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1843810568310869</v>
+        <v>0.1897124087621924</v>
       </c>
       <c r="T77">
-        <v>3.20048630094889</v>
+        <v>3.323612211597978</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.206844576786647</v>
+        <v>6.125175569197349</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07650673890292618</v>
+        <v>0.07692799059808064</v>
       </c>
       <c r="C78">
-        <v>1140.495538168209</v>
+        <v>1069.124954158904</v>
       </c>
       <c r="D78">
-        <v>2983.21953816821</v>
+        <v>2942.847954158905</v>
       </c>
       <c r="E78">
-        <v>421.5240000000001</v>
+        <v>452.5230000000004</v>
       </c>
       <c r="F78">
-        <v>2355.924</v>
+        <v>2386.923000000001</v>
       </c>
       <c r="G78">
         <v>513.2</v>
@@ -7677,45 +7677,45 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M78">
-        <v>127.9266732</v>
+        <v>131.9968419</v>
       </c>
       <c r="N78">
-        <v>655.6466601333334</v>
+        <v>651.5764914333333</v>
       </c>
       <c r="O78">
-        <v>163.5182770372534</v>
+        <v>162.5031769634734</v>
       </c>
       <c r="P78">
-        <v>492.12838309608</v>
+        <v>489.07331446986</v>
       </c>
       <c r="Q78">
-        <v>499.38838309608</v>
+        <v>496.3333144698599</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1897124087621924</v>
+        <v>0.1955073565133941</v>
       </c>
       <c r="T78">
-        <v>3.323612211597978</v>
+        <v>3.457444723173074</v>
       </c>
       <c r="U78">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V78">
         <v>0.2494</v>
       </c>
       <c r="W78">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>6.125175569197349</v>
+        <v>5.936303642226255</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07692799059808064</v>
+        <v>0.07677878629323509</v>
       </c>
       <c r="C79">
-        <v>1069.124954158904</v>
+        <v>1052.299704515364</v>
       </c>
       <c r="D79">
-        <v>2942.847954158905</v>
+        <v>2957.021704515364</v>
       </c>
       <c r="E79">
-        <v>452.5230000000004</v>
+        <v>483.5220000000002</v>
       </c>
       <c r="F79">
-        <v>2386.923000000001</v>
+        <v>2417.922</v>
       </c>
       <c r="G79">
         <v>513.2</v>
@@ -7759,28 +7759,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M79">
-        <v>131.9968419</v>
+        <v>133.7110866</v>
       </c>
       <c r="N79">
-        <v>651.5764914333333</v>
+        <v>649.8622467333333</v>
       </c>
       <c r="O79">
-        <v>162.5031769634734</v>
+        <v>162.0756443352933</v>
       </c>
       <c r="P79">
-        <v>489.07331446986</v>
+        <v>487.78660239804</v>
       </c>
       <c r="Q79">
-        <v>496.3333144698599</v>
+        <v>495.04660239804</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1955073565133941</v>
+        <v>0.2018291176965232</v>
       </c>
       <c r="T79">
-        <v>3.457444723173074</v>
+        <v>3.603443826709543</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.936303642226255</v>
+        <v>5.860197185274636</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07677878629323509</v>
+        <v>0.07662958198838957</v>
       </c>
       <c r="C80">
-        <v>1052.299704515364</v>
+        <v>1035.611646778594</v>
       </c>
       <c r="D80">
-        <v>2957.021704515364</v>
+        <v>2971.332646778594</v>
       </c>
       <c r="E80">
-        <v>483.5220000000002</v>
+        <v>514.5210000000004</v>
       </c>
       <c r="F80">
-        <v>2417.922</v>
+        <v>2448.921000000001</v>
       </c>
       <c r="G80">
         <v>513.2</v>
@@ -7841,28 +7841,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M80">
-        <v>133.7110866</v>
+        <v>135.4253313</v>
       </c>
       <c r="N80">
-        <v>649.8622467333333</v>
+        <v>648.1480020333333</v>
       </c>
       <c r="O80">
-        <v>162.0756443352933</v>
+        <v>161.6481117071133</v>
       </c>
       <c r="P80">
-        <v>487.78660239804</v>
+        <v>486.49989032622</v>
       </c>
       <c r="Q80">
-        <v>495.04660239804</v>
+        <v>493.75989032622</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2018291176965232</v>
+        <v>0.2087529513732837</v>
       </c>
       <c r="T80">
-        <v>3.603443826709543</v>
+        <v>3.763347606773295</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.860197185274636</v>
+        <v>5.786017474068628</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07662958198838957</v>
+        <v>0.07648037768354402</v>
       </c>
       <c r="C81">
-        <v>1035.611646778594</v>
+        <v>1019.062782516827</v>
       </c>
       <c r="D81">
-        <v>2971.332646778594</v>
+        <v>2985.782782516828</v>
       </c>
       <c r="E81">
-        <v>514.5210000000004</v>
+        <v>545.5200000000002</v>
       </c>
       <c r="F81">
-        <v>2448.921000000001</v>
+        <v>2479.920000000001</v>
       </c>
       <c r="G81">
         <v>513.2</v>
@@ -7923,28 +7923,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M81">
-        <v>135.4253313</v>
+        <v>137.139576</v>
       </c>
       <c r="N81">
-        <v>648.1480020333333</v>
+        <v>646.4337573333333</v>
       </c>
       <c r="O81">
-        <v>161.6481117071133</v>
+        <v>161.2205790789334</v>
       </c>
       <c r="P81">
-        <v>486.49989032622</v>
+        <v>485.2131782544</v>
       </c>
       <c r="Q81">
-        <v>493.75989032622</v>
+        <v>492.4731782544</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2087529513732837</v>
+        <v>0.2163691684177201</v>
       </c>
       <c r="T81">
-        <v>3.763347606773295</v>
+        <v>3.939241764843421</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.786017474068628</v>
+        <v>5.713692255642771</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07648037768354402</v>
+        <v>0.07633117337869846</v>
       </c>
       <c r="C82">
-        <v>1019.062782516827</v>
+        <v>1002.655152424544</v>
       </c>
       <c r="D82">
-        <v>2985.782782516828</v>
+        <v>3000.374152424545</v>
       </c>
       <c r="E82">
-        <v>545.5200000000002</v>
+        <v>576.5190000000005</v>
       </c>
       <c r="F82">
-        <v>2479.920000000001</v>
+        <v>2510.919000000001</v>
       </c>
       <c r="G82">
         <v>513.2</v>
@@ -8005,28 +8005,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M82">
-        <v>137.139576</v>
+        <v>138.8538207000001</v>
       </c>
       <c r="N82">
-        <v>646.4337573333333</v>
+        <v>644.7195126333334</v>
       </c>
       <c r="O82">
-        <v>161.2205790789334</v>
+        <v>160.7930464507533</v>
       </c>
       <c r="P82">
-        <v>485.2131782544</v>
+        <v>483.92646618258</v>
       </c>
       <c r="Q82">
-        <v>492.4731782544</v>
+        <v>491.18646618258</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2163691684177201</v>
+        <v>0.2247870925194657</v>
       </c>
       <c r="T82">
-        <v>3.939241764843421</v>
+        <v>4.133651097447245</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.713692255642771</v>
+        <v>5.643152845079279</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07633117337869846</v>
+        <v>0.07618196907385294</v>
       </c>
       <c r="C83">
-        <v>1002.655152424544</v>
+        <v>986.3908372832111</v>
       </c>
       <c r="D83">
-        <v>3000.374152424545</v>
+        <v>3015.108837283212</v>
       </c>
       <c r="E83">
-        <v>576.5190000000005</v>
+        <v>607.5180000000003</v>
       </c>
       <c r="F83">
-        <v>2510.919000000001</v>
+        <v>2541.918000000001</v>
       </c>
       <c r="G83">
         <v>513.2</v>
@@ -8087,28 +8087,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M83">
-        <v>138.8538207000001</v>
+        <v>140.5680654</v>
       </c>
       <c r="N83">
-        <v>644.7195126333334</v>
+        <v>643.0052679333334</v>
       </c>
       <c r="O83">
-        <v>160.7930464507533</v>
+        <v>160.3655138225733</v>
       </c>
       <c r="P83">
-        <v>483.92646618258</v>
+        <v>482.63975411076</v>
       </c>
       <c r="Q83">
-        <v>491.18646618258</v>
+        <v>489.89975411076</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2247870925194657</v>
+        <v>0.2341403415214053</v>
       </c>
       <c r="T83">
-        <v>4.133651097447245</v>
+        <v>4.34966146700705</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.643152845079279</v>
+        <v>5.574333907944167</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07618196907385294</v>
+        <v>0.07603276476900739</v>
       </c>
       <c r="C84">
-        <v>986.3908372832111</v>
+        <v>970.2719589504727</v>
       </c>
       <c r="D84">
-        <v>3015.108837283212</v>
+        <v>3029.988958950473</v>
       </c>
       <c r="E84">
-        <v>607.5180000000003</v>
+        <v>638.5170000000005</v>
       </c>
       <c r="F84">
-        <v>2541.918000000001</v>
+        <v>2572.917000000001</v>
       </c>
       <c r="G84">
         <v>513.2</v>
@@ -8169,28 +8169,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M84">
-        <v>140.5680654</v>
+        <v>142.2823101</v>
       </c>
       <c r="N84">
-        <v>643.0052679333334</v>
+        <v>641.2910232333334</v>
       </c>
       <c r="O84">
-        <v>160.3655138225733</v>
+        <v>159.9379811943934</v>
       </c>
       <c r="P84">
-        <v>482.63975411076</v>
+        <v>481.35304203894</v>
       </c>
       <c r="Q84">
-        <v>489.89975411076</v>
+        <v>488.61304203894</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2341403415214053</v>
+        <v>0.2445939727588671</v>
       </c>
       <c r="T84">
-        <v>4.34966146700705</v>
+        <v>4.591084821220949</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.574333907944167</v>
+        <v>5.507173258450863</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07603276476900739</v>
+        <v>0.07588356046416186</v>
       </c>
       <c r="C85">
-        <v>970.2719589504727</v>
+        <v>954.3006813787529</v>
       </c>
       <c r="D85">
-        <v>3029.988958950473</v>
+        <v>3045.016681378754</v>
       </c>
       <c r="E85">
-        <v>638.5170000000005</v>
+        <v>669.5160000000003</v>
       </c>
       <c r="F85">
-        <v>2572.917000000001</v>
+        <v>2603.916000000001</v>
       </c>
       <c r="G85">
         <v>513.2</v>
@@ -8251,28 +8251,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M85">
-        <v>142.2823101</v>
+        <v>143.9965548</v>
       </c>
       <c r="N85">
-        <v>641.2910232333334</v>
+        <v>639.5767785333334</v>
       </c>
       <c r="O85">
-        <v>159.9379811943934</v>
+        <v>159.5104485662133</v>
       </c>
       <c r="P85">
-        <v>481.35304203894</v>
+        <v>480.0663299671201</v>
       </c>
       <c r="Q85">
-        <v>488.61304203894</v>
+        <v>487.32632996712</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2445939727588671</v>
+        <v>0.2563543079010117</v>
       </c>
       <c r="T85">
-        <v>4.591084821220949</v>
+        <v>4.862686094711587</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.507173258450863</v>
+        <v>5.441611672040734</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07588356046416185</v>
+        <v>0.07573435615931631</v>
       </c>
       <c r="C86">
-        <v>954.3006813787551</v>
+        <v>938.4792116643625</v>
       </c>
       <c r="D86">
-        <v>3045.016681378755</v>
+        <v>3060.194211664363</v>
       </c>
       <c r="E86">
-        <v>669.5159999999998</v>
+        <v>700.5150000000001</v>
       </c>
       <c r="F86">
-        <v>2603.916</v>
+        <v>2634.915</v>
       </c>
       <c r="G86">
         <v>513.2</v>
@@ -8333,28 +8333,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M86">
-        <v>143.9965548</v>
+        <v>145.7107995</v>
       </c>
       <c r="N86">
-        <v>639.5767785333334</v>
+        <v>637.8625338333334</v>
       </c>
       <c r="O86">
-        <v>159.5104485662133</v>
+        <v>159.0829159380334</v>
       </c>
       <c r="P86">
-        <v>480.0663299671201</v>
+        <v>478.7796178953</v>
       </c>
       <c r="Q86">
-        <v>487.32632996712</v>
+        <v>486.0396178953</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2563543079010115</v>
+        <v>0.2696826877287754</v>
       </c>
       <c r="T86">
-        <v>4.862686094711584</v>
+        <v>5.170500871334306</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.441611672040735</v>
+        <v>5.377592711193196</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07573435615931631</v>
+        <v>0.07558515185447078</v>
       </c>
       <c r="C87">
-        <v>938.4792116643625</v>
+        <v>922.8098011280867</v>
       </c>
       <c r="D87">
-        <v>3060.194211664363</v>
+        <v>3075.523801128087</v>
       </c>
       <c r="E87">
-        <v>700.5150000000001</v>
+        <v>731.5139999999999</v>
       </c>
       <c r="F87">
-        <v>2634.915</v>
+        <v>2665.914</v>
       </c>
       <c r="G87">
         <v>513.2</v>
@@ -8415,28 +8415,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M87">
-        <v>145.7107995</v>
+        <v>147.4250442</v>
       </c>
       <c r="N87">
-        <v>637.8625338333334</v>
+        <v>636.1482891333334</v>
       </c>
       <c r="O87">
-        <v>159.0829159380334</v>
+        <v>158.6553833098534</v>
       </c>
       <c r="P87">
-        <v>478.7796178953</v>
+        <v>477.49290582348</v>
       </c>
       <c r="Q87">
-        <v>486.0396178953</v>
+        <v>484.75290582348</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2696826877287754</v>
+        <v>0.2849151218176484</v>
       </c>
       <c r="T87">
-        <v>5.170500871334306</v>
+        <v>5.522289187474558</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.377592711193196</v>
+        <v>5.315062563388624</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07558515185447078</v>
+        <v>0.07543594754962524</v>
       </c>
       <c r="C88">
-        <v>922.8098011280867</v>
+        <v>907.2947464284625</v>
       </c>
       <c r="D88">
-        <v>3075.523801128087</v>
+        <v>3091.007746428463</v>
       </c>
       <c r="E88">
-        <v>731.5139999999999</v>
+        <v>762.5130000000001</v>
       </c>
       <c r="F88">
-        <v>2665.914</v>
+        <v>2696.913</v>
       </c>
       <c r="G88">
         <v>513.2</v>
@@ -8497,28 +8497,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M88">
-        <v>147.4250442</v>
+        <v>149.1392889</v>
       </c>
       <c r="N88">
-        <v>636.1482891333334</v>
+        <v>634.4340444333334</v>
       </c>
       <c r="O88">
-        <v>158.6553833098534</v>
+        <v>158.2278506816733</v>
       </c>
       <c r="P88">
-        <v>477.49290582348</v>
+        <v>476.2061937516601</v>
       </c>
       <c r="Q88">
-        <v>484.75290582348</v>
+        <v>483.4661937516601</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2849151218176484</v>
+        <v>0.3024910073048094</v>
       </c>
       <c r="T88">
-        <v>5.522289187474558</v>
+        <v>5.928198783021004</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.315062563388624</v>
+        <v>5.253969890246227</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07543594754962524</v>
+        <v>0.07528674324477969</v>
       </c>
       <c r="C89">
-        <v>907.2947464284625</v>
+        <v>891.9363907088286</v>
       </c>
       <c r="D89">
-        <v>3091.007746428463</v>
+        <v>3106.648390708829</v>
       </c>
       <c r="E89">
-        <v>762.5130000000001</v>
+        <v>793.5120000000004</v>
       </c>
       <c r="F89">
-        <v>2696.913</v>
+        <v>2727.912000000001</v>
       </c>
       <c r="G89">
         <v>513.2</v>
@@ -8579,28 +8579,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M89">
-        <v>149.1392889</v>
+        <v>150.8535336</v>
       </c>
       <c r="N89">
-        <v>634.4340444333334</v>
+        <v>632.7197997333333</v>
       </c>
       <c r="O89">
-        <v>158.2278506816733</v>
+        <v>157.8003180534933</v>
       </c>
       <c r="P89">
-        <v>476.2061937516601</v>
+        <v>474.9194816798399</v>
       </c>
       <c r="Q89">
-        <v>483.4661937516601</v>
+        <v>482.1794816798399</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3024910073048094</v>
+        <v>0.3229962070398308</v>
       </c>
       <c r="T89">
-        <v>5.928198783021004</v>
+        <v>6.401759977825192</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.253969890246227</v>
+        <v>5.194265686947973</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07528674324477969</v>
+        <v>0.07513753893993413</v>
       </c>
       <c r="C90">
-        <v>891.9363907088286</v>
+        <v>876.7371247793749</v>
       </c>
       <c r="D90">
-        <v>3106.648390708829</v>
+        <v>3122.448124779375</v>
       </c>
       <c r="E90">
-        <v>793.5120000000004</v>
+        <v>824.5110000000002</v>
       </c>
       <c r="F90">
-        <v>2727.912000000001</v>
+        <v>2758.911000000001</v>
       </c>
       <c r="G90">
         <v>513.2</v>
@@ -8661,28 +8661,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M90">
-        <v>150.8535336</v>
+        <v>152.5677783</v>
       </c>
       <c r="N90">
-        <v>632.7197997333333</v>
+        <v>631.0055550333334</v>
       </c>
       <c r="O90">
-        <v>157.8003180534933</v>
+        <v>157.3727854253134</v>
       </c>
       <c r="P90">
-        <v>474.9194816798399</v>
+        <v>473.63276960802</v>
       </c>
       <c r="Q90">
-        <v>482.1794816798399</v>
+        <v>480.89276960802</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3229962070398308</v>
+        <v>0.3472296249084923</v>
       </c>
       <c r="T90">
-        <v>6.401759977825192</v>
+        <v>6.961423208048322</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.194265686947973</v>
+        <v>5.135903151139569</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07513753893993413</v>
+        <v>0.07498833463508861</v>
       </c>
       <c r="C91">
-        <v>876.7371247793749</v>
+        <v>861.6993883354617</v>
       </c>
       <c r="D91">
-        <v>3122.448124779375</v>
+        <v>3138.409388335463</v>
       </c>
       <c r="E91">
-        <v>824.5110000000002</v>
+        <v>855.5100000000004</v>
       </c>
       <c r="F91">
-        <v>2758.911000000001</v>
+        <v>2789.910000000001</v>
       </c>
       <c r="G91">
         <v>513.2</v>
@@ -8743,28 +8743,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M91">
-        <v>152.5677783</v>
+        <v>154.282023</v>
       </c>
       <c r="N91">
-        <v>631.0055550333334</v>
+        <v>629.2913103333333</v>
       </c>
       <c r="O91">
-        <v>157.3727854253134</v>
+        <v>156.9452527971333</v>
       </c>
       <c r="P91">
-        <v>473.63276960802</v>
+        <v>472.3460575362</v>
       </c>
       <c r="Q91">
-        <v>480.89276960802</v>
+        <v>479.6060575362</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3472296249084923</v>
+        <v>0.3763097263508862</v>
       </c>
       <c r="T91">
-        <v>6.961423208048322</v>
+        <v>7.633019084316078</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.135903151139569</v>
+        <v>5.078837560571351</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07498833463508861</v>
+        <v>0.07483913033024306</v>
       </c>
       <c r="C92">
-        <v>861.6993883354617</v>
+        <v>846.8256712134989</v>
       </c>
       <c r="D92">
-        <v>3138.409388335463</v>
+        <v>3154.534671213499</v>
       </c>
       <c r="E92">
-        <v>855.5100000000004</v>
+        <v>886.5090000000002</v>
       </c>
       <c r="F92">
-        <v>2789.910000000001</v>
+        <v>2820.909000000001</v>
       </c>
       <c r="G92">
         <v>513.2</v>
@@ -8825,28 +8825,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M92">
-        <v>154.282023</v>
+        <v>155.9962677</v>
       </c>
       <c r="N92">
-        <v>629.2913103333333</v>
+        <v>627.5770656333334</v>
       </c>
       <c r="O92">
-        <v>156.9452527971333</v>
+        <v>156.5177201689534</v>
       </c>
       <c r="P92">
-        <v>472.3460575362</v>
+        <v>471.05934546438</v>
       </c>
       <c r="Q92">
-        <v>479.6060575362</v>
+        <v>478.31934546438</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3763097263508862</v>
+        <v>0.4118520725582563</v>
       </c>
       <c r="T92">
-        <v>7.633019084316078</v>
+        <v>8.453858488643334</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.078837560571351</v>
+        <v>5.023026158806832</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07483913033024306</v>
+        <v>0.07468992602539754</v>
       </c>
       <c r="C93">
-        <v>846.8256712134989</v>
+        <v>832.1185146857083</v>
       </c>
       <c r="D93">
-        <v>3154.534671213499</v>
+        <v>3170.826514685709</v>
       </c>
       <c r="E93">
-        <v>886.5090000000002</v>
+        <v>917.5080000000005</v>
       </c>
       <c r="F93">
-        <v>2820.909000000001</v>
+        <v>2851.908000000001</v>
       </c>
       <c r="G93">
         <v>513.2</v>
@@ -8907,28 +8907,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M93">
-        <v>155.9962677</v>
+        <v>157.7105124000001</v>
       </c>
       <c r="N93">
-        <v>627.5770656333334</v>
+        <v>625.8628209333333</v>
       </c>
       <c r="O93">
-        <v>156.5177201689534</v>
+        <v>156.0901875407733</v>
       </c>
       <c r="P93">
-        <v>471.05934546438</v>
+        <v>469.77263339256</v>
       </c>
       <c r="Q93">
-        <v>478.31934546438</v>
+        <v>477.0326333925599</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4118520725582563</v>
+        <v>0.4562800053174693</v>
       </c>
       <c r="T93">
-        <v>8.453858488643334</v>
+        <v>9.47990774405241</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.023026158806832</v>
+        <v>4.968428048385017</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07468992602539754</v>
+        <v>0.07454072172055198</v>
       </c>
       <c r="C94">
-        <v>832.1185146857083</v>
+        <v>817.5805127952731</v>
       </c>
       <c r="D94">
-        <v>3170.826514685709</v>
+        <v>3187.287512795274</v>
       </c>
       <c r="E94">
-        <v>917.5080000000005</v>
+        <v>948.5070000000003</v>
       </c>
       <c r="F94">
-        <v>2851.908000000001</v>
+        <v>2882.907000000001</v>
       </c>
       <c r="G94">
         <v>513.2</v>
@@ -8989,28 +8989,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M94">
-        <v>157.7105124000001</v>
+        <v>159.4247571000001</v>
       </c>
       <c r="N94">
-        <v>625.8628209333333</v>
+        <v>624.1485762333333</v>
       </c>
       <c r="O94">
-        <v>156.0901875407733</v>
+        <v>155.6626549125933</v>
       </c>
       <c r="P94">
-        <v>469.77263339256</v>
+        <v>468.48592132074</v>
       </c>
       <c r="Q94">
-        <v>477.0326333925599</v>
+        <v>475.74592132074</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4562800053174693</v>
+        <v>0.5134016331507429</v>
       </c>
       <c r="T94">
-        <v>9.47990774405241</v>
+        <v>10.79911392957836</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.968428048385017</v>
+        <v>4.915004090875501</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07454072172055198</v>
+        <v>0.07439151741570643</v>
       </c>
       <c r="C95">
-        <v>817.5805127952731</v>
+        <v>803.2143137332287</v>
       </c>
       <c r="D95">
-        <v>3187.287512795274</v>
+        <v>3203.920313733229</v>
       </c>
       <c r="E95">
-        <v>948.5070000000003</v>
+        <v>979.5060000000005</v>
       </c>
       <c r="F95">
-        <v>2882.907000000001</v>
+        <v>2913.906000000001</v>
       </c>
       <c r="G95">
         <v>513.2</v>
@@ -9071,28 +9071,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M95">
-        <v>159.4247571000001</v>
+        <v>161.1390018</v>
       </c>
       <c r="N95">
-        <v>624.1485762333333</v>
+        <v>622.4343315333333</v>
       </c>
       <c r="O95">
-        <v>155.6626549125933</v>
+        <v>155.2351222844133</v>
       </c>
       <c r="P95">
-        <v>468.48592132074</v>
+        <v>467.1992092489199</v>
       </c>
       <c r="Q95">
-        <v>475.74592132074</v>
+        <v>474.4592092489199</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5134016331507429</v>
+        <v>0.5895638035951078</v>
       </c>
       <c r="T95">
-        <v>10.79911392957836</v>
+        <v>12.55805551027963</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.915004090875501</v>
+        <v>4.862716813312996</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07439151741570643</v>
+        <v>0.07424231311086091</v>
       </c>
       <c r="C96">
-        <v>803.2143137332287</v>
+        <v>789.0226212587368</v>
       </c>
       <c r="D96">
-        <v>3203.920313733229</v>
+        <v>3220.727621258737</v>
       </c>
       <c r="E96">
-        <v>979.5060000000005</v>
+        <v>1010.505</v>
       </c>
       <c r="F96">
-        <v>2913.906000000001</v>
+        <v>2944.905000000001</v>
       </c>
       <c r="G96">
         <v>513.2</v>
@@ -9153,28 +9153,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M96">
-        <v>161.1390018</v>
+        <v>162.8532465</v>
       </c>
       <c r="N96">
-        <v>622.4343315333333</v>
+        <v>620.7200868333333</v>
       </c>
       <c r="O96">
-        <v>155.2351222844133</v>
+        <v>154.8075896562333</v>
       </c>
       <c r="P96">
-        <v>467.1992092489199</v>
+        <v>465.9124971771</v>
       </c>
       <c r="Q96">
-        <v>474.4592092489199</v>
+        <v>473.1724971771</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5895638035951078</v>
+        <v>0.6961908422172189</v>
       </c>
       <c r="T96">
-        <v>12.55805551027963</v>
+        <v>15.02057372326141</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.862716813312996</v>
+        <v>4.81153032054128</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07424231311086091</v>
+        <v>0.07409310880601536</v>
       </c>
       <c r="C97">
-        <v>789.0226212587368</v>
+        <v>775.0081961642904</v>
       </c>
       <c r="D97">
-        <v>3220.727621258737</v>
+        <v>3237.712196164291</v>
       </c>
       <c r="E97">
-        <v>1010.505</v>
+        <v>1041.504000000001</v>
       </c>
       <c r="F97">
-        <v>2944.905000000001</v>
+        <v>2975.904000000001</v>
       </c>
       <c r="G97">
         <v>513.2</v>
@@ -9235,28 +9235,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M97">
-        <v>162.8532465</v>
+        <v>164.5674912000001</v>
       </c>
       <c r="N97">
-        <v>620.7200868333333</v>
+        <v>619.0058421333333</v>
       </c>
       <c r="O97">
-        <v>154.8075896562333</v>
+        <v>154.3800570280533</v>
       </c>
       <c r="P97">
-        <v>465.9124971771</v>
+        <v>464.62578510528</v>
       </c>
       <c r="Q97">
-        <v>473.1724971771</v>
+        <v>471.88578510528</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6961908422172189</v>
+        <v>0.8561314001503855</v>
       </c>
       <c r="T97">
-        <v>15.02057372326141</v>
+        <v>18.71435104273408</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.81153032054128</v>
+        <v>4.761410213035642</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07409310880601536</v>
+        <v>0.07394390450116983</v>
       </c>
       <c r="C98">
-        <v>775.0081961642909</v>
+        <v>761.173857787503</v>
       </c>
       <c r="D98">
-        <v>3237.712196164291</v>
+        <v>3254.876857787503</v>
       </c>
       <c r="E98">
-        <v>1041.504</v>
+        <v>1072.503</v>
       </c>
       <c r="F98">
-        <v>2975.904</v>
+        <v>3006.903</v>
       </c>
       <c r="G98">
         <v>513.2</v>
@@ -9317,28 +9317,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M98">
-        <v>164.5674912</v>
+        <v>166.2817359</v>
       </c>
       <c r="N98">
-        <v>619.0058421333333</v>
+        <v>617.2915974333333</v>
       </c>
       <c r="O98">
-        <v>154.3800570280533</v>
+        <v>153.9525243998733</v>
       </c>
       <c r="P98">
-        <v>464.62578510528</v>
+        <v>463.33907303346</v>
       </c>
       <c r="Q98">
-        <v>471.88578510528</v>
+        <v>470.5990730334599</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8561314001503832</v>
+        <v>1.12269899670566</v>
       </c>
       <c r="T98">
-        <v>18.71435104273403</v>
+        <v>24.87064657518845</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.761410213035642</v>
+        <v>4.712323509808471</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07394390450116983</v>
+        <v>0.07379470019632428</v>
       </c>
       <c r="C99">
-        <v>761.173857787503</v>
+        <v>747.5224855712727</v>
       </c>
       <c r="D99">
-        <v>3254.876857787503</v>
+        <v>3272.224485571273</v>
       </c>
       <c r="E99">
-        <v>1072.503</v>
+        <v>1103.502</v>
       </c>
       <c r="F99">
-        <v>3006.903</v>
+        <v>3037.902</v>
       </c>
       <c r="G99">
         <v>513.2</v>
@@ -9399,28 +9399,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M99">
-        <v>166.2817359</v>
+        <v>167.9959806</v>
       </c>
       <c r="N99">
-        <v>617.2915974333333</v>
+        <v>615.5773527333333</v>
       </c>
       <c r="O99">
-        <v>153.9525243998733</v>
+        <v>153.5249917716934</v>
       </c>
       <c r="P99">
-        <v>463.33907303346</v>
+        <v>462.05236096164</v>
       </c>
       <c r="Q99">
-        <v>470.5990730334599</v>
+        <v>469.31236096164</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.12269899670566</v>
+        <v>1.655834189816213</v>
       </c>
       <c r="T99">
-        <v>24.87064657518845</v>
+        <v>37.18323764009729</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.712323509808471</v>
+        <v>4.664238576034915</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07379470019632428</v>
+        <v>0.07364549589147873</v>
       </c>
       <c r="C100">
-        <v>747.5224855712727</v>
+        <v>734.0570206740781</v>
       </c>
       <c r="D100">
-        <v>3272.224485571273</v>
+        <v>3289.758020674078</v>
       </c>
       <c r="E100">
-        <v>1103.502</v>
+        <v>1134.501</v>
       </c>
       <c r="F100">
-        <v>3037.902</v>
+        <v>3068.901</v>
       </c>
       <c r="G100">
         <v>513.2</v>
@@ -9481,28 +9481,28 @@
         <v>783.5733333333334</v>
       </c>
       <c r="M100">
-        <v>167.9959806</v>
+        <v>169.7102253</v>
       </c>
       <c r="N100">
-        <v>615.5773527333333</v>
+        <v>613.8631080333333</v>
       </c>
       <c r="O100">
-        <v>153.5249917716934</v>
+        <v>153.0974591435133</v>
       </c>
       <c r="P100">
-        <v>462.05236096164</v>
+        <v>460.76564888982</v>
       </c>
       <c r="Q100">
-        <v>469.31236096164</v>
+        <v>468.02564888982</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.655834189816213</v>
+        <v>3.255239769147871</v>
       </c>
       <c r="T100">
-        <v>37.18323764009729</v>
+        <v>74.12101083482381</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.664238576034915</v>
+        <v>4.617125055064866</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07364549589147873</v>
-      </c>
-      <c r="C101">
-        <v>734.0570206740781</v>
-      </c>
-      <c r="D101">
-        <v>3289.758020674078</v>
-      </c>
-      <c r="E101">
-        <v>1134.501</v>
-      </c>
-      <c r="F101">
-        <v>3068.901</v>
-      </c>
-      <c r="G101">
-        <v>513.2</v>
-      </c>
-      <c r="H101">
-        <v>1165.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>790.8333333333334</v>
-      </c>
-      <c r="K101">
-        <v>7.26</v>
-      </c>
-      <c r="L101">
-        <v>783.5733333333334</v>
-      </c>
-      <c r="M101">
-        <v>169.7102253</v>
-      </c>
-      <c r="N101">
-        <v>613.8631080333333</v>
-      </c>
-      <c r="O101">
-        <v>153.0974591435133</v>
-      </c>
-      <c r="P101">
-        <v>460.76564888982</v>
-      </c>
-      <c r="Q101">
-        <v>468.02564888982</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.255239769147871</v>
-      </c>
-      <c r="T101">
-        <v>74.12101083482381</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.2494</v>
-      </c>
-      <c r="W101">
-        <v>0.04150818</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.617125055064866</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
